--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:58</t>
+          <t>2026-06-19 13:28:41</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:00</t>
+          <t>2026-06-19 13:28:43</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:02</t>
+          <t>2026-06-19 13:28:45</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:05</t>
+          <t>2026-06-19 13:28:47</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:07</t>
+          <t>2026-06-19 13:28:48</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:09</t>
+          <t>2026-06-19 13:28:50</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:11</t>
+          <t>2026-06-19 13:28:52</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:13</t>
+          <t>2026-06-19 13:28:53</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:14</t>
+          <t>2026-06-19 13:28:55</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:15</t>
+          <t>2026-06-19 13:28:57</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:18</t>
+          <t>2026-06-19 13:28:59</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:20</t>
+          <t>2026-06-19 13:29:01</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:23</t>
+          <t>2026-06-19 13:29:03</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:24</t>
+          <t>2026-06-19 13:29:04</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:26</t>
+          <t>2026-06-19 13:29:06</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:28</t>
+          <t>2026-06-19 13:29:08</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:29</t>
+          <t>2026-06-19 13:29:10</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:31</t>
+          <t>2026-06-19 13:29:11</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:34</t>
+          <t>2026-06-19 13:29:12</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:36</t>
+          <t>2026-06-19 13:29:14</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:38</t>
+          <t>2026-06-19 13:29:16</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:38</t>
+          <t>2026-06-19 13:29:18</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:40</t>
+          <t>2026-06-19 13:29:20</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:43</t>
+          <t>2026-06-19 13:29:22</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:45</t>
+          <t>2026-06-19 13:29:24</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:47</t>
+          <t>2026-06-19 13:29:26</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:49</t>
+          <t>2026-06-19 13:29:28</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:51</t>
+          <t>2026-06-19 13:29:29</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:54</t>
+          <t>2026-06-19 13:29:31</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:56</t>
+          <t>2026-06-19 13:29:32</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:58</t>
+          <t>2026-06-19 13:29:34</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:47:59</t>
+          <t>2026-06-19 13:29:35</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:01</t>
+          <t>2026-06-19 13:29:37</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:04</t>
+          <t>2026-06-19 13:29:38</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:06</t>
+          <t>2026-06-19 13:29:40</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:08</t>
+          <t>2026-06-19 13:29:41</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:10</t>
+          <t>2026-06-19 13:29:43</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:12</t>
+          <t>2026-06-19 13:29:44</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:14</t>
+          <t>2026-06-19 13:29:46</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:16</t>
+          <t>2026-06-19 13:29:47</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:18</t>
+          <t>2026-06-19 13:29:48</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:48:20</t>
+          <t>2026-06-19 13:29:50</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:26</t>
+          <t>2026-06-19 13:27:14</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:28</t>
+          <t>2026-06-19 13:27:15</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:30</t>
+          <t>2026-06-19 13:27:16</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:32</t>
+          <t>2026-06-19 13:27:18</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:34</t>
+          <t>2026-06-19 13:27:20</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:36</t>
+          <t>2026-06-19 13:27:22</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:38</t>
+          <t>2026-06-19 13:27:23</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:39</t>
+          <t>2026-06-19 13:27:25</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:41</t>
+          <t>2026-06-19 13:27:27</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:42</t>
+          <t>2026-06-19 13:27:29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:43</t>
+          <t>2026-06-19 13:27:31</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:45</t>
+          <t>2026-06-19 13:27:33</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:47</t>
+          <t>2026-06-19 13:27:35</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:48</t>
+          <t>2026-06-19 13:27:36</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:50</t>
+          <t>2026-06-19 13:27:38</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:51</t>
+          <t>2026-06-19 13:27:39</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:52</t>
+          <t>2026-06-19 13:27:41</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:55</t>
+          <t>2026-06-19 13:27:43</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:57</t>
+          <t>2026-06-19 13:27:45</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:58</t>
+          <t>2026-06-19 13:27:46</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:00</t>
+          <t>2026-06-19 13:27:48</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:02</t>
+          <t>2026-06-19 13:27:50</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:04</t>
+          <t>2026-06-19 13:27:51</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:06</t>
+          <t>2026-06-19 13:27:53</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:07</t>
+          <t>2026-06-19 13:27:54</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:09</t>
+          <t>2026-06-19 13:27:56</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:11</t>
+          <t>2026-06-19 13:27:58</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:13</t>
+          <t>2026-06-19 13:27:59</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:16</t>
+          <t>2026-06-19 13:28:01</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:17</t>
+          <t>2026-06-19 13:28:02</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:20</t>
+          <t>2026-06-19 13:28:04</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:22</t>
+          <t>2026-06-19 13:28:06</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:24</t>
+          <t>2026-06-19 13:28:08</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:26</t>
+          <t>2026-06-19 13:28:10</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:28</t>
+          <t>2026-06-19 13:28:12</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:30</t>
+          <t>2026-06-19 13:28:14</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:31</t>
+          <t>2026-06-19 13:28:15</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:33</t>
+          <t>2026-06-19 13:28:16</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:35</t>
+          <t>2026-06-19 13:28:18</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:37</t>
+          <t>2026-06-19 13:28:19</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:40</t>
+          <t>2026-06-19 13:28:21</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:41</t>
+          <t>2026-06-19 13:28:22</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:43</t>
+          <t>2026-06-19 13:28:24</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:45</t>
+          <t>2026-06-19 13:28:26</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:47</t>
+          <t>2026-06-19 13:28:28</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:49</t>
+          <t>2026-06-19 13:28:29</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:50</t>
+          <t>2026-06-19 13:28:32</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:52</t>
+          <t>2026-06-19 13:28:34</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:54</t>
+          <t>2026-06-19 13:28:36</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:46:56</t>
+          <t>2026-06-19 13:28:38</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:50</t>
+          <t>2026-06-19 13:25:44</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:52</t>
+          <t>2026-06-19 13:25:46</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:55</t>
+          <t>2026-06-19 13:25:48</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:57</t>
+          <t>2026-06-19 13:25:49</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:58</t>
+          <t>2026-06-19 13:25:51</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:01</t>
+          <t>2026-06-19 13:25:54</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:04</t>
+          <t>2026-06-19 13:25:55</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:05</t>
+          <t>2026-06-19 13:25:57</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:07</t>
+          <t>2026-06-19 13:26:00</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:09</t>
+          <t>2026-06-19 13:26:02</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:11</t>
+          <t>2026-06-19 13:26:03</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:13</t>
+          <t>2026-06-19 13:26:04</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:15</t>
+          <t>2026-06-19 13:26:07</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:17</t>
+          <t>2026-06-19 13:26:09</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:19</t>
+          <t>2026-06-19 13:26:11</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:21</t>
+          <t>2026-06-19 13:26:13</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:23</t>
+          <t>2026-06-19 13:26:15</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:25</t>
+          <t>2026-06-19 13:26:18</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:27</t>
+          <t>2026-06-19 13:26:20</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:29</t>
+          <t>2026-06-19 13:26:22</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:30</t>
+          <t>2026-06-19 13:26:24</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:32</t>
+          <t>2026-06-19 13:26:25</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:35</t>
+          <t>2026-06-19 13:26:26</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:37</t>
+          <t>2026-06-19 13:26:28</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:39</t>
+          <t>2026-06-19 13:26:30</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:40</t>
+          <t>2026-06-19 13:26:32</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:41</t>
+          <t>2026-06-19 13:26:33</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:43</t>
+          <t>2026-06-19 13:26:35</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:45</t>
+          <t>2026-06-19 13:26:37</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:46</t>
+          <t>2026-06-19 13:26:38</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:47</t>
+          <t>2026-06-19 13:26:40</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:50</t>
+          <t>2026-06-19 13:26:42</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:51</t>
+          <t>2026-06-19 13:26:43</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:52</t>
+          <t>2026-06-19 13:26:45</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:53</t>
+          <t>2026-06-19 13:26:47</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:55</t>
+          <t>2026-06-19 13:26:49</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:56</t>
+          <t>2026-06-19 13:26:50</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:44:58</t>
+          <t>2026-06-19 13:26:51</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:01</t>
+          <t>2026-06-19 13:26:53</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:04</t>
+          <t>2026-06-19 13:26:54</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:06</t>
+          <t>2026-06-19 13:26:56</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:08</t>
+          <t>2026-06-19 13:26:57</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:10</t>
+          <t>2026-06-19 13:26:59</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:12</t>
+          <t>2026-06-19 13:27:01</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:13</t>
+          <t>2026-06-19 13:27:03</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:15</t>
+          <t>2026-06-19 13:27:05</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:17</t>
+          <t>2026-06-19 13:27:07</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:19</t>
+          <t>2026-06-19 13:27:09</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:21</t>
+          <t>2026-06-19 13:27:11</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:45:24</t>
+          <t>2026-06-19 13:27:12</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:09</t>
+          <t>2026-06-19 13:24:18</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:11</t>
+          <t>2026-06-19 13:24:20</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:14</t>
+          <t>2026-06-19 13:24:21</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:16</t>
+          <t>2026-06-19 13:24:23</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:19</t>
+          <t>2026-06-19 13:24:25</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:21</t>
+          <t>2026-06-19 13:24:27</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:23</t>
+          <t>2026-06-19 13:24:29</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:25</t>
+          <t>2026-06-19 13:24:30</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:28</t>
+          <t>2026-06-19 13:24:32</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:30</t>
+          <t>2026-06-19 13:24:34</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:32</t>
+          <t>2026-06-19 13:24:36</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:34</t>
+          <t>2026-06-19 13:24:37</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:37</t>
+          <t>2026-06-19 13:24:39</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:39</t>
+          <t>2026-06-19 13:24:40</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:41</t>
+          <t>2026-06-19 13:24:42</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:43</t>
+          <t>2026-06-19 13:24:43</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:45</t>
+          <t>2026-06-19 13:24:45</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:48</t>
+          <t>2026-06-19 13:24:47</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:50</t>
+          <t>2026-06-19 13:24:48</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:52</t>
+          <t>2026-06-19 13:24:50</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:53</t>
+          <t>2026-06-19 13:24:52</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:56</t>
+          <t>2026-06-19 13:24:54</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:58</t>
+          <t>2026-06-19 13:24:55</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:59</t>
+          <t>2026-06-19 13:24:57</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:02</t>
+          <t>2026-06-19 13:24:59</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:04</t>
+          <t>2026-06-19 13:25:01</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:05</t>
+          <t>2026-06-19 13:25:02</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:08</t>
+          <t>2026-06-19 13:25:04</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:10</t>
+          <t>2026-06-19 13:25:06</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:12</t>
+          <t>2026-06-19 13:25:08</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:14</t>
+          <t>2026-06-19 13:25:10</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:16</t>
+          <t>2026-06-19 13:25:12</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:19</t>
+          <t>2026-06-19 13:25:13</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:21</t>
+          <t>2026-06-19 13:25:15</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:23</t>
+          <t>2026-06-19 13:25:17</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:24</t>
+          <t>2026-06-19 13:25:19</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:25</t>
+          <t>2026-06-19 13:25:21</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:27</t>
+          <t>2026-06-19 13:25:22</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:29</t>
+          <t>2026-06-19 13:25:24</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:30</t>
+          <t>2026-06-19 13:25:26</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:31</t>
+          <t>2026-06-19 13:25:28</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:33</t>
+          <t>2026-06-19 13:25:29</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:35</t>
+          <t>2026-06-19 13:25:31</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:37</t>
+          <t>2026-06-19 13:25:32</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:39</t>
+          <t>2026-06-19 13:25:34</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:41</t>
+          <t>2026-06-19 13:25:36</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:43</t>
+          <t>2026-06-19 13:25:37</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:45</t>
+          <t>2026-06-19 13:25:39</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:47</t>
+          <t>2026-06-19 13:25:41</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:43:49</t>
+          <t>2026-06-19 13:25:43</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:19</t>
+          <t>2026-06-19 13:22:44</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:20</t>
+          <t>2026-06-19 13:22:46</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:22</t>
+          <t>2026-06-19 13:22:48</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:24</t>
+          <t>2026-06-19 13:22:50</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:26</t>
+          <t>2026-06-19 13:22:52</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:29</t>
+          <t>2026-06-19 13:22:54</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:31</t>
+          <t>2026-06-19 13:22:56</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:33</t>
+          <t>2026-06-19 13:22:58</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:35</t>
+          <t>2026-06-19 13:23:00</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:37</t>
+          <t>2026-06-19 13:23:02</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:39</t>
+          <t>2026-06-19 13:23:04</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:42</t>
+          <t>2026-06-19 13:23:07</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:44</t>
+          <t>2026-06-19 13:23:10</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:46</t>
+          <t>2026-06-19 13:23:12</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:48</t>
+          <t>2026-06-19 13:23:14</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:50</t>
+          <t>2026-06-19 13:23:16</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:53</t>
+          <t>2026-06-19 13:23:18</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:55</t>
+          <t>2026-06-19 13:23:20</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:57</t>
+          <t>2026-06-19 13:23:21</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:40:59</t>
+          <t>2026-06-19 13:23:23</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:01</t>
+          <t>2026-06-19 13:23:25</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:04</t>
+          <t>2026-06-19 13:23:26</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:06</t>
+          <t>2026-06-19 13:23:28</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:09</t>
+          <t>2026-06-19 13:23:30</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:10</t>
+          <t>2026-06-19 13:23:32</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:12</t>
+          <t>2026-06-19 13:23:34</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:15</t>
+          <t>2026-06-19 13:23:35</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:17</t>
+          <t>2026-06-19 13:23:37</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:19</t>
+          <t>2026-06-19 13:23:39</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:22</t>
+          <t>2026-06-19 13:23:41</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:25</t>
+          <t>2026-06-19 13:23:42</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:27</t>
+          <t>2026-06-19 13:23:44</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:29</t>
+          <t>2026-06-19 13:23:46</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:32</t>
+          <t>2026-06-19 13:23:47</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:33</t>
+          <t>2026-06-19 13:23:49</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:35</t>
+          <t>2026-06-19 13:23:50</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:38</t>
+          <t>2026-06-19 13:23:52</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:40</t>
+          <t>2026-06-19 13:23:54</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:41</t>
+          <t>2026-06-19 13:23:55</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:43</t>
+          <t>2026-06-19 13:23:57</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:46</t>
+          <t>2026-06-19 13:23:59</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:48</t>
+          <t>2026-06-19 13:24:01</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:50</t>
+          <t>2026-06-19 13:24:03</t>
         </is>
       </c>
     </row>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:52</t>
+          <t>2026-06-19 13:24:05</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:56</t>
+          <t>2026-06-19 13:24:07</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:41:58</t>
+          <t>2026-06-19 13:24:09</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:00</t>
+          <t>2026-06-19 13:24:11</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:03</t>
+          <t>2026-06-19 13:24:13</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:05</t>
+          <t>2026-06-19 13:24:14</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 12:42:07</t>
+          <t>2026-06-19 13:24:16</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:41</t>
+          <t>2026-06-21 09:44:23</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:43</t>
+          <t>2026-06-21 09:44:24</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:45</t>
+          <t>2026-06-21 09:44:27</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:47</t>
+          <t>2026-06-21 09:44:29</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:48</t>
+          <t>2026-06-21 09:44:30</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:50</t>
+          <t>2026-06-21 09:44:32</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:52</t>
+          <t>2026-06-21 09:44:34</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:53</t>
+          <t>2026-06-21 09:44:36</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:55</t>
+          <t>2026-06-21 09:44:38</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:57</t>
+          <t>2026-06-21 09:44:40</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:59</t>
+          <t>2026-06-21 09:44:42</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:01</t>
+          <t>2026-06-21 09:44:43</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:03</t>
+          <t>2026-06-21 09:44:46</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:04</t>
+          <t>2026-06-21 09:44:47</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:06</t>
+          <t>2026-06-21 09:44:49</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:08</t>
+          <t>2026-06-21 09:44:51</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:10</t>
+          <t>2026-06-21 09:44:53</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:11</t>
+          <t>2026-06-21 09:44:54</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:12</t>
+          <t>2026-06-21 09:44:55</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:14</t>
+          <t>2026-06-21 09:44:57</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:16</t>
+          <t>2026-06-21 09:44:59</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:18</t>
+          <t>2026-06-21 09:45:01</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:20</t>
+          <t>2026-06-21 09:45:02</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:22</t>
+          <t>2026-06-21 09:45:04</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:24</t>
+          <t>2026-06-21 09:45:06</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:26</t>
+          <t>2026-06-21 09:45:08</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:28</t>
+          <t>2026-06-21 09:45:10</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:29</t>
+          <t>2026-06-21 09:45:12</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:31</t>
+          <t>2026-06-21 09:45:13</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:32</t>
+          <t>2026-06-21 09:45:15</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:34</t>
+          <t>2026-06-21 09:45:17</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:35</t>
+          <t>2026-06-21 09:45:18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:37</t>
+          <t>2026-06-21 09:45:20</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:38</t>
+          <t>2026-06-21 09:45:22</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:40</t>
+          <t>2026-06-21 09:45:24</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:41</t>
+          <t>2026-06-21 09:45:25</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:43</t>
+          <t>2026-06-21 09:45:26</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:44</t>
+          <t>2026-06-21 09:45:28</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:46</t>
+          <t>2026-06-21 09:45:29</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:47</t>
+          <t>2026-06-21 09:45:31</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:48</t>
+          <t>2026-06-21 09:45:33</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:29:50</t>
+          <t>2026-06-21 09:45:35</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:14</t>
+          <t>2026-06-21 09:43:03</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:15</t>
+          <t>2026-06-21 09:43:05</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:16</t>
+          <t>2026-06-21 09:43:07</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:18</t>
+          <t>2026-06-21 09:43:09</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:20</t>
+          <t>2026-06-21 09:43:10</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:22</t>
+          <t>2026-06-21 09:43:12</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:23</t>
+          <t>2026-06-21 09:43:14</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:25</t>
+          <t>2026-06-21 09:43:16</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:27</t>
+          <t>2026-06-21 09:43:17</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:29</t>
+          <t>2026-06-21 09:43:19</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:31</t>
+          <t>2026-06-21 09:43:20</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:33</t>
+          <t>2026-06-21 09:43:22</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:35</t>
+          <t>2026-06-21 09:43:24</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:36</t>
+          <t>2026-06-21 09:43:25</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:38</t>
+          <t>2026-06-21 09:43:26</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:39</t>
+          <t>2026-06-21 09:43:28</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:41</t>
+          <t>2026-06-21 09:43:30</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:43</t>
+          <t>2026-06-21 09:43:31</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:45</t>
+          <t>2026-06-21 09:43:33</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:46</t>
+          <t>2026-06-21 09:43:34</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:48</t>
+          <t>2026-06-21 09:43:36</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:50</t>
+          <t>2026-06-21 09:43:38</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:51</t>
+          <t>2026-06-21 09:43:40</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:53</t>
+          <t>2026-06-21 09:43:42</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:54</t>
+          <t>2026-06-21 09:43:43</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:56</t>
+          <t>2026-06-21 09:43:45</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:58</t>
+          <t>2026-06-21 09:43:47</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:59</t>
+          <t>2026-06-21 09:43:49</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:01</t>
+          <t>2026-06-21 09:43:50</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:02</t>
+          <t>2026-06-21 09:43:51</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:04</t>
+          <t>2026-06-21 09:43:52</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:06</t>
+          <t>2026-06-21 09:43:54</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:08</t>
+          <t>2026-06-21 09:43:55</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:10</t>
+          <t>2026-06-21 09:43:57</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:12</t>
+          <t>2026-06-21 09:43:58</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:14</t>
+          <t>2026-06-21 09:44:00</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:15</t>
+          <t>2026-06-21 09:44:01</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:16</t>
+          <t>2026-06-21 09:44:03</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:18</t>
+          <t>2026-06-21 09:44:04</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:19</t>
+          <t>2026-06-21 09:44:06</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:21</t>
+          <t>2026-06-21 09:44:07</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:22</t>
+          <t>2026-06-21 09:44:09</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:24</t>
+          <t>2026-06-21 09:44:10</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:26</t>
+          <t>2026-06-21 09:44:12</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:28</t>
+          <t>2026-06-21 09:44:13</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:29</t>
+          <t>2026-06-21 09:44:15</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:32</t>
+          <t>2026-06-21 09:44:16</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:34</t>
+          <t>2026-06-21 09:44:18</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:36</t>
+          <t>2026-06-21 09:44:19</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:28:38</t>
+          <t>2026-06-21 09:44:21</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:44</t>
+          <t>2026-06-21 09:41:46</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:46</t>
+          <t>2026-06-21 09:41:48</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:48</t>
+          <t>2026-06-21 09:41:49</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:49</t>
+          <t>2026-06-21 09:41:50</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:51</t>
+          <t>2026-06-21 09:41:52</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:54</t>
+          <t>2026-06-21 09:41:54</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:55</t>
+          <t>2026-06-21 09:41:55</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:57</t>
+          <t>2026-06-21 09:41:56</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:00</t>
+          <t>2026-06-21 09:41:57</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:02</t>
+          <t>2026-06-21 09:41:59</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:03</t>
+          <t>2026-06-21 09:42:00</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:04</t>
+          <t>2026-06-21 09:42:02</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:07</t>
+          <t>2026-06-21 09:42:03</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:09</t>
+          <t>2026-06-21 09:42:05</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:11</t>
+          <t>2026-06-21 09:42:07</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:13</t>
+          <t>2026-06-21 09:42:08</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:15</t>
+          <t>2026-06-21 09:42:10</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:18</t>
+          <t>2026-06-21 09:42:11</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:20</t>
+          <t>2026-06-21 09:42:13</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:22</t>
+          <t>2026-06-21 09:42:14</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:24</t>
+          <t>2026-06-21 09:42:16</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:25</t>
+          <t>2026-06-21 09:42:17</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:26</t>
+          <t>2026-06-21 09:42:19</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:28</t>
+          <t>2026-06-21 09:42:20</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:30</t>
+          <t>2026-06-21 09:42:22</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:32</t>
+          <t>2026-06-21 09:42:23</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:33</t>
+          <t>2026-06-21 09:42:25</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:35</t>
+          <t>2026-06-21 09:42:26</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:37</t>
+          <t>2026-06-21 09:42:28</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:38</t>
+          <t>2026-06-21 09:42:29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:40</t>
+          <t>2026-06-21 09:42:31</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:42</t>
+          <t>2026-06-21 09:42:32</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:43</t>
+          <t>2026-06-21 09:42:34</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:45</t>
+          <t>2026-06-21 09:42:36</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:47</t>
+          <t>2026-06-21 09:42:37</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:49</t>
+          <t>2026-06-21 09:42:39</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:50</t>
+          <t>2026-06-21 09:42:40</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:51</t>
+          <t>2026-06-21 09:42:42</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:53</t>
+          <t>2026-06-21 09:42:44</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:54</t>
+          <t>2026-06-21 09:42:46</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:56</t>
+          <t>2026-06-21 09:42:47</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:57</t>
+          <t>2026-06-21 09:42:49</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:26:59</t>
+          <t>2026-06-21 09:42:51</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:01</t>
+          <t>2026-06-21 09:42:52</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:03</t>
+          <t>2026-06-21 09:42:54</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:05</t>
+          <t>2026-06-21 09:42:55</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:07</t>
+          <t>2026-06-21 09:42:57</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:09</t>
+          <t>2026-06-21 09:42:58</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:11</t>
+          <t>2026-06-21 09:43:00</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:27:12</t>
+          <t>2026-06-21 09:43:01</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:18</t>
+          <t>2026-06-21 09:40:32</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:20</t>
+          <t>2026-06-21 09:40:34</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:21</t>
+          <t>2026-06-21 09:40:36</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:23</t>
+          <t>2026-06-21 09:40:37</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:25</t>
+          <t>2026-06-21 09:40:39</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:27</t>
+          <t>2026-06-21 09:40:40</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:29</t>
+          <t>2026-06-21 09:40:42</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:30</t>
+          <t>2026-06-21 09:40:43</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:32</t>
+          <t>2026-06-21 09:40:45</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:34</t>
+          <t>2026-06-21 09:40:46</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:36</t>
+          <t>2026-06-21 09:40:48</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:37</t>
+          <t>2026-06-21 09:40:50</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:39</t>
+          <t>2026-06-21 09:40:50</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:40</t>
+          <t>2026-06-21 09:40:52</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:42</t>
+          <t>2026-06-21 09:40:54</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:43</t>
+          <t>2026-06-21 09:40:56</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:45</t>
+          <t>2026-06-21 09:40:57</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:47</t>
+          <t>2026-06-21 09:40:59</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:48</t>
+          <t>2026-06-21 09:41:01</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:50</t>
+          <t>2026-06-21 09:41:02</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:52</t>
+          <t>2026-06-21 09:41:03</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:54</t>
+          <t>2026-06-21 09:41:05</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:55</t>
+          <t>2026-06-21 09:41:06</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:57</t>
+          <t>2026-06-21 09:41:08</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:59</t>
+          <t>2026-06-21 09:41:09</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:01</t>
+          <t>2026-06-21 09:41:11</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:02</t>
+          <t>2026-06-21 09:41:12</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:04</t>
+          <t>2026-06-21 09:41:13</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:06</t>
+          <t>2026-06-21 09:41:15</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:08</t>
+          <t>2026-06-21 09:41:17</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:10</t>
+          <t>2026-06-21 09:41:18</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:12</t>
+          <t>2026-06-21 09:41:20</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:13</t>
+          <t>2026-06-21 09:41:21</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:15</t>
+          <t>2026-06-21 09:41:22</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:17</t>
+          <t>2026-06-21 09:41:23</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:19</t>
+          <t>2026-06-21 09:41:24</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:21</t>
+          <t>2026-06-21 09:41:26</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:22</t>
+          <t>2026-06-21 09:41:28</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:24</t>
+          <t>2026-06-21 09:41:29</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:26</t>
+          <t>2026-06-21 09:41:31</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:28</t>
+          <t>2026-06-21 09:41:32</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:29</t>
+          <t>2026-06-21 09:41:34</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:31</t>
+          <t>2026-06-21 09:41:35</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:32</t>
+          <t>2026-06-21 09:41:37</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:34</t>
+          <t>2026-06-21 09:41:38</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:36</t>
+          <t>2026-06-21 09:41:39</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:37</t>
+          <t>2026-06-21 09:41:41</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:39</t>
+          <t>2026-06-21 09:41:42</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:41</t>
+          <t>2026-06-21 09:41:43</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:25:43</t>
+          <t>2026-06-21 09:41:45</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:44</t>
+          <t>2026-06-21 09:39:15</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:46</t>
+          <t>2026-06-21 09:39:17</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:48</t>
+          <t>2026-06-21 09:39:18</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:50</t>
+          <t>2026-06-21 09:39:20</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:52</t>
+          <t>2026-06-21 09:39:21</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:54</t>
+          <t>2026-06-21 09:39:23</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:56</t>
+          <t>2026-06-21 09:39:25</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:22:58</t>
+          <t>2026-06-21 09:39:26</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:00</t>
+          <t>2026-06-21 09:39:28</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:02</t>
+          <t>2026-06-21 09:39:30</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:04</t>
+          <t>2026-06-21 09:39:31</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:07</t>
+          <t>2026-06-21 09:39:33</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:10</t>
+          <t>2026-06-21 09:39:36</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:12</t>
+          <t>2026-06-21 09:39:37</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:14</t>
+          <t>2026-06-21 09:39:39</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:16</t>
+          <t>2026-06-21 09:39:40</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:18</t>
+          <t>2026-06-21 09:39:42</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:20</t>
+          <t>2026-06-21 09:39:44</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:21</t>
+          <t>2026-06-21 09:39:45</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:23</t>
+          <t>2026-06-21 09:39:47</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:25</t>
+          <t>2026-06-21 09:39:48</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:26</t>
+          <t>2026-06-21 09:39:50</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:28</t>
+          <t>2026-06-21 09:39:51</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:30</t>
+          <t>2026-06-21 09:39:53</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:32</t>
+          <t>2026-06-21 09:39:54</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:34</t>
+          <t>2026-06-21 09:39:56</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:35</t>
+          <t>2026-06-21 09:39:57</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:37</t>
+          <t>2026-06-21 09:39:58</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:39</t>
+          <t>2026-06-21 09:40:00</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:41</t>
+          <t>2026-06-21 09:40:02</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:42</t>
+          <t>2026-06-21 09:40:03</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:44</t>
+          <t>2026-06-21 09:40:05</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:46</t>
+          <t>2026-06-21 09:40:06</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:47</t>
+          <t>2026-06-21 09:40:07</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:49</t>
+          <t>2026-06-21 09:40:08</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:50</t>
+          <t>2026-06-21 09:40:10</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:52</t>
+          <t>2026-06-21 09:40:12</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:54</t>
+          <t>2026-06-21 09:40:13</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:55</t>
+          <t>2026-06-21 09:40:15</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:57</t>
+          <t>2026-06-21 09:40:16</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:23:59</t>
+          <t>2026-06-21 09:40:18</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:01</t>
+          <t>2026-06-21 09:40:19</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:03</t>
+          <t>2026-06-21 09:40:20</t>
         </is>
       </c>
     </row>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:05</t>
+          <t>2026-06-21 09:40:22</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:07</t>
+          <t>2026-06-21 09:40:23</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:09</t>
+          <t>2026-06-21 09:40:24</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:11</t>
+          <t>2026-06-21 09:40:26</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:13</t>
+          <t>2026-06-21 09:40:28</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:14</t>
+          <t>2026-06-21 09:40:29</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-19 13:24:16</t>
+          <t>2026-06-21 09:40:31</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:23</t>
+          <t>2026-06-28 08:49:42</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:24</t>
+          <t>2026-06-28 08:49:44</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:27</t>
+          <t>2026-06-28 08:49:46</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:29</t>
+          <t>2026-06-28 08:49:47</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:30</t>
+          <t>2026-06-28 08:49:49</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:32</t>
+          <t>2026-06-28 08:49:51</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:34</t>
+          <t>2026-06-28 08:49:54</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:36</t>
+          <t>2026-06-28 08:49:57</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:38</t>
+          <t>2026-06-28 08:49:59</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:40</t>
+          <t>2026-06-28 08:50:00</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:42</t>
+          <t>2026-06-28 08:50:02</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:43</t>
+          <t>2026-06-28 08:50:04</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:46</t>
+          <t>2026-06-28 08:50:06</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:47</t>
+          <t>2026-06-28 08:50:08</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:49</t>
+          <t>2026-06-28 08:50:09</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:51</t>
+          <t>2026-06-28 08:50:10</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:53</t>
+          <t>2026-06-28 08:50:12</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:54</t>
+          <t>2026-06-28 08:50:14</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:55</t>
+          <t>2026-06-28 08:50:16</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:57</t>
+          <t>2026-06-28 08:50:18</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:59</t>
+          <t>2026-06-28 08:50:19</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:01</t>
+          <t>2026-06-28 08:50:21</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:02</t>
+          <t>2026-06-28 08:50:23</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:04</t>
+          <t>2026-06-28 08:50:24</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:06</t>
+          <t>2026-06-28 08:50:26</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:08</t>
+          <t>2026-06-28 08:50:28</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:10</t>
+          <t>2026-06-28 08:50:29</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:12</t>
+          <t>2026-06-28 08:50:31</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:13</t>
+          <t>2026-06-28 08:50:33</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:15</t>
+          <t>2026-06-28 08:50:34</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:17</t>
+          <t>2026-06-28 08:50:36</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:18</t>
+          <t>2026-06-28 08:50:37</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:20</t>
+          <t>2026-06-28 08:50:39</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:22</t>
+          <t>2026-06-28 08:50:41</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:24</t>
+          <t>2026-06-28 08:50:42</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:25</t>
+          <t>2026-06-28 08:50:44</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:26</t>
+          <t>2026-06-28 08:50:46</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:28</t>
+          <t>2026-06-28 08:50:47</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:29</t>
+          <t>2026-06-28 08:50:49</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:31</t>
+          <t>2026-06-28 08:50:50</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:33</t>
+          <t>2026-06-28 08:50:51</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:45:35</t>
+          <t>2026-06-28 08:50:53</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:03</t>
+          <t>2026-06-28 08:48:13</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:05</t>
+          <t>2026-06-28 08:48:15</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:07</t>
+          <t>2026-06-28 08:48:17</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:09</t>
+          <t>2026-06-28 08:48:19</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:10</t>
+          <t>2026-06-28 08:48:21</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:12</t>
+          <t>2026-06-28 08:48:23</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:14</t>
+          <t>2026-06-28 08:48:24</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:16</t>
+          <t>2026-06-28 08:48:26</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:17</t>
+          <t>2026-06-28 08:48:28</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:19</t>
+          <t>2026-06-28 08:48:29</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:20</t>
+          <t>2026-06-28 08:48:31</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:22</t>
+          <t>2026-06-28 08:48:33</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:24</t>
+          <t>2026-06-28 08:48:35</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:25</t>
+          <t>2026-06-28 08:48:37</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:26</t>
+          <t>2026-06-28 08:48:39</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:28</t>
+          <t>2026-06-28 08:48:41</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:30</t>
+          <t>2026-06-28 08:48:43</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:31</t>
+          <t>2026-06-28 08:48:44</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:33</t>
+          <t>2026-06-28 08:48:46</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:34</t>
+          <t>2026-06-28 08:48:48</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:36</t>
+          <t>2026-06-28 08:48:49</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:38</t>
+          <t>2026-06-28 08:48:50</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:40</t>
+          <t>2026-06-28 08:48:52</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:42</t>
+          <t>2026-06-28 08:48:54</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:43</t>
+          <t>2026-06-28 08:48:56</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:45</t>
+          <t>2026-06-28 08:48:58</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:47</t>
+          <t>2026-06-28 08:49:00</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:49</t>
+          <t>2026-06-28 08:49:02</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:50</t>
+          <t>2026-06-28 08:49:05</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:51</t>
+          <t>2026-06-28 08:49:06</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:52</t>
+          <t>2026-06-28 08:49:07</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:54</t>
+          <t>2026-06-28 08:49:08</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:55</t>
+          <t>2026-06-28 08:49:10</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:57</t>
+          <t>2026-06-28 08:49:12</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:58</t>
+          <t>2026-06-28 08:49:14</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:00</t>
+          <t>2026-06-28 08:49:15</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:01</t>
+          <t>2026-06-28 08:49:17</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:03</t>
+          <t>2026-06-28 08:49:19</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:04</t>
+          <t>2026-06-28 08:49:19</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:06</t>
+          <t>2026-06-28 08:49:21</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:07</t>
+          <t>2026-06-28 08:49:23</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:09</t>
+          <t>2026-06-28 08:49:25</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:10</t>
+          <t>2026-06-28 08:49:27</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:12</t>
+          <t>2026-06-28 08:49:29</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:13</t>
+          <t>2026-06-28 08:49:31</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:15</t>
+          <t>2026-06-28 08:49:33</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:16</t>
+          <t>2026-06-28 08:49:35</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:18</t>
+          <t>2026-06-28 08:49:37</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:19</t>
+          <t>2026-06-28 08:49:39</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:44:21</t>
+          <t>2026-06-28 08:49:41</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:46</t>
+          <t>2026-06-28 08:46:39</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:48</t>
+          <t>2026-06-28 08:46:41</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:49</t>
+          <t>2026-06-28 08:46:43</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:50</t>
+          <t>2026-06-28 08:46:44</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:52</t>
+          <t>2026-06-28 08:46:46</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:54</t>
+          <t>2026-06-28 08:46:48</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:55</t>
+          <t>2026-06-28 08:46:50</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:56</t>
+          <t>2026-06-28 08:46:52</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:57</t>
+          <t>2026-06-28 08:46:53</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:59</t>
+          <t>2026-06-28 08:46:55</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:00</t>
+          <t>2026-06-28 08:46:57</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:02</t>
+          <t>2026-06-28 08:47:00</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:03</t>
+          <t>2026-06-28 08:47:01</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:05</t>
+          <t>2026-06-28 08:47:03</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:07</t>
+          <t>2026-06-28 08:47:05</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:08</t>
+          <t>2026-06-28 08:47:08</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:10</t>
+          <t>2026-06-28 08:47:10</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:11</t>
+          <t>2026-06-28 08:47:12</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:13</t>
+          <t>2026-06-28 08:47:14</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:14</t>
+          <t>2026-06-28 08:47:15</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:16</t>
+          <t>2026-06-28 08:47:17</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:17</t>
+          <t>2026-06-28 08:47:19</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:19</t>
+          <t>2026-06-28 08:47:21</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:20</t>
+          <t>2026-06-28 08:47:23</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:22</t>
+          <t>2026-06-28 08:47:25</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:23</t>
+          <t>2026-06-28 08:47:27</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:25</t>
+          <t>2026-06-28 08:47:29</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:26</t>
+          <t>2026-06-28 08:47:31</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:28</t>
+          <t>2026-06-28 08:47:33</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:29</t>
+          <t>2026-06-28 08:47:35</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:31</t>
+          <t>2026-06-28 08:47:37</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:32</t>
+          <t>2026-06-28 08:47:39</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:34</t>
+          <t>2026-06-28 08:47:41</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:36</t>
+          <t>2026-06-28 08:47:43</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:37</t>
+          <t>2026-06-28 08:47:45</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:39</t>
+          <t>2026-06-28 08:47:46</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:40</t>
+          <t>2026-06-28 08:47:48</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:42</t>
+          <t>2026-06-28 08:47:50</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:44</t>
+          <t>2026-06-28 08:47:51</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:46</t>
+          <t>2026-06-28 08:47:53</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:47</t>
+          <t>2026-06-28 08:47:55</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:49</t>
+          <t>2026-06-28 08:47:57</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:51</t>
+          <t>2026-06-28 08:47:58</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:52</t>
+          <t>2026-06-28 08:48:00</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:54</t>
+          <t>2026-06-28 08:48:02</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:55</t>
+          <t>2026-06-28 08:48:04</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:57</t>
+          <t>2026-06-28 08:48:06</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:42:58</t>
+          <t>2026-06-28 08:48:08</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:00</t>
+          <t>2026-06-28 08:48:10</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:43:01</t>
+          <t>2026-06-28 08:48:11</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:32</t>
+          <t>2026-06-28 08:45:12</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:34</t>
+          <t>2026-06-28 08:45:14</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:36</t>
+          <t>2026-06-28 08:45:15</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:37</t>
+          <t>2026-06-28 08:45:17</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:39</t>
+          <t>2026-06-28 08:45:18</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:40</t>
+          <t>2026-06-28 08:45:20</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:42</t>
+          <t>2026-06-28 08:45:22</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:43</t>
+          <t>2026-06-28 08:45:23</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:45</t>
+          <t>2026-06-28 08:45:25</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:46</t>
+          <t>2026-06-28 08:45:27</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:48</t>
+          <t>2026-06-28 08:45:28</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:50</t>
+          <t>2026-06-28 08:45:30</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:50</t>
+          <t>2026-06-28 08:45:31</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:52</t>
+          <t>2026-06-28 08:45:33</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:54</t>
+          <t>2026-06-28 08:45:35</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:56</t>
+          <t>2026-06-28 08:45:36</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:57</t>
+          <t>2026-06-28 08:45:37</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:59</t>
+          <t>2026-06-28 08:45:39</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:01</t>
+          <t>2026-06-28 08:45:41</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:02</t>
+          <t>2026-06-28 08:45:43</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:03</t>
+          <t>2026-06-28 08:45:45</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:05</t>
+          <t>2026-06-28 08:45:47</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:06</t>
+          <t>2026-06-28 08:45:48</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:08</t>
+          <t>2026-06-28 08:45:50</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:09</t>
+          <t>2026-06-28 08:45:52</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:11</t>
+          <t>2026-06-28 08:45:54</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:12</t>
+          <t>2026-06-28 08:45:55</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:13</t>
+          <t>2026-06-28 08:45:56</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:15</t>
+          <t>2026-06-28 08:45:58</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:17</t>
+          <t>2026-06-28 08:45:59</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:18</t>
+          <t>2026-06-28 08:46:00</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:20</t>
+          <t>2026-06-28 08:46:02</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:21</t>
+          <t>2026-06-28 08:46:04</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:22</t>
+          <t>2026-06-28 08:46:06</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:23</t>
+          <t>2026-06-28 08:46:08</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:24</t>
+          <t>2026-06-28 08:46:09</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:26</t>
+          <t>2026-06-28 08:46:11</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:28</t>
+          <t>2026-06-28 08:46:13</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:29</t>
+          <t>2026-06-28 08:46:15</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:31</t>
+          <t>2026-06-28 08:46:17</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:32</t>
+          <t>2026-06-28 08:46:20</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:34</t>
+          <t>2026-06-28 08:46:22</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:35</t>
+          <t>2026-06-28 08:46:24</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:37</t>
+          <t>2026-06-28 08:46:26</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:38</t>
+          <t>2026-06-28 08:46:28</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:39</t>
+          <t>2026-06-28 08:46:30</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:41</t>
+          <t>2026-06-28 08:46:32</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:42</t>
+          <t>2026-06-28 08:46:34</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:43</t>
+          <t>2026-06-28 08:46:36</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:41:45</t>
+          <t>2026-06-28 08:46:37</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:15</t>
+          <t>2026-06-28 08:43:48</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:17</t>
+          <t>2026-06-28 08:43:50</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:18</t>
+          <t>2026-06-28 08:43:51</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:20</t>
+          <t>2026-06-28 08:43:53</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:21</t>
+          <t>2026-06-28 08:43:54</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:23</t>
+          <t>2026-06-28 08:43:56</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:25</t>
+          <t>2026-06-28 08:43:57</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:26</t>
+          <t>2026-06-28 08:43:59</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:28</t>
+          <t>2026-06-28 08:44:01</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:30</t>
+          <t>2026-06-28 08:44:02</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:31</t>
+          <t>2026-06-28 08:44:04</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:33</t>
+          <t>2026-06-28 08:44:06</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:36</t>
+          <t>2026-06-28 08:44:08</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:37</t>
+          <t>2026-06-28 08:44:09</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:39</t>
+          <t>2026-06-28 08:44:11</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:40</t>
+          <t>2026-06-28 08:44:13</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:42</t>
+          <t>2026-06-28 08:44:15</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:44</t>
+          <t>2026-06-28 08:44:16</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:45</t>
+          <t>2026-06-28 08:44:18</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:47</t>
+          <t>2026-06-28 08:44:20</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:48</t>
+          <t>2026-06-28 08:44:21</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:50</t>
+          <t>2026-06-28 08:44:23</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:51</t>
+          <t>2026-06-28 08:44:24</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:53</t>
+          <t>2026-06-28 08:44:26</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:54</t>
+          <t>2026-06-28 08:44:27</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:56</t>
+          <t>2026-06-28 08:44:29</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:57</t>
+          <t>2026-06-28 08:44:31</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:39:58</t>
+          <t>2026-06-28 08:44:33</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:00</t>
+          <t>2026-06-28 08:44:34</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:02</t>
+          <t>2026-06-28 08:44:36</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:03</t>
+          <t>2026-06-28 08:44:38</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:05</t>
+          <t>2026-06-28 08:44:40</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:06</t>
+          <t>2026-06-28 08:44:41</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:07</t>
+          <t>2026-06-28 08:44:43</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:08</t>
+          <t>2026-06-28 08:44:45</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:10</t>
+          <t>2026-06-28 08:44:46</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:12</t>
+          <t>2026-06-28 08:44:48</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:13</t>
+          <t>2026-06-28 08:44:50</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:15</t>
+          <t>2026-06-28 08:44:52</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:16</t>
+          <t>2026-06-28 08:44:53</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:18</t>
+          <t>2026-06-28 08:44:55</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:19</t>
+          <t>2026-06-28 08:44:56</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:20</t>
+          <t>2026-06-28 08:44:58</t>
         </is>
       </c>
     </row>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:22</t>
+          <t>2026-06-28 08:44:59</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:23</t>
+          <t>2026-06-28 08:45:01</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:24</t>
+          <t>2026-06-28 08:45:03</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:26</t>
+          <t>2026-06-28 08:45:05</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:28</t>
+          <t>2026-06-28 08:45:07</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:29</t>
+          <t>2026-06-28 08:45:08</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21 09:40:31</t>
+          <t>2026-06-28 08:45:10</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:42</t>
+          <t>2026-07-05 08:50:55</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:44</t>
+          <t>2026-07-05 08:50:57</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:46</t>
+          <t>2026-07-05 08:51:00</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:47</t>
+          <t>2026-07-05 08:51:02</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:49</t>
+          <t>2026-07-05 08:51:04</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:51</t>
+          <t>2026-07-05 08:51:12</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:54</t>
+          <t>2026-07-05 08:51:28</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:57</t>
+          <t>2026-07-05 08:51:35</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:59</t>
+          <t>2026-07-05 08:51:40</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:00</t>
+          <t>2026-07-05 08:51:43</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:02</t>
+          <t>2026-07-05 08:51:47</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:04</t>
+          <t>2026-07-05 08:51:49</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:06</t>
+          <t>2026-07-05 08:51:52</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:08</t>
+          <t>2026-07-05 08:51:55</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:09</t>
+          <t>2026-07-05 08:51:57</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:10</t>
+          <t>2026-07-05 08:51:59</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:12</t>
+          <t>2026-07-05 08:52:01</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:14</t>
+          <t>2026-07-05 08:52:04</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:16</t>
+          <t>2026-07-05 08:52:06</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:18</t>
+          <t>2026-07-05 08:52:07</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:19</t>
+          <t>2026-07-05 08:52:10</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:21</t>
+          <t>2026-07-05 08:52:12</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:23</t>
+          <t>2026-07-05 08:52:14</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:24</t>
+          <t>2026-07-05 08:52:16</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:26</t>
+          <t>2026-07-05 08:52:18</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:28</t>
+          <t>2026-07-05 08:52:19</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:29</t>
+          <t>2026-07-05 08:52:21</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:31</t>
+          <t>2026-07-05 08:52:23</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:33</t>
+          <t>2026-07-05 08:52:25</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:34</t>
+          <t>2026-07-05 08:52:27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:36</t>
+          <t>2026-07-05 08:52:30</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:37</t>
+          <t>2026-07-05 08:52:32</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:39</t>
+          <t>2026-07-05 08:52:34</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:41</t>
+          <t>2026-07-05 08:52:36</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:42</t>
+          <t>2026-07-05 08:52:38</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:44</t>
+          <t>2026-07-05 08:52:40</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:46</t>
+          <t>2026-07-05 08:52:42</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:47</t>
+          <t>2026-07-05 08:52:43</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:49</t>
+          <t>2026-07-05 08:52:45</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:50</t>
+          <t>2026-07-05 08:52:47</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:51</t>
+          <t>2026-07-05 08:52:49</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:50:53</t>
+          <t>2026-07-05 08:52:51</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:13</t>
+          <t>2026-07-05 08:49:17</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:15</t>
+          <t>2026-07-05 08:49:19</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:17</t>
+          <t>2026-07-05 08:49:21</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:19</t>
+          <t>2026-07-05 08:49:23</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:21</t>
+          <t>2026-07-05 08:49:25</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:23</t>
+          <t>2026-07-05 08:49:27</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:24</t>
+          <t>2026-07-05 08:49:29</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:26</t>
+          <t>2026-07-05 08:49:31</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:28</t>
+          <t>2026-07-05 08:49:33</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:29</t>
+          <t>2026-07-05 08:49:35</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:31</t>
+          <t>2026-07-05 08:49:37</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:33</t>
+          <t>2026-07-05 08:49:39</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:35</t>
+          <t>2026-07-05 08:49:41</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:37</t>
+          <t>2026-07-05 08:49:42</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:39</t>
+          <t>2026-07-05 08:49:44</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:41</t>
+          <t>2026-07-05 08:49:46</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:43</t>
+          <t>2026-07-05 08:49:48</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:44</t>
+          <t>2026-07-05 08:49:50</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:46</t>
+          <t>2026-07-05 08:49:52</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:48</t>
+          <t>2026-07-05 08:49:55</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:49</t>
+          <t>2026-07-05 08:49:57</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:50</t>
+          <t>2026-07-05 08:49:59</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:52</t>
+          <t>2026-07-05 08:50:01</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:54</t>
+          <t>2026-07-05 08:50:02</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:56</t>
+          <t>2026-07-05 08:50:04</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:58</t>
+          <t>2026-07-05 08:50:07</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:00</t>
+          <t>2026-07-05 08:50:09</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:02</t>
+          <t>2026-07-05 08:50:11</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:05</t>
+          <t>2026-07-05 08:50:13</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:06</t>
+          <t>2026-07-05 08:50:15</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:07</t>
+          <t>2026-07-05 08:50:18</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:08</t>
+          <t>2026-07-05 08:50:20</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:10</t>
+          <t>2026-07-05 08:50:22</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:12</t>
+          <t>2026-07-05 08:50:24</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:14</t>
+          <t>2026-07-05 08:50:27</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:15</t>
+          <t>2026-07-05 08:50:28</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:17</t>
+          <t>2026-07-05 08:50:30</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:19</t>
+          <t>2026-07-05 08:50:32</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:19</t>
+          <t>2026-07-05 08:50:33</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:21</t>
+          <t>2026-07-05 08:50:35</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:23</t>
+          <t>2026-07-05 08:50:37</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:25</t>
+          <t>2026-07-05 08:50:39</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:27</t>
+          <t>2026-07-05 08:50:41</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:29</t>
+          <t>2026-07-05 08:50:43</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:31</t>
+          <t>2026-07-05 08:50:44</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:33</t>
+          <t>2026-07-05 08:50:46</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:35</t>
+          <t>2026-07-05 08:50:47</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:37</t>
+          <t>2026-07-05 08:50:49</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:39</t>
+          <t>2026-07-05 08:50:51</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:49:41</t>
+          <t>2026-07-05 08:50:53</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:39</t>
+          <t>2026-07-05 08:47:43</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:41</t>
+          <t>2026-07-05 08:47:45</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:43</t>
+          <t>2026-07-05 08:47:47</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:44</t>
+          <t>2026-07-05 08:47:49</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:46</t>
+          <t>2026-07-05 08:47:51</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:48</t>
+          <t>2026-07-05 08:47:52</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:50</t>
+          <t>2026-07-05 08:47:54</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:52</t>
+          <t>2026-07-05 08:47:56</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:53</t>
+          <t>2026-07-05 08:47:58</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:55</t>
+          <t>2026-07-05 08:48:00</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:57</t>
+          <t>2026-07-05 08:48:02</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:00</t>
+          <t>2026-07-05 08:48:04</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:01</t>
+          <t>2026-07-05 08:48:05</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:03</t>
+          <t>2026-07-05 08:48:06</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:05</t>
+          <t>2026-07-05 08:48:08</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:08</t>
+          <t>2026-07-05 08:48:10</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:10</t>
+          <t>2026-07-05 08:48:12</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:12</t>
+          <t>2026-07-05 08:48:14</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:14</t>
+          <t>2026-07-05 08:48:15</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:15</t>
+          <t>2026-07-05 08:48:17</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:17</t>
+          <t>2026-07-05 08:48:20</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:19</t>
+          <t>2026-07-05 08:48:21</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:21</t>
+          <t>2026-07-05 08:48:23</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:23</t>
+          <t>2026-07-05 08:48:25</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:25</t>
+          <t>2026-07-05 08:48:27</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:27</t>
+          <t>2026-07-05 08:48:29</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:29</t>
+          <t>2026-07-05 08:48:32</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:31</t>
+          <t>2026-07-05 08:48:33</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:33</t>
+          <t>2026-07-05 08:48:35</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:35</t>
+          <t>2026-07-05 08:48:37</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:37</t>
+          <t>2026-07-05 08:48:39</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:39</t>
+          <t>2026-07-05 08:48:41</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:41</t>
+          <t>2026-07-05 08:48:43</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:43</t>
+          <t>2026-07-05 08:48:45</t>
         </is>
       </c>
     </row>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:45</t>
+          <t>2026-07-05 08:48:46</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:46</t>
+          <t>2026-07-05 08:48:48</t>
         </is>
       </c>
     </row>
@@ -8596,7 +8596,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:48</t>
+          <t>2026-07-05 08:48:50</t>
         </is>
       </c>
     </row>
@@ -8658,7 +8658,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:50</t>
+          <t>2026-07-05 08:48:52</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:51</t>
+          <t>2026-07-05 08:48:54</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:53</t>
+          <t>2026-07-05 08:48:56</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:55</t>
+          <t>2026-07-05 08:48:58</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:57</t>
+          <t>2026-07-05 08:49:00</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:47:58</t>
+          <t>2026-07-05 08:49:02</t>
         </is>
       </c>
     </row>
@@ -9030,7 +9030,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:00</t>
+          <t>2026-07-05 08:49:04</t>
         </is>
       </c>
     </row>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:02</t>
+          <t>2026-07-05 08:49:05</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:04</t>
+          <t>2026-07-05 08:49:07</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:06</t>
+          <t>2026-07-05 08:49:10</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:08</t>
+          <t>2026-07-05 08:49:11</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:10</t>
+          <t>2026-07-05 08:49:13</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:48:11</t>
+          <t>2026-07-05 08:49:15</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:12</t>
+          <t>2026-07-05 08:46:01</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:14</t>
+          <t>2026-07-05 08:46:02</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9588,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:15</t>
+          <t>2026-07-05 08:46:05</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:17</t>
+          <t>2026-07-05 08:46:07</t>
         </is>
       </c>
     </row>
@@ -9712,7 +9712,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:18</t>
+          <t>2026-07-05 08:46:08</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9774,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:20</t>
+          <t>2026-07-05 08:46:10</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:22</t>
+          <t>2026-07-05 08:46:12</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:23</t>
+          <t>2026-07-05 08:46:14</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:25</t>
+          <t>2026-07-05 08:46:17</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:27</t>
+          <t>2026-07-05 08:46:19</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:28</t>
+          <t>2026-07-05 08:46:22</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:30</t>
+          <t>2026-07-05 08:46:24</t>
         </is>
       </c>
     </row>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:31</t>
+          <t>2026-07-05 08:46:26</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:33</t>
+          <t>2026-07-05 08:46:28</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:35</t>
+          <t>2026-07-05 08:46:31</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10386,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:36</t>
+          <t>2026-07-05 08:46:33</t>
         </is>
       </c>
     </row>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:37</t>
+          <t>2026-07-05 08:46:35</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:39</t>
+          <t>2026-07-05 08:46:37</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:41</t>
+          <t>2026-07-05 08:46:39</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:43</t>
+          <t>2026-07-05 08:46:41</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10696,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:45</t>
+          <t>2026-07-05 08:46:43</t>
         </is>
       </c>
     </row>
@@ -10758,7 +10758,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:47</t>
+          <t>2026-07-05 08:46:46</t>
         </is>
       </c>
     </row>
@@ -10820,7 +10820,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:48</t>
+          <t>2026-07-05 08:46:48</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:50</t>
+          <t>2026-07-05 08:46:50</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:52</t>
+          <t>2026-07-05 08:46:52</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:54</t>
+          <t>2026-07-05 08:46:54</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:55</t>
+          <t>2026-07-05 08:46:57</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:56</t>
+          <t>2026-07-05 08:46:58</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:58</t>
+          <t>2026-07-05 08:47:00</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:59</t>
+          <t>2026-07-05 08:47:02</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:00</t>
+          <t>2026-07-05 08:47:04</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:02</t>
+          <t>2026-07-05 08:47:06</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:04</t>
+          <t>2026-07-05 08:47:08</t>
         </is>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:06</t>
+          <t>2026-07-05 08:47:10</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:08</t>
+          <t>2026-07-05 08:47:13</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11626,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:09</t>
+          <t>2026-07-05 08:47:15</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:11</t>
+          <t>2026-07-05 08:47:17</t>
         </is>
       </c>
     </row>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:13</t>
+          <t>2026-07-05 08:47:19</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:15</t>
+          <t>2026-07-05 08:47:19</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:17</t>
+          <t>2026-07-05 08:47:21</t>
         </is>
       </c>
     </row>
@@ -11936,7 +11936,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:20</t>
+          <t>2026-07-05 08:47:23</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:22</t>
+          <t>2026-07-05 08:47:25</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:24</t>
+          <t>2026-07-05 08:47:27</t>
         </is>
       </c>
     </row>
@@ -12122,7 +12122,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:26</t>
+          <t>2026-07-05 08:47:29</t>
         </is>
       </c>
     </row>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:28</t>
+          <t>2026-07-05 08:47:31</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:30</t>
+          <t>2026-07-05 08:47:33</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:32</t>
+          <t>2026-07-05 08:47:34</t>
         </is>
       </c>
     </row>
@@ -12370,7 +12370,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:34</t>
+          <t>2026-07-05 08:47:37</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:36</t>
+          <t>2026-07-05 08:47:39</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:46:37</t>
+          <t>2026-07-05 08:47:41</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12556,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:48</t>
+          <t>2026-07-05 08:44:19</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12618,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:50</t>
+          <t>2026-07-05 08:44:21</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12680,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:51</t>
+          <t>2026-07-05 08:44:23</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12742,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:53</t>
+          <t>2026-07-05 08:44:25</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12804,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:54</t>
+          <t>2026-07-05 08:44:27</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:56</t>
+          <t>2026-07-05 08:44:29</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:57</t>
+          <t>2026-07-05 08:44:31</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12990,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:43:59</t>
+          <t>2026-07-05 08:44:33</t>
         </is>
       </c>
     </row>
@@ -13052,7 +13052,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:01</t>
+          <t>2026-07-05 08:44:35</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:02</t>
+          <t>2026-07-05 08:44:37</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:04</t>
+          <t>2026-07-05 08:44:40</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:06</t>
+          <t>2026-07-05 08:44:42</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:08</t>
+          <t>2026-07-05 08:44:44</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:09</t>
+          <t>2026-07-05 08:44:47</t>
         </is>
       </c>
     </row>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:11</t>
+          <t>2026-07-05 08:44:49</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:13</t>
+          <t>2026-07-05 08:44:52</t>
         </is>
       </c>
     </row>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:15</t>
+          <t>2026-07-05 08:44:54</t>
         </is>
       </c>
     </row>
@@ -13610,7 +13610,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:16</t>
+          <t>2026-07-05 08:44:56</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:18</t>
+          <t>2026-07-05 08:44:57</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13734,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:20</t>
+          <t>2026-07-05 08:44:58</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:21</t>
+          <t>2026-07-05 08:45:02</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:23</t>
+          <t>2026-07-05 08:45:03</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:24</t>
+          <t>2026-07-05 08:45:05</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:26</t>
+          <t>2026-07-05 08:45:08</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14044,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:27</t>
+          <t>2026-07-05 08:45:11</t>
         </is>
       </c>
     </row>
@@ -14106,7 +14106,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:29</t>
+          <t>2026-07-05 08:45:12</t>
         </is>
       </c>
     </row>
@@ -14168,7 +14168,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:31</t>
+          <t>2026-07-05 08:45:13</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:33</t>
+          <t>2026-07-05 08:45:16</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:34</t>
+          <t>2026-07-05 08:45:17</t>
         </is>
       </c>
     </row>
@@ -14354,7 +14354,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:36</t>
+          <t>2026-07-05 08:45:20</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:38</t>
+          <t>2026-07-05 08:45:21</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:40</t>
+          <t>2026-07-05 08:45:23</t>
         </is>
       </c>
     </row>
@@ -14540,7 +14540,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:41</t>
+          <t>2026-07-05 08:45:26</t>
         </is>
       </c>
     </row>
@@ -14602,7 +14602,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:43</t>
+          <t>2026-07-05 08:45:28</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:45</t>
+          <t>2026-07-05 08:45:28</t>
         </is>
       </c>
     </row>
@@ -14718,7 +14718,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:46</t>
+          <t>2026-07-05 08:45:31</t>
         </is>
       </c>
     </row>
@@ -14780,7 +14780,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:48</t>
+          <t>2026-07-05 08:45:32</t>
         </is>
       </c>
     </row>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:50</t>
+          <t>2026-07-05 08:45:35</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:52</t>
+          <t>2026-07-05 08:45:37</t>
         </is>
       </c>
     </row>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:53</t>
+          <t>2026-07-05 08:45:39</t>
         </is>
       </c>
     </row>
@@ -15028,7 +15028,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:55</t>
+          <t>2026-07-05 08:45:41</t>
         </is>
       </c>
     </row>
@@ -15090,7 +15090,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:56</t>
+          <t>2026-07-05 08:45:43</t>
         </is>
       </c>
     </row>
@@ -15152,7 +15152,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:58</t>
+          <t>2026-07-05 08:45:45</t>
         </is>
       </c>
     </row>
@@ -15214,7 +15214,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:44:59</t>
+          <t>2026-07-05 08:45:47</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:01</t>
+          <t>2026-07-05 08:45:49</t>
         </is>
       </c>
     </row>
@@ -15338,7 +15338,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:03</t>
+          <t>2026-07-05 08:45:51</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:05</t>
+          <t>2026-07-05 08:45:53</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:07</t>
+          <t>2026-07-05 08:45:55</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:08</t>
+          <t>2026-07-05 08:45:57</t>
         </is>
       </c>
     </row>
@@ -15586,7 +15586,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28 08:45:10</t>
+          <t>2026-07-05 08:45:59</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:17</t>
+          <t>2026-07-19 08:08:02</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:18</t>
+          <t>2026-07-19 08:08:04</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:20</t>
+          <t>2026-07-19 08:08:05</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:21</t>
+          <t>2026-07-19 08:08:07</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:23</t>
+          <t>2026-07-19 08:08:09</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:25</t>
+          <t>2026-07-19 08:08:10</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:27</t>
+          <t>2026-07-19 08:08:13</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:28</t>
+          <t>2026-07-19 08:08:14</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:29</t>
+          <t>2026-07-19 08:08:16</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:31</t>
+          <t>2026-07-19 08:08:18</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:32</t>
+          <t>2026-07-19 08:08:20</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:34</t>
+          <t>2026-07-19 08:08:22</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:36</t>
+          <t>2026-07-19 08:08:24</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:37</t>
+          <t>2026-07-19 08:08:26</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:39</t>
+          <t>2026-07-19 08:08:28</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:40</t>
+          <t>2026-07-19 08:08:30</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:42</t>
+          <t>2026-07-19 08:08:31</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:43</t>
+          <t>2026-07-19 08:08:33</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:44</t>
+          <t>2026-07-19 08:08:34</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:46</t>
+          <t>2026-07-19 08:08:36</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:48</t>
+          <t>2026-07-19 08:08:37</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:50</t>
+          <t>2026-07-19 08:08:39</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:51</t>
+          <t>2026-07-19 08:08:41</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:53</t>
+          <t>2026-07-19 08:08:43</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:55</t>
+          <t>2026-07-19 08:08:45</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:56</t>
+          <t>2026-07-19 08:08:47</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:58</t>
+          <t>2026-07-19 08:08:48</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:59</t>
+          <t>2026-07-19 08:08:50</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:00</t>
+          <t>2026-07-19 08:08:52</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:02</t>
+          <t>2026-07-19 08:08:53</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:04</t>
+          <t>2026-07-19 08:08:55</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:05</t>
+          <t>2026-07-19 08:08:57</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:06</t>
+          <t>2026-07-19 08:08:59</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:07</t>
+          <t>2026-07-19 08:09:00</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:09</t>
+          <t>2026-07-19 08:09:02</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:10</t>
+          <t>2026-07-19 08:09:04</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:12</t>
+          <t>2026-07-19 08:09:05</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:13</t>
+          <t>2026-07-19 08:09:07</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:14</t>
+          <t>2026-07-19 08:09:09</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:16</t>
+          <t>2026-07-19 08:09:10</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:18</t>
+          <t>2026-07-19 08:09:11</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:10:19</t>
+          <t>2026-07-19 08:09:13</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:57</t>
+          <t>2026-07-19 08:06:36</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:58</t>
+          <t>2026-07-19 08:06:38</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:00</t>
+          <t>2026-07-19 08:06:40</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:02</t>
+          <t>2026-07-19 08:06:42</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:04</t>
+          <t>2026-07-19 08:06:43</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:05</t>
+          <t>2026-07-19 08:06:45</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:07</t>
+          <t>2026-07-19 08:06:47</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:08</t>
+          <t>2026-07-19 08:06:48</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:10</t>
+          <t>2026-07-19 08:06:50</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:12</t>
+          <t>2026-07-19 08:06:51</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:14</t>
+          <t>2026-07-19 08:06:53</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:16</t>
+          <t>2026-07-19 08:06:55</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:17</t>
+          <t>2026-07-19 08:06:57</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:18</t>
+          <t>2026-07-19 08:06:58</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:19</t>
+          <t>2026-07-19 08:07:00</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:21</t>
+          <t>2026-07-19 08:07:02</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:22</t>
+          <t>2026-07-19 08:07:03</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:24</t>
+          <t>2026-07-19 08:07:05</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:26</t>
+          <t>2026-07-19 08:07:07</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:27</t>
+          <t>2026-07-19 08:07:09</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:29</t>
+          <t>2026-07-19 08:07:10</t>
         </is>
       </c>
     </row>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:31</t>
+          <t>2026-07-19 08:07:12</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:33</t>
+          <t>2026-07-19 08:07:14</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:35</t>
+          <t>2026-07-19 08:07:16</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:37</t>
+          <t>2026-07-19 08:07:18</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:39</t>
+          <t>2026-07-19 08:07:20</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:41</t>
+          <t>2026-07-19 08:07:21</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:42</t>
+          <t>2026-07-19 08:07:23</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:44</t>
+          <t>2026-07-19 08:07:25</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:46</t>
+          <t>2026-07-19 08:07:26</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:48</t>
+          <t>2026-07-19 08:07:28</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:49</t>
+          <t>2026-07-19 08:07:29</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:51</t>
+          <t>2026-07-19 08:07:30</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:52</t>
+          <t>2026-07-19 08:07:32</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:55</t>
+          <t>2026-07-19 08:07:36</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:56</t>
+          <t>2026-07-19 08:07:37</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:58</t>
+          <t>2026-07-19 08:07:39</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:59</t>
+          <t>2026-07-19 08:07:41</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:00</t>
+          <t>2026-07-19 08:07:43</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:02</t>
+          <t>2026-07-19 08:07:45</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:03</t>
+          <t>2026-07-19 08:07:47</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:04</t>
+          <t>2026-07-19 08:07:48</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:06</t>
+          <t>2026-07-19 08:07:50</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:07</t>
+          <t>2026-07-19 08:07:52</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:09</t>
+          <t>2026-07-19 08:07:53</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:11</t>
+          <t>2026-07-19 08:07:56</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:16</t>
+          <t>2026-07-19 08:08:00</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:08:53</t>
+          <t>2026-07-19 08:07:34</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:12</t>
+          <t>2026-07-19 08:07:57</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:09:14</t>
+          <t>2026-07-19 08:07:59</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:40</t>
+          <t>2026-07-19 08:05:18</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:41</t>
+          <t>2026-07-19 08:05:20</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:43</t>
+          <t>2026-07-19 08:05:22</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:44</t>
+          <t>2026-07-19 08:05:23</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:46</t>
+          <t>2026-07-19 08:05:25</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:48</t>
+          <t>2026-07-19 08:05:27</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:49</t>
+          <t>2026-07-19 08:05:28</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:50</t>
+          <t>2026-07-19 08:05:30</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:51</t>
+          <t>2026-07-19 08:05:31</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:53</t>
+          <t>2026-07-19 08:05:33</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:55</t>
+          <t>2026-07-19 08:05:34</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:56</t>
+          <t>2026-07-19 08:05:36</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:57</t>
+          <t>2026-07-19 08:05:37</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:59</t>
+          <t>2026-07-19 08:05:38</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:00</t>
+          <t>2026-07-19 08:05:40</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:02</t>
+          <t>2026-07-19 08:05:42</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:03</t>
+          <t>2026-07-19 08:05:43</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:05</t>
+          <t>2026-07-19 08:05:44</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:06</t>
+          <t>2026-07-19 08:05:46</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:08</t>
+          <t>2026-07-19 08:05:47</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:10</t>
+          <t>2026-07-19 08:05:49</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:11</t>
+          <t>2026-07-19 08:05:50</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:13</t>
+          <t>2026-07-19 08:05:51</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:14</t>
+          <t>2026-07-19 08:05:53</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:16</t>
+          <t>2026-07-19 08:05:54</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:18</t>
+          <t>2026-07-19 08:05:56</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:19</t>
+          <t>2026-07-19 08:05:57</t>
         </is>
       </c>
     </row>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:21</t>
+          <t>2026-07-19 08:05:58</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:22</t>
+          <t>2026-07-19 08:06:00</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:24</t>
+          <t>2026-07-19 08:06:01</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:25</t>
+          <t>2026-07-19 08:06:02</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:27</t>
+          <t>2026-07-19 08:06:03</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:28</t>
+          <t>2026-07-19 08:06:08</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:30</t>
+          <t>2026-07-19 08:06:10</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:31</t>
+          <t>2026-07-19 08:06:12</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:33</t>
+          <t>2026-07-19 08:06:13</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:35</t>
+          <t>2026-07-19 08:06:15</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:36</t>
+          <t>2026-07-19 08:06:17</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:38</t>
+          <t>2026-07-19 08:06:19</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:39</t>
+          <t>2026-07-19 08:06:20</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:41</t>
+          <t>2026-07-19 08:06:21</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:42</t>
+          <t>2026-07-19 08:06:22</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:44</t>
+          <t>2026-07-19 08:06:24</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:45</t>
+          <t>2026-07-19 08:06:26</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:47</t>
+          <t>2026-07-19 08:06:27</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:48</t>
+          <t>2026-07-19 08:06:28</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:50</t>
+          <t>2026-07-19 08:06:30</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:52</t>
+          <t>2026-07-19 08:06:31</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:54</t>
+          <t>2026-07-19 08:06:33</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:07:55</t>
+          <t>2026-07-19 08:06:35</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:06</t>
+          <t>2026-07-19 08:03:57</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:07</t>
+          <t>2026-07-19 08:03:58</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:09</t>
+          <t>2026-07-19 08:04:00</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:10</t>
+          <t>2026-07-19 08:04:02</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:12</t>
+          <t>2026-07-19 08:04:05</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:14</t>
+          <t>2026-07-19 08:04:06</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:16</t>
+          <t>2026-07-19 08:04:08</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:18</t>
+          <t>2026-07-19 08:04:10</t>
         </is>
       </c>
     </row>
@@ -9968,7 +9968,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:19</t>
+          <t>2026-07-19 08:04:11</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:21</t>
+          <t>2026-07-19 08:04:13</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:23</t>
+          <t>2026-07-19 08:04:15</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:24</t>
+          <t>2026-07-19 08:04:17</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:26</t>
+          <t>2026-07-19 08:04:20</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:28</t>
+          <t>2026-07-19 08:04:21</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:29</t>
+          <t>2026-07-19 08:04:24</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:31</t>
+          <t>2026-07-19 08:04:26</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:32</t>
+          <t>2026-07-19 08:04:27</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:34</t>
+          <t>2026-07-19 08:04:29</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:35</t>
+          <t>2026-07-19 08:04:31</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:37</t>
+          <t>2026-07-19 08:04:32</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:38</t>
+          <t>2026-07-19 08:04:34</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:40</t>
+          <t>2026-07-19 08:04:35</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:41</t>
+          <t>2026-07-19 08:04:37</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:43</t>
+          <t>2026-07-19 08:04:39</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:45</t>
+          <t>2026-07-19 08:04:40</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:46</t>
+          <t>2026-07-19 08:04:42</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:48</t>
+          <t>2026-07-19 08:04:43</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:50</t>
+          <t>2026-07-19 08:04:44</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:51</t>
+          <t>2026-07-19 08:04:46</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:53</t>
+          <t>2026-07-19 08:04:47</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:54</t>
+          <t>2026-07-19 08:04:48</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:55</t>
+          <t>2026-07-19 08:04:50</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:57</t>
+          <t>2026-07-19 08:04:51</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:58</t>
+          <t>2026-07-19 08:04:53</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:00</t>
+          <t>2026-07-19 08:04:54</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:01</t>
+          <t>2026-07-19 08:04:56</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:03</t>
+          <t>2026-07-19 08:04:57</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:17</t>
+          <t>2026-07-19 08:04:59</t>
         </is>
       </c>
     </row>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:19</t>
+          <t>2026-07-19 08:05:01</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:20</t>
+          <t>2026-07-19 08:05:02</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:22</t>
+          <t>2026-07-19 08:05:03</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:24</t>
+          <t>2026-07-19 08:05:05</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:26</t>
+          <t>2026-07-19 08:05:06</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:28</t>
+          <t>2026-07-19 08:05:08</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:30</t>
+          <t>2026-07-19 08:05:10</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:31</t>
+          <t>2026-07-19 08:05:11</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:33</t>
+          <t>2026-07-19 08:05:13</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:35</t>
+          <t>2026-07-19 08:05:15</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:36</t>
+          <t>2026-07-19 08:05:16</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:06:38</t>
+          <t>2026-07-19 08:05:17</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:49</t>
+          <t>2026-07-19 08:02:40</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:51</t>
+          <t>2026-07-19 08:02:41</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:52</t>
+          <t>2026-07-19 08:02:43</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:53</t>
+          <t>2026-07-19 08:02:44</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:54</t>
+          <t>2026-07-19 08:02:46</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:56</t>
+          <t>2026-07-19 08:02:48</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:57</t>
+          <t>2026-07-19 08:02:50</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:03:59</t>
+          <t>2026-07-19 08:02:51</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:01</t>
+          <t>2026-07-19 08:02:53</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:02</t>
+          <t>2026-07-19 08:02:55</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:03</t>
+          <t>2026-07-19 08:02:57</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:04</t>
+          <t>2026-07-19 08:02:58</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:06</t>
+          <t>2026-07-19 08:03:00</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:07</t>
+          <t>2026-07-19 08:03:01</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:09</t>
+          <t>2026-07-19 08:03:03</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:10</t>
+          <t>2026-07-19 08:03:04</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:12</t>
+          <t>2026-07-19 08:03:05</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:13</t>
+          <t>2026-07-19 08:03:07</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:14</t>
+          <t>2026-07-19 08:03:08</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:15</t>
+          <t>2026-07-19 08:03:09</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:17</t>
+          <t>2026-07-19 08:03:11</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:18</t>
+          <t>2026-07-19 08:03:12</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13928,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:19</t>
+          <t>2026-07-19 08:03:14</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:21</t>
+          <t>2026-07-19 08:03:15</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:22</t>
+          <t>2026-07-19 08:03:17</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:24</t>
+          <t>2026-07-19 08:03:18</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:25</t>
+          <t>2026-07-19 08:03:19</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:27</t>
+          <t>2026-07-19 08:03:21</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:29</t>
+          <t>2026-07-19 08:03:22</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:30</t>
+          <t>2026-07-19 08:03:23</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:32</t>
+          <t>2026-07-19 08:03:25</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:33</t>
+          <t>2026-07-19 08:03:27</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:35</t>
+          <t>2026-07-19 08:03:28</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:37</t>
+          <t>2026-07-19 08:03:29</t>
         </is>
       </c>
     </row>
@@ -14664,7 +14664,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:39</t>
+          <t>2026-07-19 08:03:31</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:41</t>
+          <t>2026-07-19 08:03:33</t>
         </is>
       </c>
     </row>
@@ -14788,7 +14788,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:43</t>
+          <t>2026-07-19 08:03:34</t>
         </is>
       </c>
     </row>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:45</t>
+          <t>2026-07-19 08:03:36</t>
         </is>
       </c>
     </row>
@@ -14912,7 +14912,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:46</t>
+          <t>2026-07-19 08:03:37</t>
         </is>
       </c>
     </row>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:48</t>
+          <t>2026-07-19 08:03:39</t>
         </is>
       </c>
     </row>
@@ -15036,7 +15036,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:49</t>
+          <t>2026-07-19 08:03:41</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:51</t>
+          <t>2026-07-19 08:03:42</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:52</t>
+          <t>2026-07-19 08:03:43</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:54</t>
+          <t>2026-07-19 08:03:45</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:56</t>
+          <t>2026-07-19 08:03:46</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:58</t>
+          <t>2026-07-19 08:03:48</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:04:59</t>
+          <t>2026-07-19 08:03:50</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:01</t>
+          <t>2026-07-19 08:03:52</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15532,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:03</t>
+          <t>2026-07-19 08:03:53</t>
         </is>
       </c>
     </row>
@@ -15594,7 +15594,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-07-12 08:05:04</t>
+          <t>2026-07-19 08:03:55</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:54</t>
+          <t>2026-08-02 08:15:09</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:56</t>
+          <t>2026-08-02 08:15:11</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:58</t>
+          <t>2026-08-02 08:15:13</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:59</t>
+          <t>2026-08-02 08:15:14</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:00</t>
+          <t>2026-08-02 08:15:16</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:02</t>
+          <t>2026-08-02 08:15:18</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:03</t>
+          <t>2026-08-02 08:15:19</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:06</t>
+          <t>2026-08-02 08:15:21</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:07</t>
+          <t>2026-08-02 08:15:22</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:09</t>
+          <t>2026-08-02 08:15:24</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:11</t>
+          <t>2026-08-02 08:15:26</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:13</t>
+          <t>2026-08-02 08:15:28</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:13</t>
+          <t>2026-08-02 08:15:30</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:15</t>
+          <t>2026-08-02 08:15:32</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:17</t>
+          <t>2026-08-02 08:15:33</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:19</t>
+          <t>2026-08-02 08:15:37</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:21</t>
+          <t>2026-08-02 08:15:38</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:22</t>
+          <t>2026-08-02 08:15:40</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:24</t>
+          <t>2026-08-02 08:15:41</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:26</t>
+          <t>2026-08-02 08:15:42</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:28</t>
+          <t>2026-08-02 08:15:44</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:29</t>
+          <t>2026-08-02 08:15:46</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:31</t>
+          <t>2026-08-02 08:15:47</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:32</t>
+          <t>2026-08-02 08:15:49</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:34</t>
+          <t>2026-08-02 08:15:51</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:35</t>
+          <t>2026-08-02 08:15:53</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:36</t>
+          <t>2026-08-02 08:15:54</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:37</t>
+          <t>2026-08-02 08:15:56</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:39</t>
+          <t>2026-08-02 08:15:58</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:41</t>
+          <t>2026-08-02 08:16:00</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:42</t>
+          <t>2026-08-02 08:16:01</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:43</t>
+          <t>2026-08-02 08:16:03</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:45</t>
+          <t>2026-08-02 08:16:04</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:47</t>
+          <t>2026-08-02 08:16:06</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:49</t>
+          <t>2026-08-02 08:16:08</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:51</t>
+          <t>2026-08-02 08:16:09</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:52</t>
+          <t>2026-08-02 08:16:11</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:54</t>
+          <t>2026-08-02 08:16:12</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:57</t>
+          <t>2026-08-02 08:16:14</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:18:58</t>
+          <t>2026-08-02 08:16:15</t>
         </is>
       </c>
     </row>
@@ -3164,39 +3164,39 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:19:00</t>
+          <t>2026-08-02 08:16:16</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTAIRE EnR à LYON (69004) | 32 rue Jacques-Louis Hénon</t>
+          <t>Office notarial SELARL SIMON &amp; CHAMBON-PERUS, NOTAIRES ASSOCIES à LYON (69002) | 6 rue Emile Zola</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>fanny.rebmann@notaires.fr</t>
+          <t>sevane.cazarian@notaires.fr</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>fanny.rebmann@notaires.fr</t>
+          <t>sevane.cazarian@notaires.fr</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0478389273</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0478389273</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 32 rue Jacques-Louis Hénon 69004 LYON France</t>
+          <t>Bureau principal 6 rue Emile Zola 69002 LYON France</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notaire-enr</t>
+          <t>https://www.notaires.fr/fr/office/selarl-simon-chambon-perus-notaires-associes</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -3226,39 +3226,39 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:52</t>
+          <t>2026-08-02 08:15:35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL CADRAN Notaires Conseils à TASSIN-LA-DEMI-LUNE (69160) | 3 avenue de Lauterbourg</t>
+          <t>Office notarial SARL CHAINE ET ASSOCIES NOTAIRES à LYON (69006) | 139 rue Vendôme</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>etude.chaine@notaires.fr</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>etude.chaine@notaires.fr</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>0478343602</t>
+          <t>0472757600</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>0478343602</t>
+          <t>0472757600</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 3 avenue de Lauterbourg 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 139 rue Vendôme 69006 LYON France</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils-0</t>
+          <t>https://www.notaires.fr/fr/office/sarl-chaine-et-associes-notaires</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
@@ -3288,39 +3288,39 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:25</t>
+          <t>2026-08-02 08:13:40</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL CHAINE ET ASSOCIES NOTAIRES à LYON (69006) | 139 rue Vendôme</t>
+          <t>Office notarial SARL GAMBIEZ - COTTE - Notaires Champagne au Mont d’Or à CHAMPAGNE-AU-MONT-D'OR (69410) | 33 avenue de Lanessan</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>etude.chaine@notaires.fr</t>
+          <t>gambiez.cotte@notaires.fr</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>etude.chaine@notaires.fr</t>
+          <t>gambiez.cotte@notaires.fr</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>0472757600</t>
+          <t>0472521717</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>0472757600</t>
+          <t>0472521717</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 139 rue Vendôme 69006 LYON France</t>
+          <t>Bureau principal 33 avenue de Lanessan 69410 CHAMPAGNE-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -3335,12 +3335,12 @@
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Champagne-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-chaine-et-associes-notaires</t>
+          <t>https://www.notaires.fr/fr/office/sarl-gambiez-cotte-notaires-champagne-au-mont-dor</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
@@ -3350,39 +3350,39 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:27</t>
+          <t>2026-08-02 08:13:41</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL GAMBIEZ - COTTE - Notaires Champagne au Mont d’Or à CHAMPAGNE-AU-MONT-D'OR (69410) | 33 avenue de Lanessan</t>
+          <t>Office notarial SARL HYVERNAT - CARNIEL - TAITHE - GAILLARD-DEBIESSE – NOTAIRES à VILLEFRANCHE-SUR-SAÔNE (69400) | 14 PLACE HUMBERT III</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>gambiez.cotte@notaires.fr</t>
+          <t>accueil.villefranche@enoas.notaires.fr</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>gambiez.cotte@notaires.fr</t>
+          <t>accueil.villefranche@enoas.notaires.fr</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>0472521717</t>
+          <t>0474653236</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>0472521717</t>
+          <t>0474653236</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 33 avenue de Lanessan 69410 CHAMPAGNE-AU-MONT-D'OR France</t>
+          <t>Bureau principal 14 PLACE HUMBERT III 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Champagne-Au-Mont-D'or</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-gambiez-cotte-notaires-champagne-au-mont-dor</t>
+          <t>https://www.notaires.fr/fr/office/sarl-hyvernat-carniel-taithe-gaillard-debiesse-notaires</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
@@ -3412,39 +3412,39 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:29</t>
+          <t>2026-08-02 08:13:43</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL HYVERNAT - CARNIEL - TAITHE - GAILLARD-DEBIESSE – NOTAIRES à VILLEFRANCHE-SUR-SAÔNE (69400) | 14 PLACE HUMBERT III</t>
+          <t>Office notarial SARL HYVERNAT - CARNIEL - TAITHE - GAILLARD-DEBIESSE – NOTAIRES à ANSE (69480) | RUE DE VERDUN</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>accueil.villefranche@enoas.notaires.fr</t>
+          <t>accueil.anse@enoas.notaires.fr</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>accueil.villefranche@enoas.notaires.fr</t>
+          <t>accueil.anse@enoas.notaires.fr</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>0474653236</t>
+          <t>0474672848</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>0474653236</t>
+          <t>0474672848</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 14 PLACE HUMBERT III 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal RUE DE VERDUN 69480 ANSE France</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -3459,12 +3459,12 @@
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Anse</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-hyvernat-carniel-taithe-gaillard-debiesse-notaires</t>
+          <t>https://www.notaires.fr/fr/office/sarl-hyvernat-carniel-taithe-gaillard-debiesse-notaires-0</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
@@ -3474,39 +3474,39 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:30</t>
+          <t>2026-08-02 08:13:45</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL HYVERNAT - CARNIEL - TAITHE - GAILLARD-DEBIESSE – NOTAIRES à ANSE (69480) | RUE DE VERDUN</t>
+          <t>Office notarial SARL LES AUTHENTIQUES et associés à CAILLOUX-SUR-FONTAINES (69270) | 350 route du Tilleul</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>accueil.anse@enoas.notaires.fr</t>
+          <t>laure.todeschini@notaires.fr</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>accueil.anse@enoas.notaires.fr</t>
+          <t>laure.todeschini@notaires.fr</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>0474672848</t>
+          <t>0487870535</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>0474672848</t>
+          <t>0487870535</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal RUE DE VERDUN 69480 ANSE France</t>
+          <t>Bureau principal 350 route du Tilleul 69270 CAILLOUX-SUR-FONTAINES France</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Anse</t>
+          <t>Cailloux-Sur-Fontaines</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-hyvernat-carniel-taithe-gaillard-debiesse-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/sarl-les-authentiques-et-associes</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
@@ -3536,39 +3536,39 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:32</t>
+          <t>2026-08-02 08:13:47</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL LES AUTHENTIQUES et associés à CAILLOUX-SUR-FONTAINES (69270) | 350 route du Tilleul</t>
+          <t>Office notarial SARL LOVY et associés à FONTAINES-SUR-SAÔNE (69270) | 37 B RUE PIERRE BOUVIER</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>laure.todeschini@notaires.fr</t>
+          <t>agoract@notaires.fr</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>laure.todeschini@notaires.fr</t>
+          <t>agoract@notaires.fr</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>0487870535</t>
+          <t>0478223425</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>0487870535</t>
+          <t>0478223425</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 350 route du Tilleul 69270 CAILLOUX-SUR-FONTAINES France</t>
+          <t>Bureau principal 37 B RUE PIERRE BOUVIER 69270 FONTAINES-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -3583,12 +3583,12 @@
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Cailloux-Sur-Fontaines</t>
+          <t>Fontaines-Sur-Saône</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-les-authentiques-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/sarl-lovy-et-associes</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
@@ -3598,39 +3598,39 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:33</t>
+          <t>2026-08-02 08:13:49</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL LOVY et associés à FONTAINES-SUR-SAÔNE (69270) | 37 B RUE PIERRE BOUVIER</t>
+          <t>Office notarial SARL NOTAIRE LYON BUGEAUD à LYON (69006) | 51 rue Bugeaud</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>agoract@notaires.fr</t>
+          <t>accueil@nlb.notaires.fr</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>agoract@notaires.fr</t>
+          <t>accueil@nlb.notaires.fr</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>0478223425</t>
+          <t>0426682000</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>0478223425</t>
+          <t>0426682000</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 37 B RUE PIERRE BOUVIER 69270 FONTAINES-SUR-SAÔNE France</t>
+          <t>Bureau principal 51 rue Bugeaud 69006 LYON France</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Fontaines-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-lovy-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/sarl-notaire-lyon-bugeaud</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
@@ -3660,39 +3660,39 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:35</t>
+          <t>2026-08-02 08:13:51</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL NOTAIRE LYON BUGEAUD à LYON (69006) | 51 rue Bugeaud</t>
+          <t>Office notarial SARL NOTAIRES FOCH à LYON (69006) | 5 cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>accueil@nlb.notaires.fr</t>
+          <t>accueil@69010.notaires.fr</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>accueil@nlb.notaires.fr</t>
+          <t>accueil@69010.notaires.fr</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>0426682000</t>
+          <t>0472699292</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>0426682000</t>
+          <t>0472699292</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 51 rue Bugeaud 69006 LYON France</t>
+          <t>Bureau principal 5 cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-notaire-lyon-bugeaud</t>
+          <t>https://www.notaires.fr/fr/office/sarl-notaires-foch</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
@@ -3722,39 +3722,39 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:38</t>
+          <t>2026-08-02 08:13:52</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL NOTAIRES FOCH à LYON (69006) | 5 cours Franklin Roosevelt</t>
+          <t>Office notarial SARL NOTAMIONS Valérie JACQUE et Associés à MIONS (69780) | 19 Rue du 8 Mai 1945</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>accueil@69010.notaires.fr</t>
+          <t>accueil@notamions.notaires.fr</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>accueil@69010.notaires.fr</t>
+          <t>accueil@notamions.notaires.fr</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>0472699292</t>
+          <t>0428290050</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>0472699292</t>
+          <t>0428290050</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 5 cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 19 Rue du 8 Mai 1945 69780 MIONS France</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Mions</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-notaires-foch</t>
+          <t>https://www.notaires.fr/fr/office/sarl-notamions-valerie-jacque-et-associes</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -3784,39 +3784,39 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:40</t>
+          <t>2026-08-02 08:13:54</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL NOTAMIONS Valérie JACQUE et Associés à MIONS (69780) | 19 Rue du 8 Mai 1945</t>
+          <t>Office notarial SARL O.M.L. - NOTAIRES à SAINT-MARTIN-EN-HAUT (69850) | 11 route de Lyon</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>accueil@notamions.notaires.fr</t>
+          <t>accueil@69064.notaires.fr</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>accueil@notamions.notaires.fr</t>
+          <t>accueil@69064.notaires.fr</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>0428290050</t>
+          <t>0478486043</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>0428290050</t>
+          <t>0478486043</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 19 Rue du 8 Mai 1945 69780 MIONS France</t>
+          <t>Bureau principal 11 route de Lyon 69850 SAINT-MARTIN-EN-HAUT France</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Mions</t>
+          <t>Saint-Martin-En-Haut</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-notamions-valerie-jacque-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/sarl-oml-notaires</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
@@ -3846,39 +3846,39 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:41</t>
+          <t>2026-08-02 08:13:56</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL O.M.L. - NOTAIRES à SAINT-MARTIN-EN-HAUT (69850) | 11 route de Lyon</t>
+          <t>Office notarial SARL PERROT &amp; associé à LYON (69002) | 1 rue Tupin</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>accueil@69064.notaires.fr</t>
+          <t>scpdoucetbonperrot@notaires.fr</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>accueil@69064.notaires.fr</t>
+          <t>scpdoucetbonperrot@notaires.fr</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>0478486043</t>
+          <t>0478421700</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>0478486043</t>
+          <t>0478421700</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 11 route de Lyon 69850 SAINT-MARTIN-EN-HAUT France</t>
+          <t>Bureau principal 1 rue Tupin 69002 LYON France</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Saint-Martin-En-Haut</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-oml-notaires</t>
+          <t>https://www.notaires.fr/fr/office/sarl-perrot-associe</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
@@ -3908,39 +3908,39 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:43</t>
+          <t>2026-08-02 08:13:57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL PERROT &amp; associé à LYON (69002) | 1 rue Tupin</t>
+          <t>Office notarial SARL THIVEL NOTAIRES à LYON (69002) | 27 rue Ferrandière</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>scpdoucetbonperrot@notaires.fr</t>
+          <t>thivel@notaires.fr</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>scpdoucetbonperrot@notaires.fr</t>
+          <t>thivel@notaires.fr</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>0478421700</t>
+          <t>0478280700</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>0478421700</t>
+          <t>0478280700</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Tupin 69002 LYON France</t>
+          <t>Bureau principal 27 rue Ferrandière 69002 LYON France</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-perrot-associe</t>
+          <t>https://www.notaires.fr/fr/office/sarl-thivel-notaires</t>
         </is>
       </c>
       <c r="K55" s="7" t="inlineStr">
@@ -3970,14 +3970,14 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:45</t>
+          <t>2026-08-02 08:13:59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL THIVEL NOTAIRES à LYON (69002) | 27 rue Ferrandière</t>
+          <t>Office notarial SARL THIVEL NOTAIRES à TARARE (69170) | 2 boulevard du Commandant Thivel</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
@@ -3992,17 +3992,17 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>0478280700</t>
+          <t>0474053190</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>0478280700</t>
+          <t>0474053190</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 27 rue Ferrandière 69002 LYON France</t>
+          <t>Bureau principal 2 boulevard du Commandant Thivel 69170 TARARE France</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Tarare</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-thivel-notaires</t>
+          <t>https://www.notaires.fr/fr/office/sarl-thivel-notaires-0</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
@@ -4032,39 +4032,39 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:46</t>
+          <t>2026-08-02 08:14:01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL THIVEL NOTAIRES à TARARE (69170) | 2 boulevard du Commandant Thivel</t>
+          <t>Office notarial SAS ADEVODENCE à FRANCHEVILLE (69340) | 8 route du Bruissin</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>thivel@notaires.fr</t>
+          <t>contact@adevodence.fr</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>thivel@notaires.fr</t>
+          <t>contact@adevodence.fr</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>0474053190</t>
+          <t>0437238191</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>0474053190</t>
+          <t>0437238191</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 boulevard du Commandant Thivel 69170 TARARE France</t>
+          <t>Bureau principal 8 route du Bruissin 69340 FRANCHEVILLE France</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>Tarare</t>
+          <t>Francheville</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-thivel-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/sas-adevodence</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -4094,39 +4094,39 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:48</t>
+          <t>2026-08-02 08:14:03</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS ADEVODENCE à FRANCHEVILLE (69340) | 8 route du Bruissin</t>
+          <t>Office notarial SAS BREMENS NOTAIRES à LYON (69006) | 45 quai Charles de Gaulle</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>contact@adevodence.fr</t>
+          <t>accueil@groupebremens.notaires.fr</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>contact@adevodence.fr</t>
+          <t>accueil@groupebremens.notaires.fr</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>0437238191</t>
+          <t>0472406900</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>0437238191</t>
+          <t>0472406900</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 8 route du Bruissin 69340 FRANCHEVILLE France</t>
+          <t>Bureau principal 45 quai Charles de Gaulle 69006 LYON France</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Francheville</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-adevodence</t>
+          <t>https://www.notaires.fr/fr/office/sas-bremens-notaires-0</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -4156,39 +4156,39 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:49</t>
+          <t>2026-08-02 08:14:05</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS BREMENS NOTAIRES à LYON (69006) | 45 quai Charles de Gaulle</t>
+          <t>Office notarial SAS a contrario à LYON (69002) | 21 rue Ferrandière</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>accueil@groupebremens.notaires.fr</t>
+          <t>lmancion@acontrario.notaires.fr</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>accueil@groupebremens.notaires.fr</t>
+          <t>lmancion@acontrario.notaires.fr</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>0472406900</t>
+          <t>0478626501</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>0472406900</t>
+          <t>0478626501</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 45 quai Charles de Gaulle 69006 LYON France</t>
+          <t>Bureau principal 21 rue Ferrandière 69002 LYON France</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-bremens-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/sas-contrario-0</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
@@ -4218,39 +4218,39 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:51</t>
+          <t>2026-08-02 08:14:07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS a contrario à LYON (69002) | 21 rue Ferrandière</t>
+          <t>Office notarial SAS des CEDRES à TASSIN-LA-DEMI-LUNE (69160) | 93 avenue du 11 Novembre 1918</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>lmancion@acontrario.notaires.fr</t>
+          <t>etude.69182@notaires.fr</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>lmancion@acontrario.notaires.fr</t>
+          <t>etude.69182@notaires.fr</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>0478626501</t>
+          <t>0437584277</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>0478626501</t>
+          <t>0437584277</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 21 rue Ferrandière 69002 LYON France</t>
+          <t>Bureau principal 93 avenue du 11 Novembre 1918 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-contrario-0</t>
+          <t>https://www.notaires.fr/fr/office/sas-des-cedres</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -4280,39 +4280,39 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:54</t>
+          <t>2026-08-02 08:14:09</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS des CEDRES à TASSIN-LA-DEMI-LUNE (69160) | 93 avenue du 11 Novembre 1918</t>
+          <t>Office notarial SAS EFFICIENCE LYON à LYON (69002) | 50 rue de la République</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>etude.69182@notaires.fr</t>
+          <t>jerome.roche@efficience.notaires.fr</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>etude.69182@notaires.fr</t>
+          <t>jerome.roche@efficience.notaires.fr</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>0437584277</t>
+          <t>0457584348</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>0437584277</t>
+          <t>0457584348</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 93 avenue du 11 Novembre 1918 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 50 rue de la République 69002 LYON France</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-des-cedres</t>
+          <t>https://www.notaires.fr/fr/office/sas-efficience-lyon</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
@@ -4342,39 +4342,31 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:56</t>
+          <t>2026-08-02 08:14:11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS EFFICIENCE LYON à LYON (69002) | 50 rue de la République</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>jerome.roche@efficience.notaires.fr</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>jerome.roche@efficience.notaires.fr</t>
-        </is>
-      </c>
+          <t>Office notarial SAS MOREL-VULLIEZ et associées à LYON (69006) | 13 bis place Jules Ferry</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr"/>
+      <c r="C62" s="5" t="inlineStr"/>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>0457584348</t>
+          <t>0481132999</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>0457584348</t>
+          <t>0481132999</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 50 rue de la République 69002 LYON France</t>
+          <t>Bureau principal 13 bis place Jules Ferry 69006 LYON France</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -4394,7 +4386,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-efficience-lyon</t>
+          <t>https://www.notaires.fr/fr/office/sas-morel-vulliez-et-associees</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -4404,31 +4396,39 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:57</t>
+          <t>2026-08-02 08:14:12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS MOREL-VULLIEZ et associées à LYON (69006) | 13 bis place Jules Ferry</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr"/>
-      <c r="C63" s="7" t="inlineStr"/>
+          <t>Office notarial SAS NOTAIRES DU VAL DU RHONE à VERNAISON (69390) | 1 Square Cardinal</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>office69041.vernaison@notaires.fr</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>office69041.vernaison@notaires.fr</t>
+        </is>
+      </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>0481132999</t>
+          <t>0478461033</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>0481132999</t>
+          <t>0478461033</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 13 bis place Jules Ferry 69006 LYON France</t>
+          <t>Bureau principal 1 Square Cardinal 69390 VERNAISON France</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Vernaison</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-morel-vulliez-et-associees</t>
+          <t>https://www.notaires.fr/fr/office/sas-notaires-du-val-du-rhone</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
@@ -4458,39 +4458,39 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:59</t>
+          <t>2026-08-02 08:14:14</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS NOTAIRES DU VAL DU RHONE à VERNAISON (69390) | 1 Square Cardinal</t>
+          <t>Office notarial SAS NOTLEX à LYON (69003) | 41 rue de Bonnel</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>office69041.vernaison@notaires.fr</t>
+          <t>hugo.rassion@notlex.notaires.fr</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>office69041.vernaison@notaires.fr</t>
+          <t>hugo.rassion@notlex.notaires.fr</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>0478461033</t>
+          <t>0481132385</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>0478461033</t>
+          <t>0481132385</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Square Cardinal 69390 VERNAISON France</t>
+          <t>Bureau principal 41 rue de Bonnel 69003 LYON France</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Vernaison</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-notaires-du-val-du-rhone</t>
+          <t>https://www.notaires.fr/fr/office/sas-notlex-1</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
@@ -4520,39 +4520,39 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:01</t>
+          <t>2026-08-02 08:14:16</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS NOTLEX à LYON (69003) | 41 rue de Bonnel</t>
+          <t>Office notarial SCHIBLER-JACQUET et associée à SAINT-PIERRE-DE-CHANDIEU (69780) | 23 place Charles de Gaulle</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>hugo.rassion@notlex.notaires.fr</t>
+          <t>etude.69112@notaires.fr</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>hugo.rassion@notlex.notaires.fr</t>
+          <t>etude.69112@notaires.fr</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>0481132385</t>
+          <t>0478403333</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>0481132385</t>
+          <t>0478403333</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 41 rue de Bonnel 69003 LYON France</t>
+          <t>Bureau principal 23 place Charles de Gaulle 69780 SAINT-PIERRE-DE-CHANDIEU France</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Pierre-De-Chandieu</t>
         </is>
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-notlex-1</t>
+          <t>https://www.notaires.fr/fr/office/schibler-jacquet-et-associee</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
@@ -4582,39 +4582,39 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:03</t>
+          <t>2026-08-02 08:14:18</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SCHIBLER-JACQUET et associée à SAINT-PIERRE-DE-CHANDIEU (69780) | 23 place Charles de Gaulle</t>
+          <t>Office notarial SCP Carole POULAIN-CHARPENTIER, Guillaume BONFILS, Romain THOLON et Caroline SALANSON-BOTTAZZI, notaires associés à LYON (69003) | 144 avenue Maréchal de Saxe</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>etude.69112@notaires.fr</t>
+          <t>notasaxe.69017@notaires.fr</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>etude.69112@notaires.fr</t>
+          <t>notasaxe.69017@notaires.fr</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>0478403333</t>
+          <t>0472847200</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>0478403333</t>
+          <t>0472847200</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 23 place Charles de Gaulle 69780 SAINT-PIERRE-DE-CHANDIEU France</t>
+          <t>Bureau principal 144 avenue Maréchal de Saxe 69003 LYON France</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Saint-Pierre-De-Chandieu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/schibler-jacquet-et-associee</t>
+          <t>https://www.notaires.fr/fr/office/scp-carole-poulain-charpentier-guillaume-bonfils-romain-tholon-et-caroline-salanson-bottazzi-notaires-associes</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -4644,39 +4644,39 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:05</t>
+          <t>2026-08-02 08:14:19</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SCP Carole POULAIN-CHARPENTIER, Guillaume BONFILS, Romain THOLON et Caroline SALANSON-BOTTAZZI, notaires associés à LYON (69003) | 144 avenue Maréchal de Saxe</t>
+          <t>Office notarial SCP Emmanuel de BAILLIENCOURT, Christophe RICHARD, Dimitri JANIN et Baptiste FRANCOIS Notaires, associés à LYON (69006) | 10 rue Boileau</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>notasaxe.69017@notaires.fr</t>
+          <t>notaires9republique@notaires.fr</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>notasaxe.69017@notaires.fr</t>
+          <t>notaires9republique@notaires.fr</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>0472847200</t>
+          <t>0478281577</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>0472847200</t>
+          <t>0478281577</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 144 avenue Maréchal de Saxe 69003 LYON France</t>
+          <t>Bureau principal 10 rue Boileau 69006 LYON France</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/scp-carole-poulain-charpentier-guillaume-bonfils-romain-tholon-et-caroline-salanson-bottazzi-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/scp-emmanuel-de-bailliencourt-christophe-richard-dimitri-janin-et-baptiste-francois-notaires-associes</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
@@ -4706,39 +4706,39 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:07</t>
+          <t>2026-08-02 08:14:21</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SCP Emmanuel de BAILLIENCOURT, Christophe RICHARD, Dimitri JANIN et Baptiste FRANCOIS Notaires, associés à LYON (69006) | 10 rue Boileau</t>
+          <t>Office notarial SCP Lionel ROBIN et Florence BOACHON, Notaires associés à CALUIRE-ET-CUIRE (69300) | 2 RUE DE MARGNOLLES</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>notaires9republique@notaires.fr</t>
+          <t>etude.robinetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>notaires9republique@notaires.fr</t>
+          <t>etude.robinetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>0478281577</t>
+          <t>0478294310</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>0478281577</t>
+          <t>0478294310</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 rue Boileau 69006 LYON France</t>
+          <t>Bureau principal 2 RUE DE MARGNOLLES 69300 CALUIRE-ET-CUIRE France</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Caluire-Et-Cuire</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/scp-emmanuel-de-bailliencourt-christophe-richard-dimitri-janin-et-baptiste-francois-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/scp-lionel-robin-et-florence-boachon-notaires-associes</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -4768,39 +4768,39 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:09</t>
+          <t>2026-08-02 08:14:23</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SCP Lionel ROBIN et Florence BOACHON, Notaires associés à CALUIRE-ET-CUIRE (69300) | 2 RUE DE MARGNOLLES</t>
+          <t>Office notarial SDV NOTAIRES, SELAS à LYON (69003) | 54 cours Lafayette</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>etude.robinetassocies@notaires.fr</t>
+          <t>s.selman@sdv.notaires.fr</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>etude.robinetassocies@notaires.fr</t>
+          <t>s.selman@sdv.notaires.fr</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>0478294310</t>
+          <t>0478793309</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>0478294310</t>
+          <t>0478793309</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 RUE DE MARGNOLLES 69300 CALUIRE-ET-CUIRE France</t>
+          <t>Bureau principal 54 cours Lafayette 69003 LYON France</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Caluire-Et-Cuire</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/scp-lionel-robin-et-florence-boachon-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/sdv-notaires-selas</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
@@ -4830,39 +4830,39 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:10</t>
+          <t>2026-08-02 08:14:25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SDV NOTAIRES, SELAS à LYON (69003) | 54 cours Lafayette</t>
+          <t>Office notarial SEL, NOTAIRES DE CHAPONNAY, SARL à CHAPONNAY (69970) | 22 rue de la Poste</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>s.selman@sdv.notaires.fr</t>
+          <t>notairesdechaponnay@notaires.fr</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>s.selman@sdv.notaires.fr</t>
+          <t>notairesdechaponnay@notaires.fr</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>0478793309</t>
+          <t>0478960403</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>0478793309</t>
+          <t>0478960403</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 54 cours Lafayette 69003 LYON France</t>
+          <t>Bureau principal 22 rue de la Poste 69970 CHAPONNAY France</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chaponnay</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sdv-notaires-selas</t>
+          <t>https://www.notaires.fr/fr/office/sel-notaires-de-chaponnay-sarl</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -4892,39 +4892,39 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:12</t>
+          <t>2026-08-02 08:14:26</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SEL, NOTAIRES DE CHAPONNAY, SARL à CHAPONNAY (69970) | 22 rue de la Poste</t>
+          <t>Office notarial SELARL 1629 NOTAIRES à LYON (69001) | 9 rue du Bât d'Argent</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>notairesdechaponnay@notaires.fr</t>
+          <t>accueil@1629.notaires.fr</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>notairesdechaponnay@notaires.fr</t>
+          <t>accueil@1629.notaires.fr</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>0478960403</t>
+          <t>0478270290</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>0478960403</t>
+          <t>0478270290</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 22 rue de la Poste 69970 CHAPONNAY France</t>
+          <t>Bureau principal 9 rue du Bât d'Argent 69001 LYON France</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>Chaponnay</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sel-notaires-de-chaponnay-sarl</t>
+          <t>https://www.notaires.fr/fr/office/selarl-1629-notaires</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
@@ -4954,39 +4954,39 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:14</t>
+          <t>2026-08-02 08:14:28</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL 1629 NOTAIRES à LYON (69001) | 9 rue du Bât d'Argent</t>
+          <t>Office notarial SELARL 1979 NOT’ACTES, Notaires à LA MULATIERE à LA MULATIÈRE (69350) | 2A CHEMIN DE LA BASTERO</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>accueil@1629.notaires.fr</t>
+          <t>etude69125.lamulatiere@notaires.fr</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>accueil@1629.notaires.fr</t>
+          <t>etude69125.lamulatiere@notaires.fr</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>0478270290</t>
+          <t>0478500794</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>0478270290</t>
+          <t>0478500794</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue du Bât d'Argent 69001 LYON France</t>
+          <t>Bureau principal 2A CHEMIN DE LA BASTERO 69350 LA MULATIÈRE France</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>La Mulatière</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-1629-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-1979-notactes-notaires-la-mulatiere</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -5016,39 +5016,39 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:14</t>
+          <t>2026-08-02 08:14:30</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL 1979 NOT’ACTES, Notaires à LA MULATIERE à LA MULATIÈRE (69350) | 2A CHEMIN DE LA BASTERO</t>
+          <t>Office notarial SELARL ACTALION Notaires à LYON (69003) | 1 rue Montébello</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>etude69125.lamulatiere@notaires.fr</t>
+          <t>actalion@notaires.fr</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>etude69125.lamulatiere@notaires.fr</t>
+          <t>actalion@notaires.fr</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>0478500794</t>
+          <t>0478606034</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>0478500794</t>
+          <t>0478606034</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2A CHEMIN DE LA BASTERO 69350 LA MULATIÈRE France</t>
+          <t>Bureau principal 1 rue Montébello 69003 LYON France</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>La Mulatière</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-1979-notactes-notaires-la-mulatiere</t>
+          <t>https://www.notaires.fr/fr/office/selarl-actalion-notaires-1</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
@@ -5078,39 +5078,39 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:16</t>
+          <t>2026-08-02 08:14:32</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ACTALION Notaires à LYON (69003) | 1 rue Montébello</t>
+          <t>Office notarial SELARL AJC NOTAIRES à CALUIRE-ET-CUIRE (69300) | 13 rue Jean Moulin</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>actalion@notaires.fr</t>
+          <t>alexia.juan@notaires.fr</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>actalion@notaires.fr</t>
+          <t>alexia.juan@notaires.fr</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>0478606034</t>
+          <t>0478088741</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>0478606034</t>
+          <t>0478088741</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Montébello 69003 LYON France</t>
+          <t>Bureau principal 13 rue Jean Moulin 69300 CALUIRE-ET-CUIRE France</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Caluire-Et-Cuire</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-actalion-notaires-1</t>
+          <t>https://www.notaires.fr/fr/office/selarl-ajc-notaires</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -5140,39 +5140,39 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:18</t>
+          <t>2026-08-02 08:14:35</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL AJC NOTAIRES à CALUIRE-ET-CUIRE (69300) | 13 rue Jean Moulin</t>
+          <t>Office notarial SELARL ALEXANDRE BRUYERE ET THOMAS BOURLIERE à LYON (69007) | 287 rue de Créqui</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>alexia.juan@notaires.fr</t>
+          <t>accueil.69006@notaires.fr</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>alexia.juan@notaires.fr</t>
+          <t>accueil.69006@notaires.fr</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>0478088741</t>
+          <t>0478422186</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>0478088741</t>
+          <t>0478422186</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 13 rue Jean Moulin 69300 CALUIRE-ET-CUIRE France</t>
+          <t>Bureau principal 287 rue de Créqui 69007 LYON France</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>Caluire-Et-Cuire</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-ajc-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-alexandre-bruyere-et-thomas-bourliere</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -5202,39 +5202,39 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:21</t>
+          <t>2026-08-02 08:14:37</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ALEXANDRE BRUYERE ET THOMAS BOURLIERE à LYON (69007) | 287 rue de Créqui</t>
+          <t>Office notarial SELARL BCA NOTAIRES à LYON (69002) | 5 place Bellecour</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>accueil.69006@notaires.fr</t>
+          <t>contact.69205@bca.notaires.fr</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>accueil.69006@notaires.fr</t>
+          <t>contact.69205@bca.notaires.fr</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>0478422186</t>
+          <t>0428382030</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>0478422186</t>
+          <t>0428382030</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 287 rue de Créqui 69007 LYON France</t>
+          <t>Bureau principal 5 place Bellecour 69002 LYON France</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-alexandre-bruyere-et-thomas-bourliere</t>
+          <t>https://www.notaires.fr/fr/office/selarl-bca-notaires</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -5264,39 +5264,39 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:22</t>
+          <t>2026-08-02 08:14:41</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL BCA NOTAIRES à LYON (69002) | 5 place Bellecour</t>
+          <t>Office notarial SELARL CARBONNEL &amp; FREMONT - Notaires à SAINTE-FOY-LÈS-LYON (69110) | 32 avenue Maréchal Foch</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>contact.69205@bca.notaires.fr</t>
+          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>contact.69205@bca.notaires.fr</t>
+          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>0428382030</t>
+          <t>0472413598</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>0428382030</t>
+          <t>0472413598</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 5 place Bellecour 69002 LYON France</t>
+          <t>Bureau principal 32 avenue Maréchal Foch 69110 SAINTE-FOY-LÈS-LYON France</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Sainte-Foy-Lès-Lyon</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-bca-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-carbonnel-fremont-notaires</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
@@ -5326,39 +5326,39 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:26</t>
+          <t>2026-08-02 08:14:43</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL CARBONNEL &amp; FREMONT - Notaires à SAINTE-FOY-LÈS-LYON (69110) | 32 avenue Maréchal Foch</t>
+          <t>Office notarial SELARL Caroline MARCHAIS-EPARVIER et Sylvain EPARVIER à TASSIN-LA-DEMI-LUNE (69160) | 169 Avenue Charles de Gaulle</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
+          <t>caroline.marchais-eparvier@notaires.fr</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
+          <t>caroline.marchais-eparvier@notaires.fr</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>0472413598</t>
+          <t>0437465199</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>0472413598</t>
+          <t>0437465199</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 32 avenue Maréchal Foch 69110 SAINTE-FOY-LÈS-LYON France</t>
+          <t>Bureau principal 169 Avenue Charles de Gaulle 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Sainte-Foy-Lès-Lyon</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-carbonnel-fremont-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-caroline-marchais-eparvier-et-sylvain-eparvier</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -5388,39 +5388,39 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:28</t>
+          <t>2026-08-02 08:14:44</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Caroline MARCHAIS-EPARVIER et Sylvain EPARVIER à TASSIN-LA-DEMI-LUNE (69160) | 169 Avenue Charles de Gaulle</t>
+          <t>Office notarial SELARL Des Paroles &amp; Des Actes à LYON (69006) | 111 rue Bugeaud</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>caroline.marchais-eparvier@notaires.fr</t>
+          <t>clement.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>caroline.marchais-eparvier@notaires.fr</t>
+          <t>clement.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>0437465199</t>
+          <t>0474531148</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>0437465199</t>
+          <t>0474531148</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 169 Avenue Charles de Gaulle 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 111 rue Bugeaud 69006 LYON France</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-caroline-marchais-eparvier-et-sylvain-eparvier</t>
+          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
@@ -5450,24 +5450,24 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:30</t>
+          <t>2026-08-02 08:14:46</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Des Paroles &amp; Des Actes à LYON (69006) | 111 rue Bugeaud</t>
+          <t>Office notarial SELARL Des Paroles &amp; Des Actes à SAINTE-COLOMBE (69560) | 49 rue Paul Doumer</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>clement.janey@rhonactes.notaires.fr</t>
+          <t>eric.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>clement.janey@rhonactes.notaires.fr</t>
+          <t>eric.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 111 rue Bugeaud 69006 LYON France</t>
+          <t>Bureau principal 49 rue Paul Doumer 69560 SAINTE-COLOMBE France</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Sainte-Colombe</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes</t>
+          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes-0</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -5512,39 +5512,39 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:32</t>
+          <t>2026-08-02 08:14:48</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Des Paroles &amp; Des Actes à SAINTE-COLOMBE (69560) | 49 rue Paul Doumer</t>
+          <t>Office notarial SELARL ENTANDEM NOTAIRES à SAINT-GERMAIN-AU-MONT-D'OR (69650) | 1 A Place de l'Esplanade</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>eric.janey@rhonactes.notaires.fr</t>
+          <t>s.vacher@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>eric.janey@rhonactes.notaires.fr</t>
+          <t>s.vacher@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>0474531148</t>
+          <t>0428380640</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>0474531148</t>
+          <t>0428380640</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 49 rue Paul Doumer 69560 SAINTE-COLOMBE France</t>
+          <t>Bureau principal 1 A Place de l'Esplanade 69650 SAINT-GERMAIN-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>Sainte-Colombe</t>
+          <t>Saint-Germain-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes-0</t>
+          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -5574,39 +5574,39 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:34</t>
+          <t>2026-08-02 08:14:50</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ENTANDEM NOTAIRES à SAINT-GERMAIN-AU-MONT-D'OR (69650) | 1 A Place de l'Esplanade</t>
+          <t>Office notarial SELARL ENTANDEM NOTAIRES à LYON (69006) | 50 cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>s.vacher@entandem.notaires.fr</t>
+          <t>office@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>s.vacher@entandem.notaires.fr</t>
+          <t>office@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>0428380640</t>
+          <t>0428382230</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>0428380640</t>
+          <t>0428382230</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 A Place de l'Esplanade 69650 SAINT-GERMAIN-AU-MONT-D'OR France</t>
+          <t>Bureau principal 50 cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Saint-Germain-Au-Mont-D'or</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires-0</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
@@ -5636,39 +5636,39 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:36</t>
+          <t>2026-08-02 08:14:51</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ENTANDEM NOTAIRES à LYON (69006) | 50 cours Franklin Roosevelt</t>
+          <t>Office notarial SELARL ETUDE BLANC à OULLINS-PIERRE-BÉNITE - OULLINS (69600) | 1 boulevard Emile Zola</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>office@entandem.notaires.fr</t>
+          <t>etude.blanc@notaires.fr</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>office@entandem.notaires.fr</t>
+          <t>etude.blanc@notaires.fr</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>0428382230</t>
+          <t>0478513155</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>0428382230</t>
+          <t>0478513155</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 50 cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 1 boulevard Emile Zola 69600 OULLINS-PIERRE-BÉNITE - OULLINS France</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Oullins-Pierre-Bénite - Oullins</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/selarl-etude-blanc</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:37</t>
+          <t>2026-08-02 08:14:53</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ETUDE BLANC à OULLINS-PIERRE-BÉNITE - OULLINS (69600) | 1 boulevard Emile Zola</t>
+          <t>Office notarial SELARL Fideis Notaires à SAINTE-FOY-LÈS-LYON (69110) | 18 Place Xavier Ricard</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>etude.blanc@notaires.fr</t>
+          <t>contact@fideis.notaires.fr</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>etude.blanc@notaires.fr</t>
+          <t>contact@fideis.notaires.fr</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>0478513155</t>
+          <t>0472329065</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>0478513155</t>
+          <t>0472329065</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 boulevard Emile Zola 69600 OULLINS-PIERRE-BÉNITE - OULLINS France</t>
+          <t>Bureau principal 18 Place Xavier Ricard 69110 SAINTE-FOY-LÈS-LYON France</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Oullins-Pierre-Bénite - Oullins</t>
+          <t>Sainte-Foy-Lès-Lyon</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-etude-blanc</t>
+          <t>https://www.notaires.fr/fr/office/selarl-fideis-notaires</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
@@ -5760,39 +5760,39 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:40</t>
+          <t>2026-08-02 08:14:55</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Fideis Notaires à SAINTE-FOY-LÈS-LYON (69110) | 18 Place Xavier Ricard</t>
+          <t>Office notarial SELARL GAUMIER NOTAIRES à LYON (69009) | 18 quai Jaÿr</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>contact@fideis.notaires.fr</t>
+          <t>matthieu.gaumier@notaires.fr</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>contact@fideis.notaires.fr</t>
+          <t>matthieu.gaumier@notaires.fr</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>0472329065</t>
+          <t>0472197508</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>0472329065</t>
+          <t>0472197508</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 18 Place Xavier Ricard 69110 SAINTE-FOY-LÈS-LYON France</t>
+          <t>Bureau principal 18 quai Jaÿr 69009 LYON France</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>Sainte-Foy-Lès-Lyon</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-fideis-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-gaumier-notaires</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
@@ -5822,39 +5822,39 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:41</t>
+          <t>2026-08-02 08:14:56</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL GAUMIER NOTAIRES à LYON (69009) | 18 quai Jaÿr</t>
+          <t>Office notarial SELARL Jean-Christophe HOCHE, Maxime CASTELLI et Denis MESTRALLET, Notaires des crus à VILLEFRANCHE-SUR-SAÔNE (69400) | 248 rue de la Paix</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>matthieu.gaumier@notaires.fr</t>
+          <t>notairesdescrus@ndc.notaires.fr</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>matthieu.gaumier@notaires.fr</t>
+          <t>notairesdescrus@ndc.notaires.fr</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>0472197508</t>
+          <t>0474042486</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>0472197508</t>
+          <t>0474042486</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 18 quai Jaÿr 69009 LYON France</t>
+          <t>Bureau principal 248 rue de la Paix 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-gaumier-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-jean-christophe-hoche-maxime-castelli-et-denis-mestrallet-notaires-des-crus</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -5884,39 +5884,39 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:43</t>
+          <t>2026-08-02 08:15:02</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Jean-Christophe HOCHE, Maxime CASTELLI et Denis MESTRALLET, Notaires des crus à VILLEFRANCHE-SUR-SAÔNE (69400) | 248 rue de la Paix</t>
+          <t>Office notarial SELARL LEMBREZ et Associés, Notaires à LYON (69004) | 5 rue Duviard</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>notairesdescrus@ndc.notaires.fr</t>
+          <t>simon.thiriat@lembrez.notaires.fr</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>notairesdescrus@ndc.notaires.fr</t>
+          <t>simon.thiriat@lembrez.notaires.fr</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>0474042486</t>
+          <t>0426316958</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>0474042486</t>
+          <t>0426316958</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 248 rue de la Paix 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 5 rue Duviard 69004 LYON France</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-jean-christophe-hoche-maxime-castelli-et-denis-mestrallet-notaires-des-crus</t>
+          <t>https://www.notaires.fr/fr/office/selarl-lembrez-et-associes-notaires</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
@@ -5946,39 +5946,39 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:47</t>
+          <t>2026-08-02 08:15:04</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL LEMBREZ et Associés, Notaires à LYON (69004) | 5 rue Duviard</t>
+          <t>Office notarial SELARL ACTES@VAULX à VAULX-EN-VELIN (69120) | 2 rue Lounès Matoub</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>simon.thiriat@lembrez.notaires.fr</t>
+          <t>actesavaulx@notaires.fr</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>simon.thiriat@lembrez.notaires.fr</t>
+          <t>actesavaulx@notaires.fr</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>0426316958</t>
+          <t>0478799224</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>0426316958</t>
+          <t>0478799224</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 5 rue Duviard 69004 LYON France</t>
+          <t>Bureau principal 2 rue Lounès Matoub 69120 VAULX-EN-VELIN France</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Vaulx-En-Velin</t>
         </is>
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-lembrez-et-associes-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-actesvaulx</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
@@ -6008,39 +6008,39 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:49</t>
+          <t>2026-08-02 08:14:34</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ACTES@VAULX à VAULX-EN-VELIN (69120) | 2 rue Lounès Matoub</t>
+          <t>Office notarial SELARL Grégoire ODIN, Édouard BLONDOT à LYON (69006) | 23 quai Général Sarrail</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>actesavaulx@notaires.fr</t>
+          <t>odin-blondot@69109.notaires.fr</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>actesavaulx@notaires.fr</t>
+          <t>odin-blondot@69109.notaires.fr</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>0478799224</t>
+          <t>0478521524</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>0478799224</t>
+          <t>0478521524</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 rue Lounès Matoub 69120 VAULX-EN-VELIN France</t>
+          <t>Bureau principal 23 quai Général Sarrail 69006 LYON France</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
-          <t>Vaulx-En-Velin</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-actesvaulx</t>
+          <t>https://www.notaires.fr/fr/office/selarl-gregoire-odin-edouard-blondot</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:19</t>
+          <t>2026-08-02 08:14:58</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Grégoire ODIN, Édouard BLONDOT à LYON (69006) | 23 quai Général Sarrail</t>
+          <t>Office notarial SELARL INGAB NOTAIRE à LYON (69003) | 95 rue Molière</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>odin-blondot@69109.notaires.fr</t>
+          <t>s.guilbert@notaires.fr</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>odin-blondot@69109.notaires.fr</t>
+          <t>s.guilbert@notaires.fr</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>0478521524</t>
+          <t>0428013998</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>0478521524</t>
+          <t>0428013998</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 23 quai Général Sarrail 69006 LYON France</t>
+          <t>Bureau principal 95 rue Molière 69003 LYON France</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-gregoire-odin-edouard-blondot</t>
+          <t>https://www.notaires.fr/fr/office/selarl-ingab-notaire</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
@@ -6132,39 +6132,39 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:44</t>
+          <t>2026-08-02 08:15:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL INGAB NOTAIRE à LYON (69003) | 95 rue Molière</t>
+          <t>Office notarial SELARL AUTHENTICA NOTAIRE à LYON (69003) | 228 rue de Vendôme</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>s.guilbert@notaires.fr</t>
+          <t>authentica@notaires.fr</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>s.guilbert@notaires.fr</t>
+          <t>authentica@notaires.fr</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>0428013998</t>
+          <t>04-28-29-28-10</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>0428013998</t>
+          <t>04-28-29-28-10</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 95 rue Molière 69003 LYON France</t>
+          <t>Bureau principal 228 rue de Vendôme 69003 LYON France</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-ingab-notaire</t>
+          <t>https://www.notaires.fr/fr/office/selarl-authentica-notaire</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
@@ -6194,39 +6194,39 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:46</t>
+          <t>2026-08-02 08:14:39</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL AUTHENTICA NOTAIRE à LYON (69003) | 228 rue de Vendôme</t>
+          <t>Office notarial SELARL Lucie BONNEFOY, Notaire à CALUIRE-ET-CUIRE (69300) | 71-73 rue Jean Moulin</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>authentica@notaires.fr</t>
+          <t>etudebonnefoy@bonnefoy.notaires.fr</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>authentica@notaires.fr</t>
+          <t>etudebonnefoy@bonnefoy.notaires.fr</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>04-28-29-28-10</t>
+          <t>0472055122</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>04-28-29-28-10</t>
+          <t>0472055122</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 228 rue de Vendôme 69003 LYON France</t>
+          <t>Bureau principal 71-73 rue Jean Moulin 69300 CALUIRE-ET-CUIRE France</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Caluire-Et-Cuire</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-authentica-notaire</t>
+          <t>https://www.notaires.fr/fr/office/selarl-lucie-bonnefoy-notaire</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
@@ -6256,39 +6256,39 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:25</t>
+          <t>2026-08-02 08:15:05</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Lucie BONNEFOY, Notaire à CALUIRE-ET-CUIRE (69300) | 71-73 rue Jean Moulin</t>
+          <t>Office notarial SELARL NOTAIRE EnR à LYON (69004) | 32 rue Jacques-Louis Hénon</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>etudebonnefoy@bonnefoy.notaires.fr</t>
+          <t>fanny.rebmann@notaires.fr</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>etudebonnefoy@bonnefoy.notaires.fr</t>
+          <t>fanny.rebmann@notaires.fr</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>0472055122</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>0472055122</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 71-73 rue Jean Moulin 69300 CALUIRE-ET-CUIRE France</t>
+          <t>Bureau principal 32 rue Jacques-Louis Hénon 69004 LYON France</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
-          <t>Caluire-Et-Cuire</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-lucie-bonnefoy-notaire</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notaire-enr</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
@@ -6318,39 +6318,39 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:17:51</t>
+          <t>2026-08-02 08:15:07</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Office notarial Maître MILESI Notaire, SARL à SATHONAY-CAMP (69580) | 9 Avenue Félix Faure</t>
+          <t>Office notarial MARECHAL Thibault à LYON (69002) | 56 Cours Charlemagne</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>officenotarial@69214.notaires.fr</t>
+          <t>thibault.marechal@69178.notaires.fr</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>officenotarial@69214.notaires.fr</t>
+          <t>thibault.marechal@69178.notaires.fr</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0472134695</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0472134695</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 9 Avenue Félix Faure 69580 SATHONAY-CAMP France</t>
+          <t>Bureau principal 56 Cours Charlemagne 69002 LYON France</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Sathonay-Camp</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/maitre-milesi-notaire-sarl</t>
+          <t>https://www.notaires.fr/fr/office/marechal-thibault</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
@@ -6380,39 +6380,39 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:01</t>
+          <t>2026-08-02 08:12:17</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MARECHAL Thibault à LYON (69002) | 56 Cours Charlemagne</t>
+          <t>Office notarial MARIOTTE Stéphanie à LYON (69006) | 10 Boulevard Jules Favre</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>thibault.marechal@69178.notaires.fr</t>
+          <t>stephanie.mariotte@notaires.fr</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>thibault.marechal@69178.notaires.fr</t>
+          <t>stephanie.mariotte@notaires.fr</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>0472134695</t>
+          <t>0481060795</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>0472134695</t>
+          <t>0481060795</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 56 Cours Charlemagne 69002 LYON France</t>
+          <t>Bureau principal 10 Boulevard Jules Favre 69006 LYON France</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/marechal-thibault</t>
+          <t>https://www.notaires.fr/fr/office/mariotte-stephanie</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -6442,39 +6442,39 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:03</t>
+          <t>2026-08-02 08:12:19</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MARIOTTE Stéphanie à LYON (69006) | 10 Boulevard Jules Favre</t>
+          <t>Office notarial MATA Victoria à LYON (69008) | 310 Avenue Berthelot</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>stephanie.mariotte@notaires.fr</t>
+          <t>victoria.mata@notaires.fr</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>stephanie.mariotte@notaires.fr</t>
+          <t>victoria.mata@notaires.fr</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>0481060795</t>
+          <t>0472780290</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>0481060795</t>
+          <t>0472780290</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 Boulevard Jules Favre 69006 LYON France</t>
+          <t>Bureau principal 310 Avenue Berthelot 69008 LYON France</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mariotte-stephanie</t>
+          <t>https://www.notaires.fr/fr/office/mata-victoria</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -6504,39 +6504,39 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:04</t>
+          <t>2026-08-02 08:12:20</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MATA Victoria à LYON (69008) | 310 Avenue Berthelot</t>
+          <t>Office notarial MAUGAIN NOTAIRES, SELARL à LYON (69003) | 34 cours Lafayette</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>victoria.mata@notaires.fr</t>
+          <t>bertram.julienne@notaires.fr</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>victoria.mata@notaires.fr</t>
+          <t>bertram.julienne@notaires.fr</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>0472780290</t>
+          <t>0472130397</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>0472780290</t>
+          <t>0472130397</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 310 Avenue Berthelot 69008 LYON France</t>
+          <t>Bureau principal 34 cours Lafayette 69003 LYON France</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mata-victoria</t>
+          <t>https://www.notaires.fr/fr/office/maugain-notaires-selarl</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -6566,39 +6566,39 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:06</t>
+          <t>2026-08-02 08:12:22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MAUGAIN NOTAIRES, SELARL à LYON (69003) | 34 cours Lafayette</t>
+          <t>Office notarial MERMET Pierre à LIMAS (69400) | 84 rue Henri Dépagneux</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>bertram.julienne@notaires.fr</t>
+          <t>pierre.mermet@notaires.fr</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>bertram.julienne@notaires.fr</t>
+          <t>pierre.mermet@notaires.fr</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>0472130397</t>
+          <t>0474045153</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>0472130397</t>
+          <t>0474045153</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 34 cours Lafayette 69003 LYON France</t>
+          <t>Bureau principal 84 rue Henri Dépagneux 69400 LIMAS France</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -6613,12 +6613,12 @@
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Limas</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/maugain-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/mermet-pierre</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -6628,39 +6628,39 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:08</t>
+          <t>2026-08-02 08:12:24</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MERMET Pierre à LIMAS (69400) | 84 rue Henri Dépagneux</t>
+          <t>Office notarial MESSERI Aurore à LYON (69003) | 6 cours de la Liberté</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>pierre.mermet@notaires.fr</t>
+          <t>aurore.messeri@notaires.fr</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>pierre.mermet@notaires.fr</t>
+          <t>aurore.messeri@notaires.fr</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>0474045153</t>
+          <t>0481061360</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>0474045153</t>
+          <t>0481061360</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 84 rue Henri Dépagneux 69400 LIMAS France</t>
+          <t>Bureau principal 6 cours de la Liberté 69003 LYON France</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Limas</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mermet-pierre</t>
+          <t>https://www.notaires.fr/fr/office/messeri-aurore</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
@@ -6690,39 +6690,39 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:09</t>
+          <t>2026-08-02 08:12:25</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MESSERI Aurore à LYON (69003) | 6 cours de la Liberté</t>
+          <t>Office notarial MONTEL Hélène à VERNAISON (69390) | 336 rue de la Fée des Eaux</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>aurore.messeri@notaires.fr</t>
+          <t>h.montel@notaires.fr</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>aurore.messeri@notaires.fr</t>
+          <t>h.montel@notaires.fr</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>0481061360</t>
+          <t>0482531832</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>0481061360</t>
+          <t>0482531832</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 6 cours de la Liberté 69003 LYON France</t>
+          <t>Bureau principal 336 rue de la Fée des Eaux 69390 VERNAISON France</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="I100" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Vernaison</t>
         </is>
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/messeri-aurore</t>
+          <t>https://www.notaires.fr/fr/office/montel-helene</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -6752,39 +6752,39 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:10</t>
+          <t>2026-08-02 08:12:27</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MONTEL Hélène à VERNAISON (69390) | 336 rue de la Fée des Eaux</t>
+          <t>Office notarial MOREL Laetitia à LYON (69003) | 127 cours du Docteur Long</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>h.montel@notaires.fr</t>
+          <t>morel.laetitia@notaires.fr</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>h.montel@notaires.fr</t>
+          <t>morel.laetitia@notaires.fr</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>0482531832</t>
+          <t>0481061095</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>0482531832</t>
+          <t>0481061095</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 336 rue de la Fée des Eaux 69390 VERNAISON France</t>
+          <t>Bureau principal 127 cours du Docteur Long 69003 LYON France</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Vernaison</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/montel-helene</t>
+          <t>https://www.notaires.fr/fr/office/morel-laetitia</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
@@ -6814,39 +6814,39 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:12</t>
+          <t>2026-08-02 08:12:29</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MOREL Laetitia à LYON (69003) | 127 cours du Docteur Long</t>
+          <t>Office notarial MURANA-CHARLUET Raphaëlle à SAINT-DIDIER-AU-MONT-D'OR (69370) | 11 rue Voie Lactée</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>morel.laetitia@notaires.fr</t>
+          <t>r.murana@notaires.fr</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>morel.laetitia@notaires.fr</t>
+          <t>r.murana@notaires.fr</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>0481061095</t>
+          <t>0485680145</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>0481061095</t>
+          <t>0485680145</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 127 cours du Docteur Long 69003 LYON France</t>
+          <t>Bureau principal 11 rue Voie Lactée 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Didier-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/morel-laetitia</t>
+          <t>https://www.notaires.fr/fr/office/murana-charluet-raphaelle</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -6876,39 +6876,39 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:13</t>
+          <t>2026-08-02 08:12:31</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MURANA-CHARLUET Raphaëlle à SAINT-DIDIER-AU-MONT-D'OR (69370) | 11 rue Voie Lactée</t>
+          <t>Office notarial MURAT Marie-Pierre à VILLEURBANNE (69100) | 109 Cours Emile Zola</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>r.murana@notaires.fr</t>
+          <t>office.murat@notaires.fr</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>r.murana@notaires.fr</t>
+          <t>office.murat@notaires.fr</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>0485680145</t>
+          <t>0437431922</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>0485680145</t>
+          <t>0437431922</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 11 rue Voie Lactée 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
+          <t>Bureau principal 109 Cours Emile Zola 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Saint-Didier-Au-Mont-D'or</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/murana-charluet-raphaelle</t>
+          <t>https://www.notaires.fr/fr/office/murat-marie-pierre</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr">
@@ -6938,39 +6938,39 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:14</t>
+          <t>2026-08-02 08:12:32</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MURAT Marie-Pierre à VILLEURBANNE (69100) | 109 Cours Emile Zola</t>
+          <t>Office notarial NARDINI Magali à CHAZAY-D'AZERGUES (69380) | 9 rue Marius Berliet</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>office.murat@notaires.fr</t>
+          <t>office.nardini@notaires.fr</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>office.murat@notaires.fr</t>
+          <t>office.nardini@notaires.fr</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>0437431922</t>
+          <t>04.86.11.05.15</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>0437431922</t>
+          <t>04.86.11.05.15</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 109 Cours Emile Zola 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 9 rue Marius Berliet 69380 CHAZAY-D'AZERGUES France</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6985,12 +6985,12 @@
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Chazay-D'azergues</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/murat-marie-pierre</t>
+          <t>https://www.notaires.fr/fr/office/nardini-magali</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -7000,39 +7000,39 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:16</t>
+          <t>2026-08-02 08:12:34</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NARDINI Magali à CHAZAY-D'AZERGUES (69380) | 9 rue Marius Berliet</t>
+          <t>Office notarial NICOLLE et associés à LYON (69003) | 90 rue Paul Bert</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>office.nardini@notaires.fr</t>
+          <t>christian.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>office.nardini@notaires.fr</t>
+          <t>christian.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>04.86.11.05.15</t>
+          <t>0492309230</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>04.86.11.05.15</t>
+          <t>0492309230</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue Marius Berliet 69380 CHAZAY-D'AZERGUES France</t>
+          <t>Bureau principal 90 rue Paul Bert 69003 LYON France</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Chazay-D'azergues</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/nardini-magali</t>
+          <t>https://www.notaires.fr/fr/office/nicolle-et-associes-0</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
@@ -7062,39 +7062,39 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:18</t>
+          <t>2026-08-02 08:12:37</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NICOLLE et associés à LYON (69003) | 90 rue Paul Bert</t>
+          <t>Office notarial NOHARET Françoise à LYON (69007) | 200 AVENUE JEAN JAURES</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>christian.nicolle@notaires.fr</t>
+          <t>office.noharet@notaires.fr</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>christian.nicolle@notaires.fr</t>
+          <t>office.noharet@notaires.fr</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>0492309230</t>
+          <t>0437376850</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>0492309230</t>
+          <t>0437376850</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 90 rue Paul Bert 69003 LYON France</t>
+          <t>Bureau principal 200 AVENUE JEAN JAURES 69007 LYON France</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/nicolle-et-associes-0</t>
+          <t>https://www.notaires.fr/fr/office/noharet-francoise</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr">
@@ -7124,39 +7124,39 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:20</t>
+          <t>2026-08-02 08:12:38</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOHARET Françoise à LYON (69007) | 200 AVENUE JEAN JAURES</t>
+          <t>Office notarial NOT’ACTES MARCY à MARCY (69480) | 20, Rue de la Tour</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>office.noharet@notaires.fr</t>
+          <t>renaud.fontaine@69169.notaires.fr</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>office.noharet@notaires.fr</t>
+          <t>renaud.fontaine@69169.notaires.fr</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>0437376850</t>
+          <t>0437552285</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>0437376850</t>
+          <t>0437552285</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 200 AVENUE JEAN JAURES 69007 LYON France</t>
+          <t>Bureau principal 20, Rue de la Tour 69480 MARCY France</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Marcy</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/noharet-francoise</t>
+          <t>https://www.notaires.fr/fr/office/notactes-marcy</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
@@ -7186,39 +7186,39 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:21</t>
+          <t>2026-08-02 08:12:40</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOT’ACTES MARCY à MARCY (69480) | 20, Rue de la Tour</t>
+          <t>Office notarial NOTAEM et associés à SAINT-CYR-AU-MONT-D'OR (69450) | 1 rue Reynier</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>renaud.fontaine@69169.notaires.fr</t>
+          <t>notaem@notaem.notaires.fr</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>renaud.fontaine@69169.notaires.fr</t>
+          <t>notaem@notaem.notaires.fr</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>0437552285</t>
+          <t>0478472483</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>0437552285</t>
+          <t>0478472483</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 20, Rue de la Tour 69480 MARCY France</t>
+          <t>Bureau principal 1 rue Reynier 69450 SAINT-CYR-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Marcy</t>
+          <t>Saint-Cyr-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notactes-marcy</t>
+          <t>https://www.notaires.fr/fr/office/notaem-et-associes</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -7248,39 +7248,39 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:23</t>
+          <t>2026-08-02 08:12:41</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOTAEM et associés à SAINT-CYR-AU-MONT-D'OR (69450) | 1 rue Reynier</t>
+          <t>Office notarial NOTAIRES GAMBETTA à VILLEFRANCHE-SUR-SAÔNE (69400) | 257 rue Boiron</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>notaem@notaem.notaires.fr</t>
+          <t>secretariat@etudegambetta.notaires.fr</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>notaem@notaem.notaires.fr</t>
+          <t>secretariat@etudegambetta.notaires.fr</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>0478472483</t>
+          <t>0474029910</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>0478472483</t>
+          <t>0474029910</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Reynier 69450 SAINT-CYR-AU-MONT-D'OR France</t>
+          <t>Bureau principal 257 rue Boiron 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>Saint-Cyr-Au-Mont-D'or</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notaem-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/notaires-gambetta</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -7310,39 +7310,39 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:24</t>
+          <t>2026-08-02 08:12:42</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOTAIRES GAMBETTA à VILLEFRANCHE-SUR-SAÔNE (69400) | 257 rue Boiron</t>
+          <t>Office notarial NOTARA à LYON (69007) | 152 Grande Rue de la Guillotière</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>secretariat@etudegambetta.notaires.fr</t>
+          <t>notara.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>secretariat@etudegambetta.notaires.fr</t>
+          <t>notara.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>0474029910</t>
+          <t>0983211434</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>0474029910</t>
+          <t>0983211434</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 257 rue Boiron 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 152 Grande Rue de la Guillotière 69007 LYON France</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notaires-gambetta</t>
+          <t>https://www.notaires.fr/fr/office/notara</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -7372,39 +7372,39 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:26</t>
+          <t>2026-08-02 08:12:44</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOTARA à LYON (69007) | 152 Grande Rue de la Guillotière</t>
+          <t>Office notarial ODO, notaire à THIZY-LES-BOURGS (69240) | 47 RUE JEAN JAURES</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>notara.lyon@notaires.fr</t>
+          <t>notaires.thizy@notaires.fr</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>notara.lyon@notaires.fr</t>
+          <t>notaires.thizy@notaires.fr</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>0983211434</t>
+          <t>0474640048</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>0983211434</t>
+          <t>0474640048</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 152 Grande Rue de la Guillotière 69007 LYON France</t>
+          <t>Bureau principal 47 RUE JEAN JAURES 69240 THIZY-LES-BOURGS France</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -7419,12 +7419,12 @@
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Thizy-Les-Bourgs</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notara</t>
+          <t>https://www.notaires.fr/fr/office/odo-notaire</t>
         </is>
       </c>
       <c r="K111" s="7" t="inlineStr">
@@ -7434,39 +7434,39 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:27</t>
+          <t>2026-08-02 08:12:45</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ODO, notaire à THIZY-LES-BOURGS (69240) | 47 RUE JEAN JAURES</t>
+          <t>Office notarial OFFICE NOTARIAL DE PRESSENSE, SELARL à VILLEURBANNE (69100) | 46 rue Francis de Pressensé</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>notaires.thizy@notaires.fr</t>
+          <t>helene.geraud@notaires.fr</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>notaires.thizy@notaires.fr</t>
+          <t>helene.geraud@notaires.fr</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>0474640048</t>
+          <t>0437482561</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>0474640048</t>
+          <t>0437482561</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 47 RUE JEAN JAURES 69240 THIZY-LES-BOURGS France</t>
+          <t>Bureau principal 46 rue Francis de Pressensé 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Thizy-Les-Bourgs</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/odo-notaire</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-de-pressense-selarl</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -7496,39 +7496,39 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:28</t>
+          <t>2026-08-02 08:12:47</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DE PRESSENSE, SELARL à VILLEURBANNE (69100) | 46 rue Francis de Pressensé</t>
+          <t>Office notarial OFFICE NOTARIAL DES CHARPENNES-VILLEURBANNE, SELARL à VILLEURBANNE (69100) | 50 A Cours Emile Zola</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>helene.geraud@notaires.fr</t>
+          <t>oncv@69136.notaires.fr</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>helene.geraud@notaires.fr</t>
+          <t>oncv@69136.notaires.fr</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>0437482561</t>
+          <t>0472759396</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>0437482561</t>
+          <t>0472759396</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 46 rue Francis de Pressensé 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 50 A Cours Emile Zola 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-de-pressense-selarl</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-des-charpennes-villeurbanne-selarl</t>
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr">
@@ -7558,39 +7558,39 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:30</t>
+          <t>2026-08-02 08:12:48</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DES CHARPENNES-VILLEURBANNE, SELARL à VILLEURBANNE (69100) | 50 A Cours Emile Zola</t>
+          <t>Office notarial Office Notarial des Jacobins, SAS à LYON (69002) | 8 place des Jacobins</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>oncv@69136.notaires.fr</t>
+          <t>office.jacobins.lyon@69004.notaires.fr</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>oncv@69136.notaires.fr</t>
+          <t>office.jacobins.lyon@69004.notaires.fr</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>0472759396</t>
+          <t>0478371744</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>0472759396</t>
+          <t>0478371744</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 50 A Cours Emile Zola 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 8 place des Jacobins 69002 LYON France</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-des-charpennes-villeurbanne-selarl</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-des-jacobins-sas</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -7620,39 +7620,39 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:32</t>
+          <t>2026-08-02 08:12:50</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Office notarial Office Notarial des Jacobins, SAS à LYON (69002) | 8 place des Jacobins</t>
+          <t>Office notarial OFFICE NOTARIAL DU PAYS ARBRESLOIS, SELARL à L'ARBRESLE (69210) | 54, rue Claude Terrasse</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>office.jacobins.lyon@69004.notaires.fr</t>
+          <t>office.larbresle@onpa.notaires.fr</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>office.jacobins.lyon@69004.notaires.fr</t>
+          <t>office.larbresle@onpa.notaires.fr</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>0478371744</t>
+          <t>0474010014</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>0478371744</t>
+          <t>0474010014</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 8 place des Jacobins 69002 LYON France</t>
+          <t>Bureau principal 54, rue Claude Terrasse 69210 L'ARBRESLE France</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
@@ -7667,12 +7667,12 @@
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>L'arbresle</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-des-jacobins-sas</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-du-pays-arbreslois-selarl</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr">
@@ -7682,39 +7682,39 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:33</t>
+          <t>2026-08-02 08:12:51</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DU PAYS ARBRESLOIS, SELARL à L'ARBRESLE (69210) | 54, rue Claude Terrasse</t>
+          <t>Office notarial OFFICE ROOSEVELT et associés, SELARL à LYON (69006) | 24 Cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>office.larbresle@onpa.notaires.fr</t>
+          <t>scp.bronnert@notaires.fr</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>office.larbresle@onpa.notaires.fr</t>
+          <t>scp.bronnert@notaires.fr</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>0474010014</t>
+          <t>0472838080</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>0474010014</t>
+          <t>0472838080</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 54, rue Claude Terrasse 69210 L'ARBRESLE France</t>
+          <t>Bureau principal 24 Cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>L'arbresle</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-du-pays-arbreslois-selarl</t>
+          <t>https://www.notaires.fr/fr/office/office-roosevelt-et-associes-selarl</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -7744,39 +7744,39 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:35</t>
+          <t>2026-08-02 08:12:53</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE ROOSEVELT et associés, SELARL à LYON (69006) | 24 Cours Franklin Roosevelt</t>
+          <t>Office notarial ONPC NOTAIRES, SELARL à LYON (69006) | 58 rue Tête d'Or</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>scp.bronnert@notaires.fr</t>
+          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>scp.bronnert@notaires.fr</t>
+          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>0472838080</t>
+          <t>0481098330</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>0472838080</t>
+          <t>0481098330</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 24 Cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 58 rue Tête d'Or 69006 LYON France</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-roosevelt-et-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/onpc-notaires-selarl</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
@@ -7806,39 +7806,39 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:37</t>
+          <t>2026-08-02 08:12:55</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ONPC NOTAIRES, SELARL à LYON (69006) | 58 rue Tête d'Or</t>
+          <t>Office notarial PARISET, Notaire, SARL à LYON (69001) | 2 rue de Provence</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
+          <t>scp.paillard-pariset@notaires.fr</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
+          <t>scp.paillard-pariset@notaires.fr</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>0481098330</t>
+          <t>0472982798</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>0481098330</t>
+          <t>0472982798</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 58 rue Tête d'Or 69006 LYON France</t>
+          <t>Bureau principal 2 rue de Provence 69001 LYON France</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -7858,7 +7858,7 @@
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/onpc-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/pariset-notaire-sarl</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
@@ -7868,39 +7868,39 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:38</t>
+          <t>2026-08-02 08:12:57</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PARISET, Notaire, SARL à LYON (69001) | 2 rue de Provence</t>
+          <t>Office notarial PARTOUCHE Sébastien à LISSIEU (69380) | 101 Route Nationale 6</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>scp.paillard-pariset@notaires.fr</t>
+          <t>sebastien.partouche@notaires.fr</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>scp.paillard-pariset@notaires.fr</t>
+          <t>sebastien.partouche@notaires.fr</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>0472982798</t>
+          <t>0472599128</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>0472982798</t>
+          <t>0472599128</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 rue de Provence 69001 LYON France</t>
+          <t>Bureau principal 101 Route Nationale 6 69380 LISSIEU France</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lissieu</t>
         </is>
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pariset-notaire-sarl</t>
+          <t>https://www.notaires.fr/fr/office/partouche-sebastien</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
@@ -7930,39 +7930,39 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:40</t>
+          <t>2026-08-02 08:12:58</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PARTOUCHE Sébastien à LISSIEU (69380) | 101 Route Nationale 6</t>
+          <t>Office notarial PAUL &amp; associés – Notaires Lyon, SELAS à LYON (69009) | 28 rue Joannès Carret</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>sebastien.partouche@notaires.fr</t>
+          <t>corinne.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>sebastien.partouche@notaires.fr</t>
+          <t>corinne.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>0472599128</t>
+          <t>0412054740</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>0472599128</t>
+          <t>0412054740</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 101 Route Nationale 6 69380 LISSIEU France</t>
+          <t>Bureau principal 28 rue Joannès Carret 69009 LYON France</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -7977,12 +7977,12 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Lissieu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/partouche-sebastien</t>
+          <t>https://www.notaires.fr/fr/office/paul-associes-notaires-lyon-selas</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -7992,39 +7992,39 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:42</t>
+          <t>2026-08-02 08:13:00</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PAUL &amp; associés – Notaires Lyon, SELAS à LYON (69009) | 28 rue Joannès Carret</t>
+          <t>Office notarial PCMV NOTAIRES, SARL à LYON (69004) | 18/19 Place de la Croix Rousse</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>corinne.nicolle@notaires.fr</t>
+          <t>office@pcmv.notaires.fr</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>corinne.nicolle@notaires.fr</t>
+          <t>office@pcmv.notaires.fr</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>0412054740</t>
+          <t>0437408084</t>
         </is>
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>0412054740</t>
+          <t>0437408084</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 28 rue Joannès Carret 69009 LYON France</t>
+          <t>Bureau principal 18/19 Place de la Croix Rousse 69004 LYON France</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/paul-associes-notaires-lyon-selas</t>
+          <t>https://www.notaires.fr/fr/office/pcmv-notaires-sarl</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr">
@@ -8054,39 +8054,31 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:44</t>
+          <t>2026-08-02 08:13:01</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PCMV NOTAIRES, SARL à LYON (69004) | 18/19 Place de la Croix Rousse</t>
+          <t>Office notarial PERRAUD &amp; Associés - Notaires, SAS à LYON (69003) | 19 boulevard Eugène Deruelle</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>office@pcmv.notaires.fr</t>
+          <t>perraud.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>office@pcmv.notaires.fr</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>0437408084</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr">
-        <is>
-          <t>0437408084</t>
-        </is>
-      </c>
+          <t>perraud.lyon@notaires.fr</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr"/>
+      <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 18/19 Place de la Croix Rousse 69004 LYON France</t>
+          <t>Bureau principal 19 boulevard Eugène Deruelle 69003 LYON France</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -8106,7 +8098,7 @@
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pcmv-notaires-sarl</t>
+          <t>https://www.notaires.fr/fr/office/perraud-associes-notaires-sas-0</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -8116,31 +8108,39 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:45</t>
+          <t>2026-08-02 08:13:03</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PERRAUD &amp; Associés - Notaires, SAS à LYON (69003) | 19 boulevard Eugène Deruelle</t>
+          <t>Office notarial PESSIA Faustine à DOMMARTIN (69380) | 1702 route des Bois</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>perraud.lyon@notaires.fr</t>
+          <t>faustine.pessia@69072.notaires.fr</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>perraud.lyon@notaires.fr</t>
-        </is>
-      </c>
-      <c r="D123" s="7" t="inlineStr"/>
-      <c r="E123" s="7" t="inlineStr"/>
+          <t>faustine.pessia@69072.notaires.fr</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>0000000000</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>0000000000</t>
+        </is>
+      </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 19 boulevard Eugène Deruelle 69003 LYON France</t>
+          <t>Bureau principal 1702 route des Bois 69380 DOMMARTIN France</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Dommartin</t>
         </is>
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/perraud-associes-notaires-sas-0</t>
+          <t>https://www.notaires.fr/fr/office/pessia-faustine</t>
         </is>
       </c>
       <c r="K123" s="7" t="inlineStr">
@@ -8170,39 +8170,39 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:47</t>
+          <t>2026-08-02 08:13:04</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PESSIA Faustine à DOMMARTIN (69380) | 1702 route des Bois</t>
+          <t>Office notarial PICOT Laura à LYON (69006) | 63 rue Boileau</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>faustine.pessia@69072.notaires.fr</t>
+          <t>laura.picot@69212.notaires.fr</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>faustine.pessia@69072.notaires.fr</t>
+          <t>laura.picot@69212.notaires.fr</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0478133758</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0478133758</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1702 route des Bois 69380 DOMMARTIN France</t>
+          <t>Bureau principal 63 rue Boileau 69006 LYON France</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Dommartin</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pessia-faustine</t>
+          <t>https://www.notaires.fr/fr/office/picot-laura</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -8232,39 +8232,39 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:49</t>
+          <t>2026-08-02 08:13:06</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PICOT Laura à LYON (69006) | 63 rue Boileau</t>
+          <t>Office notarial PROUVOST-CLAEYS, SAS à associé unique à L'ARBRESLE (69210) | 193 Route de Sain-Bel</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>laura.picot@69212.notaires.fr</t>
+          <t>louise.prouvost@69209.notaires.fr</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>laura.picot@69212.notaires.fr</t>
+          <t>louise.prouvost@69209.notaires.fr</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>0478133758</t>
+          <t>0428299066</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>0478133758</t>
+          <t>0428299066</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 63 rue Boileau 69006 LYON France</t>
+          <t>Bureau principal 193 Route de Sain-Bel 69210 L'ARBRESLE France</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>L'arbresle</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/picot-laura</t>
+          <t>https://www.notaires.fr/fr/office/prouvost-claeys-sas-associe-unique</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr">
@@ -8294,39 +8294,39 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:50</t>
+          <t>2026-08-02 08:13:07</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PROUVOST-CLAEYS, SAS à associé unique à L'ARBRESLE (69210) | 193 Route de Sain-Bel</t>
+          <t>Office notarial RAY et associé, SELARL à SAINT-FONS (69190) | 1 Avenue Jean Jaurès</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>louise.prouvost@69209.notaires.fr</t>
+          <t>ray.sassard@notaires.fr</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>louise.prouvost@69209.notaires.fr</t>
+          <t>ray.sassard@notaires.fr</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>0428299066</t>
+          <t>0478700047</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>0428299066</t>
+          <t>0478700047</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 193 Route de Sain-Bel 69210 L'ARBRESLE France</t>
+          <t>Bureau principal 1 Avenue Jean Jaurès 69190 SAINT-FONS France</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>L'arbresle</t>
+          <t>Saint-Fons</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/prouvost-claeys-sas-associe-unique</t>
+          <t>https://www.notaires.fr/fr/office/ray-et-associe-selarl</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -8356,39 +8356,39 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:52</t>
+          <t>2026-08-02 08:13:10</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Office notarial RAY et associé, SELARL à SAINT-FONS (69190) | 1 Avenue Jean Jaurès</t>
+          <t>Office notarial REAL LEX Notaires à CRAPONNE (69290) | 123 AVENUE PIERRE DUMOND</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>ray.sassard@notaires.fr</t>
+          <t>office69066.craponne@notaires.fr</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>ray.sassard@notaires.fr</t>
+          <t>office69066.craponne@notaires.fr</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>0478700047</t>
+          <t>0478578039</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>0478700047</t>
+          <t>0478578039</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Avenue Jean Jaurès 69190 SAINT-FONS France</t>
+          <t>Bureau principal 123 AVENUE PIERRE DUMOND 69290 CRAPONNE France</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="I127" s="7" t="inlineStr">
         <is>
-          <t>Saint-Fons</t>
+          <t>Craponne</t>
         </is>
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/ray-et-associe-selarl</t>
+          <t>https://www.notaires.fr/fr/office/real-lex-notaires</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
@@ -8418,39 +8418,39 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:53</t>
+          <t>2026-08-02 08:13:11</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Office notarial REAL LEX Notaires à CRAPONNE (69290) | 123 AVENUE PIERRE DUMOND</t>
+          <t>Office notarial REBOTIER PERET LEVRAULT ET MERLE NOTAIRES ASSOCIES, SELARL à LYON (69009) | 2 boulevard Antoine de Saint Exupéry</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>office69066.craponne@notaires.fr</t>
+          <t>notaires.vaise@notaires.fr</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>office69066.craponne@notaires.fr</t>
+          <t>notaires.vaise@notaires.fr</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>0478578039</t>
+          <t>0478646749</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>0478578039</t>
+          <t>0478646749</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 123 AVENUE PIERRE DUMOND 69290 CRAPONNE France</t>
+          <t>Bureau principal 2 boulevard Antoine de Saint Exupéry 69009 LYON France</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Craponne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/real-lex-notaires</t>
+          <t>https://www.notaires.fr/fr/office/rebotier-peret-levrault-et-merle-notaires-associes-selarl</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
@@ -8480,39 +8480,39 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:55</t>
+          <t>2026-08-02 08:13:13</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Office notarial REBOTIER PERET LEVRAULT ET MERLE NOTAIRES ASSOCIES, SELARL à LYON (69009) | 2 boulevard Antoine de Saint Exupéry</t>
+          <t>Office notarial RENETEAU Anaïs à CHAPONOST (69630) | 1 Route des Troques</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>notaires.vaise@notaires.fr</t>
+          <t>anais.reneteau@reneteau.notaires.fr</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>notaires.vaise@notaires.fr</t>
+          <t>anais.reneteau@reneteau.notaires.fr</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>0478646749</t>
+          <t>0478563572</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>0478646749</t>
+          <t>0478563572</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 boulevard Antoine de Saint Exupéry 69009 LYON France</t>
+          <t>Bureau principal 1 Route des Troques 69630 CHAPONOST France</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="I129" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chaponost</t>
         </is>
       </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rebotier-peret-levrault-et-merle-notaires-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/reneteau-anais</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
@@ -8542,39 +8542,39 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:57</t>
+          <t>2026-08-02 08:13:15</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Office notarial RENETEAU Anaïs à CHAPONOST (69630) | 1 Route des Troques</t>
+          <t>Office notarial REY Karyne à LYON (69002) | 3 rue Victor Hugo</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>anais.reneteau@reneteau.notaires.fr</t>
+          <t>etude.rey@notaires.fr</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>anais.reneteau@reneteau.notaires.fr</t>
+          <t>etude.rey@notaires.fr</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>0478563572</t>
+          <t>0472162590</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>0478563572</t>
+          <t>0472162590</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Route des Troques 69630 CHAPONOST France</t>
+          <t>Bureau principal 3 rue Victor Hugo 69002 LYON France</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Chaponost</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/reneteau-anais</t>
+          <t>https://www.notaires.fr/fr/office/rey-karyne</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -8604,39 +8604,39 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:15:59</t>
+          <t>2026-08-02 08:13:16</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Office notarial REY Karyne à LYON (69002) | 3 rue Victor Hugo</t>
+          <t>Office notarial ROBIN Axel à LYON (69003) | 123 cours Albert Thomas</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>etude.rey@notaires.fr</t>
+          <t>etude@69047.notaires.fr</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>etude.rey@notaires.fr</t>
+          <t>etude@69047.notaires.fr</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>0472162590</t>
+          <t>0449232420</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>0472162590</t>
+          <t>0449232420</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 3 rue Victor Hugo 69002 LYON France</t>
+          <t>Bureau principal 123 cours Albert Thomas 69003 LYON France</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="J131" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rey-karyne</t>
+          <t>https://www.notaires.fr/fr/office/robin-axel</t>
         </is>
       </c>
       <c r="K131" s="7" t="inlineStr">
@@ -8666,39 +8666,39 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:01</t>
+          <t>2026-08-02 08:13:18</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ROBIN Axel à LYON (69003) | 123 cours Albert Thomas</t>
+          <t>Office notarial ROCHELOIS LYON, SELAS à LYON (69003) | 10-12 boulevard Marius Vivier Merle</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>etude@69047.notaires.fr</t>
+          <t>contact@rocheloislyon.notaires.fr</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>etude@69047.notaires.fr</t>
+          <t>contact@rocheloislyon.notaires.fr</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>0449232420</t>
+          <t>0487658201</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>0449232420</t>
+          <t>0487658201</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 123 cours Albert Thomas 69003 LYON France</t>
+          <t>Bureau principal 10-12 boulevard Marius Vivier Merle 69003 LYON France</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/robin-axel</t>
+          <t>https://www.notaires.fr/fr/office/rochelois-lyon-selas</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -8728,39 +8728,39 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:03</t>
+          <t>2026-08-02 08:13:20</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Office notarial ROCHELOIS LYON, SELAS à LYON (69003) | 10-12 boulevard Marius Vivier Merle</t>
+          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à LYON (69003) | 40 Rue Antoine Charial</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>contact@rocheloislyon.notaires.fr</t>
+          <t>corine.mussio@notaires.fr</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>contact@rocheloislyon.notaires.fr</t>
+          <t>corine.mussio@notaires.fr</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>0487658201</t>
+          <t>0472459539</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>0487658201</t>
+          <t>0472459539</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 10-12 boulevard Marius Vivier Merle 69003 LYON France</t>
+          <t>Bureau principal 40 Rue Antoine Charial 69003 LYON France</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rochelois-lyon-selas</t>
+          <t>https://www.notaires.fr/fr/office/rostaing-mussio-et-associee-selarl-0</t>
         </is>
       </c>
       <c r="K133" s="7" t="inlineStr">
@@ -8790,39 +8790,39 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:04</t>
+          <t>2026-08-02 08:13:22</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à LYON (69003) | 40 Rue Antoine Charial</t>
+          <t>Office notarial RUCHON Edouard à LYON (69005) | 60 avenue du Point du Jour</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>corine.mussio@notaires.fr</t>
+          <t>edouard.ruchon@notaires.fr</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>corine.mussio@notaires.fr</t>
+          <t>edouard.ruchon@notaires.fr</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>0472459539</t>
+          <t>0472544808</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>0472459539</t>
+          <t>0472544808</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 40 Rue Antoine Charial 69003 LYON France</t>
+          <t>Bureau principal 60 avenue du Point du Jour 69005 LYON France</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rostaing-mussio-et-associee-selarl-0</t>
+          <t>https://www.notaires.fr/fr/office/ruchon-edouard</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -8852,39 +8852,39 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:06</t>
+          <t>2026-08-02 08:13:23</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Office notarial RUCHON Edouard à LYON (69005) | 60 avenue du Point du Jour</t>
+          <t>Office notarial S2R NOTAIRES CONSEILS, SELARL à LYON (69006) | 50 boulevard des Belges</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>edouard.ruchon@notaires.fr</t>
+          <t>simon.reboul@69225.notaires.fr</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>edouard.ruchon@notaires.fr</t>
+          <t>simon.reboul@69225.notaires.fr</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>0472544808</t>
+          <t>0437479982</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>0472544808</t>
+          <t>0437479982</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 60 avenue du Point du Jour 69005 LYON France</t>
+          <t>Bureau principal 50 boulevard des Belges 69006 LYON France</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/ruchon-edouard</t>
+          <t>https://www.notaires.fr/fr/office/s2r-notaires-conseils-selarl</t>
         </is>
       </c>
       <c r="K135" s="7" t="inlineStr">
@@ -8914,39 +8914,39 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:08</t>
+          <t>2026-08-02 08:13:25</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Office notarial S2R NOTAIRES CONSEILS, SELARL à LYON (69006) | 50 boulevard des Belges</t>
+          <t>Office notarial SALAGNAT Frédéric à CHASSIEU (69680) | 56 route de Genas</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>simon.reboul@69225.notaires.fr</t>
+          <t>salagnat@notaires.fr</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>simon.reboul@69225.notaires.fr</t>
+          <t>salagnat@notaires.fr</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>0437479982</t>
+          <t>0472797470</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>0437479982</t>
+          <t>0472797470</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 50 boulevard des Belges 69006 LYON France</t>
+          <t>Bureau principal 56 route de Genas 69680 CHASSIEU France</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -8961,12 +8961,12 @@
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chassieu</t>
         </is>
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/s2r-notaires-conseils-selarl</t>
+          <t>https://www.notaires.fr/fr/office/salagnat-frederic</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -8976,39 +8976,39 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:10</t>
+          <t>2026-08-02 08:13:27</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SALAGNAT Frédéric à CHASSIEU (69680) | 56 route de Genas</t>
+          <t>Office notarial SALICHON &amp; ASSOCIES, SARL à LYON (69006) | 3 Cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>salagnat@notaires.fr</t>
+          <t>salichonetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>salagnat@notaires.fr</t>
+          <t>salichonetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>0472797470</t>
+          <t>0478931098</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>0472797470</t>
+          <t>0478931098</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 56 route de Genas 69680 CHASSIEU France</t>
+          <t>Bureau principal 3 Cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>Chassieu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/salagnat-frederic</t>
+          <t>https://www.notaires.fr/fr/office/salichon-associes-sarl</t>
         </is>
       </c>
       <c r="K137" s="7" t="inlineStr">
@@ -9038,39 +9038,39 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:12</t>
+          <t>2026-08-02 08:13:28</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SALICHON &amp; ASSOCIES, SARL à LYON (69006) | 3 Cours Franklin Roosevelt</t>
+          <t>Office notarial SARL à associé unique GONDRAN, notaire associée à BELLEVILLE (69220) | 19 rue des Remparts</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>salichonetassocies@notaires.fr</t>
+          <t>anne.gondran@69248.notaires.fr</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>salichonetassocies@notaires.fr</t>
+          <t>anne.gondran@69248.notaires.fr</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>0478931098</t>
+          <t>04 87 01 02 10</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>0478931098</t>
+          <t>04 87 01 02 10</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 3 Cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 19 rue des Remparts 69220 BELLEVILLE France</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/salichon-associes-sarl</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-gondran-notaire-associee</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -9100,39 +9100,39 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:14</t>
+          <t>2026-08-02 08:13:30</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique GONDRAN, notaire associée à BELLEVILLE (69220) | 19 rue des Remparts</t>
+          <t>Office notarial SARL à associé unique Notaires du Promenoir à VILLEFRANCHE-SUR-SAÔNE (69400) | 61 rue d'Anse</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>anne.gondran@69248.notaires.fr</t>
+          <t>etude@promenoir.notaires.fr</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>anne.gondran@69248.notaires.fr</t>
+          <t>etude@promenoir.notaires.fr</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>04 87 01 02 10</t>
+          <t>0474654500</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>04 87 01 02 10</t>
+          <t>0474654500</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 19 rue des Remparts 69220 BELLEVILLE France</t>
+          <t>Bureau principal 61 rue d'Anse 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J139" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-gondran-notaire-associee</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-notaires-du-promenoir</t>
         </is>
       </c>
       <c r="K139" s="7" t="inlineStr">
@@ -9162,39 +9162,39 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:16</t>
+          <t>2026-08-02 08:13:32</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique Notaires du Promenoir à VILLEFRANCHE-SUR-SAÔNE (69400) | 61 rue d'Anse</t>
+          <t>Office notarial SARL à associé unique OFFICE NOTARIAL DE LA TABLE DE PIERRE à FRANCHEVILLE (69340) | 26 Avenue de la Table de Pierre</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>etude@promenoir.notaires.fr</t>
+          <t>christelle.farce@69220.notaires.fr</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>etude@promenoir.notaires.fr</t>
+          <t>christelle.farce@69220.notaires.fr</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>0474654500</t>
+          <t>0437202524</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>0474654500</t>
+          <t>0437202524</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 61 rue d'Anse 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 26 Avenue de la Table de Pierre 69340 FRANCHEVILLE France</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Francheville</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-notaires-du-promenoir</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-office-notarial-de-la-table-de-pierre</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
@@ -9224,39 +9224,39 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:17</t>
+          <t>2026-08-02 08:13:33</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique OFFICE NOTARIAL DE LA TABLE DE PIERRE à FRANCHEVILLE (69340) | 26 Avenue de la Table de Pierre</t>
+          <t>Office notarial SARL à associée unique NOTAIRE VALLE D'AZERGUES à LAMURE-SUR-AZERGUES (69870) | 10 impasse Chavanet</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>christelle.farce@69220.notaires.fr</t>
+          <t>office@69095.notaires.fr</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>christelle.farce@69220.notaires.fr</t>
+          <t>office@69095.notaires.fr</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>0437202524</t>
+          <t>0474030522</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>0437202524</t>
+          <t>0474030522</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 26 Avenue de la Table de Pierre 69340 FRANCHEVILLE France</t>
+          <t>Bureau principal 10 impasse Chavanet 69870 LAMURE-SUR-AZERGUES France</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
-          <t>Francheville</t>
+          <t>Lamure-Sur-Azergues</t>
         </is>
       </c>
       <c r="J141" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-office-notarial-de-la-table-de-pierre</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associee-unique-notaire-valle-dazergues</t>
         </is>
       </c>
       <c r="K141" s="7" t="inlineStr">
@@ -9286,39 +9286,39 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:20</t>
+          <t>2026-08-02 08:13:35</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associée unique NOTAIRE VALLE D'AZERGUES à LAMURE-SUR-AZERGUES (69870) | 10 impasse Chavanet</t>
+          <t>Office notarial SARL CADRAN Notaires Conseils à LYON (69007) | 75 rue Chevreul</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>office@69095.notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>office@69095.notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>0474030522</t>
+          <t>0437261144</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>0474030522</t>
+          <t>0437261144</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 impasse Chavanet 69870 LAMURE-SUR-AZERGUES France</t>
+          <t>Bureau principal 75 rue Chevreul 69007 LYON France</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Lamure-Sur-Azergues</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associee-unique-notaire-valle-dazergues</t>
+          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -9348,14 +9348,14 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:22</t>
+          <t>2026-08-02 08:13:36</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL CADRAN Notaires Conseils à LYON (69007) | 75 rue Chevreul</t>
+          <t>Office notarial SARL CADRAN Notaires Conseils à TASSIN-LA-DEMI-LUNE (69160) | 3 avenue de Lauterbourg</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
@@ -9370,17 +9370,17 @@
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>0437261144</t>
+          <t>0478343602</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>0437261144</t>
+          <t>0478343602</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 75 rue Chevreul 69007 LYON France</t>
+          <t>Bureau principal 3 avenue de Lauterbourg 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils</t>
+          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils-0</t>
         </is>
       </c>
       <c r="K143" s="7" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:16:24</t>
+          <t>2026-08-02 08:13:38</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:35</t>
+          <t>2026-08-02 08:10:45</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:37</t>
+          <t>2026-08-02 08:10:47</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:39</t>
+          <t>2026-08-02 08:10:49</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:41</t>
+          <t>2026-08-02 08:10:51</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:43</t>
+          <t>2026-08-02 08:10:53</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:46</t>
+          <t>2026-08-02 08:10:55</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:47</t>
+          <t>2026-08-02 08:10:56</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:48</t>
+          <t>2026-08-02 08:10:58</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:50</t>
+          <t>2026-08-02 08:10:59</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:52</t>
+          <t>2026-08-02 08:11:01</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:53</t>
+          <t>2026-08-02 08:11:03</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:55</t>
+          <t>2026-08-02 08:11:04</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:56</t>
+          <t>2026-08-02 08:11:06</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:58</t>
+          <t>2026-08-02 08:11:08</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:59</t>
+          <t>2026-08-02 08:11:09</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:01</t>
+          <t>2026-08-02 08:11:11</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:02</t>
+          <t>2026-08-02 08:11:13</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:04</t>
+          <t>2026-08-02 08:11:15</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:06</t>
+          <t>2026-08-02 08:11:17</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:07</t>
+          <t>2026-08-02 08:11:18</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:09</t>
+          <t>2026-08-02 08:11:20</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:11</t>
+          <t>2026-08-02 08:11:22</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:12</t>
+          <t>2026-08-02 08:11:24</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:14</t>
+          <t>2026-08-02 08:11:26</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:16</t>
+          <t>2026-08-02 08:11:28</t>
         </is>
       </c>
     </row>
@@ -11014,39 +11014,39 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:17</t>
+          <t>2026-08-02 08:11:30</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
         <is>
-          <t>Office notarial HAMPARSOUMIAN et CAZARIAN, SELARL à LYON (69002) | 6 rue Emile Zola</t>
+          <t>Office notarial HAMPARSOUMIAN Magalie à SAINT-DIDIER-AU-MONT-D'OR (69370) | 113 rue de Saint Cyr</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>sevane.cazarian@notaires.fr</t>
+          <t>m.hamparsoumian@notaires.fr</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>sevane.cazarian@notaires.fr</t>
+          <t>m.hamparsoumian@notaires.fr</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>0478389273</t>
+          <t>0472091288</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>0478389273</t>
+          <t>0472091288</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 6 rue Emile Zola 69002 LYON France</t>
+          <t>Bureau principal 113 rue de Saint Cyr 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G170" s="5" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="I170" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Didier-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J170" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/hamparsoumian-et-cazarian-selarl</t>
+          <t>https://www.notaires.fr/fr/office/hamparsoumian-magalie</t>
         </is>
       </c>
       <c r="K170" s="5" t="inlineStr">
@@ -11076,39 +11076,39 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:19</t>
+          <t>2026-08-02 08:11:32</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="7" t="inlineStr">
         <is>
-          <t>Office notarial HAMPARSOUMIAN Magalie à SAINT-DIDIER-AU-MONT-D'OR (69370) | 113 rue de Saint Cyr</t>
+          <t>Office notarial HEITZ-ESCUDIER et associée, SELAS à LYON (69006) | 20 Avenue du Maréchal Foch</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>m.hamparsoumian@notaires.fr</t>
+          <t>office.lyon.foch.69175@notaires.fr</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>m.hamparsoumian@notaires.fr</t>
+          <t>office.lyon.foch.69175@notaires.fr</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>0472091288</t>
+          <t>0437482555</t>
         </is>
       </c>
       <c r="E171" s="7" t="inlineStr">
         <is>
-          <t>0472091288</t>
+          <t>0437482555</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 113 rue de Saint Cyr 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
+          <t>Bureau principal 20 Avenue du Maréchal Foch 69006 LYON France</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
@@ -11123,12 +11123,12 @@
       </c>
       <c r="I171" s="7" t="inlineStr">
         <is>
-          <t>Saint-Didier-Au-Mont-D'or</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J171" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/hamparsoumian-magalie</t>
+          <t>https://www.notaires.fr/fr/office/heitz-escudier-et-associee-selas</t>
         </is>
       </c>
       <c r="K171" s="7" t="inlineStr">
@@ -11138,39 +11138,39 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:20</t>
+          <t>2026-08-02 08:11:34</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
         <is>
-          <t>Office notarial HEITZ-ESCUDIER et associée, SELAS à LYON (69006) | 20 Avenue du Maréchal Foch</t>
+          <t>Office notarial HEYMONET Diane à LYON (69003) | 38 cours Eugénie</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>office.lyon.foch.69175@notaires.fr</t>
+          <t>etude.heymonet@notaires.fr</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>office.lyon.foch.69175@notaires.fr</t>
+          <t>etude.heymonet@notaires.fr</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>0437482555</t>
+          <t>0437560711</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>0437482555</t>
+          <t>0437560711</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 20 Avenue du Maréchal Foch 69006 LYON France</t>
+          <t>Bureau principal 38 cours Eugénie 69003 LYON France</t>
         </is>
       </c>
       <c r="G172" s="5" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="J172" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/heitz-escudier-et-associee-selas</t>
+          <t>https://www.notaires.fr/fr/office/heymonet-diane</t>
         </is>
       </c>
       <c r="K172" s="5" t="inlineStr">
@@ -11200,39 +11200,39 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:22</t>
+          <t>2026-08-02 08:11:36</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="7" t="inlineStr">
         <is>
-          <t>Office notarial HEYMONET Diane à LYON (69003) | 38 cours Eugénie</t>
+          <t>Office notarial Homnia notaires, SAS à VILLEURBANNE (69100) | 1 place Charles Hernu</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>etude.heymonet@notaires.fr</t>
+          <t>homnia.69069@notaires.fr</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>etude.heymonet@notaires.fr</t>
+          <t>homnia.69069@notaires.fr</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>0437560711</t>
+          <t>0472114787</t>
         </is>
       </c>
       <c r="E173" s="7" t="inlineStr">
         <is>
-          <t>0437560711</t>
+          <t>0472114787</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 38 cours Eugénie 69003 LYON France</t>
+          <t>Bureau principal 1 place Charles Hernu 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="I173" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J173" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/heymonet-diane</t>
+          <t>https://www.notaires.fr/fr/office/homnia-notaires-sas</t>
         </is>
       </c>
       <c r="K173" s="7" t="inlineStr">
@@ -11262,39 +11262,39 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:23</t>
+          <t>2026-08-02 08:11:38</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="inlineStr">
         <is>
-          <t>Office notarial Homnia notaires, SAS à VILLEURBANNE (69100) | 1 place Charles Hernu</t>
+          <t>Office notarial Homnia notaires, SAS à LYON (69002) | 2 rue Childebert</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>homnia.69069@notaires.fr</t>
+          <t>elodie.coche@notaires.fr</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>homnia.69069@notaires.fr</t>
+          <t>elodie.coche@notaires.fr</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>0472114787</t>
+          <t>0478925695</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>0472114787</t>
+          <t>0478925695</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 place Charles Hernu 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 2 rue Childebert 69002 LYON France</t>
         </is>
       </c>
       <c r="G174" s="5" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J174" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/homnia-notaires-sas</t>
+          <t>https://www.notaires.fr/fr/office/homnia-notaires-sas-0</t>
         </is>
       </c>
       <c r="K174" s="5" t="inlineStr">
@@ -11324,39 +11324,39 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:25</t>
+          <t>2026-08-02 08:11:40</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="inlineStr">
         <is>
-          <t>Office notarial Homnia notaires, SAS à LYON (69002) | 2 rue Childebert</t>
+          <t>Office notarial JACOB – CARTIER, notaires, SELARL à LYON (69001) | 1 rue Puits Gaillot</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>elodie.coche@notaires.fr</t>
+          <t>jacobcartier.69016@notaires.fr</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>elodie.coche@notaires.fr</t>
+          <t>jacobcartier.69016@notaires.fr</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>0478925695</t>
+          <t>0478286299</t>
         </is>
       </c>
       <c r="E175" s="7" t="inlineStr">
         <is>
-          <t>0478925695</t>
+          <t>0478286299</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 rue Childebert 69002 LYON France</t>
+          <t>Bureau principal 1 rue Puits Gaillot 69001 LYON France</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="J175" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/homnia-notaires-sas-0</t>
+          <t>https://www.notaires.fr/fr/office/jacob-cartier-notaires-selarl</t>
         </is>
       </c>
       <c r="K175" s="7" t="inlineStr">
@@ -11386,39 +11386,39 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:27</t>
+          <t>2026-08-02 08:11:42</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
         <is>
-          <t>Office notarial JACOB – CARTIER, notaires, SELARL à LYON (69001) | 1 rue Puits Gaillot</t>
+          <t>Office notarial Julie SCHLÄPPI, SELURL à SAINT-DIDIER-AU-MONT-D'OR (69370) | 44 avenue de la République</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>jacobcartier.69016@notaires.fr</t>
+          <t>julie.schlappi@notaires.fr</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>jacobcartier.69016@notaires.fr</t>
+          <t>julie.schlappi@notaires.fr</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>0478286299</t>
+          <t>0662910631</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>0478286299</t>
+          <t>0662910631</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Puits Gaillot 69001 LYON France</t>
+          <t>Bureau principal 44 avenue de la République 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G176" s="5" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Didier-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J176" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/jacob-cartier-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/julie-schlappi-selurl</t>
         </is>
       </c>
       <c r="K176" s="5" t="inlineStr">
@@ -11448,39 +11448,39 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:29</t>
+          <t>2026-08-02 08:11:44</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="inlineStr">
         <is>
-          <t>Office notarial Julie SCHLÄPPI, SELURL à SAINT-DIDIER-AU-MONT-D'OR (69370) | 44 avenue de la République</t>
+          <t>Office notarial KAEUFLING NOTAIRES, SARL à SAINT-PRIEST (69800) | 12 Bd François Reymond</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>julie.schlappi@notaires.fr</t>
+          <t>kaeufling@notaires.fr</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>julie.schlappi@notaires.fr</t>
+          <t>kaeufling@notaires.fr</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>0662910631</t>
+          <t>0478201103</t>
         </is>
       </c>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>0662910631</t>
+          <t>0478201103</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 44 avenue de la République 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
+          <t>Bureau principal 12 Bd François Reymond 69800 SAINT-PRIEST France</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="I177" s="7" t="inlineStr">
         <is>
-          <t>Saint-Didier-Au-Mont-D'or</t>
+          <t>Saint-Priest</t>
         </is>
       </c>
       <c r="J177" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/julie-schlappi-selurl</t>
+          <t>https://www.notaires.fr/fr/office/kaeufling-notaires-sarl</t>
         </is>
       </c>
       <c r="K177" s="7" t="inlineStr">
@@ -11510,39 +11510,39 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:30</t>
+          <t>2026-08-02 08:11:46</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
         <is>
-          <t>Office notarial KAEUFLING NOTAIRES, SARL à SAINT-PRIEST (69800) | 12 Bd François Reymond</t>
+          <t>Office notarial KINTZIG et associé à SAINT-LAURENT-DE-MURE (69720) | 77 avenue Jean Moulin</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>kaeufling@notaires.fr</t>
+          <t>contact@kintzig.notaires.fr</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>kaeufling@notaires.fr</t>
+          <t>contact@kintzig.notaires.fr</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>0478201103</t>
+          <t>0472486363</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>0478201103</t>
+          <t>0472486363</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 12 Bd François Reymond 69800 SAINT-PRIEST France</t>
+          <t>Bureau principal 77 avenue Jean Moulin 69720 SAINT-LAURENT-DE-MURE France</t>
         </is>
       </c>
       <c r="G178" s="5" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>Saint-Priest</t>
+          <t>Saint-Laurent-De-Mure</t>
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/kaeufling-notaires-sarl</t>
+          <t>https://www.notaires.fr/fr/office/kintzig-et-associe</t>
         </is>
       </c>
       <c r="K178" s="5" t="inlineStr">
@@ -11572,39 +11572,39 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:32</t>
+          <t>2026-08-02 08:11:48</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="inlineStr">
         <is>
-          <t>Office notarial KINTZIG et associé à SAINT-LAURENT-DE-MURE (69720) | 77 avenue Jean Moulin</t>
+          <t>Office notarial KLEPPING Julien à LYON (69007) | 23 rue Crépet</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>contact@kintzig.notaires.fr</t>
+          <t>contact.69288@notaires.fr</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>contact@kintzig.notaires.fr</t>
+          <t>contact.69288@notaires.fr</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>0472486363</t>
+          <t>0465848565</t>
         </is>
       </c>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>0472486363</t>
+          <t>0465848565</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 77 avenue Jean Moulin 69720 SAINT-LAURENT-DE-MURE France</t>
+          <t>Bureau principal 23 rue Crépet 69007 LYON France</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
@@ -11619,12 +11619,12 @@
       </c>
       <c r="I179" s="7" t="inlineStr">
         <is>
-          <t>Saint-Laurent-De-Mure</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J179" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/kintzig-et-associe</t>
+          <t>https://www.notaires.fr/fr/office/klepping-julien</t>
         </is>
       </c>
       <c r="K179" s="7" t="inlineStr">
@@ -11634,39 +11634,39 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:34</t>
+          <t>2026-08-02 08:11:50</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
         <is>
-          <t>Office notarial KLEPPING Julien à LYON (69007) | 23 rue Crépet</t>
+          <t>Office notarial KLIF Notaire, SELAS à associé unique à LYON (69006) | 49 cours Vitton</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>contact.69288@notaires.fr</t>
+          <t>melanie.klif@notaires.fr</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>contact.69288@notaires.fr</t>
+          <t>melanie.klif@notaires.fr</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>0465848565</t>
+          <t>0478174702</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>0465848565</t>
+          <t>0478174702</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 23 rue Crépet 69007 LYON France</t>
+          <t>Bureau principal 49 cours Vitton 69006 LYON France</t>
         </is>
       </c>
       <c r="G180" s="5" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="J180" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/klepping-julien</t>
+          <t>https://www.notaires.fr/fr/office/klif-notaire-selas-associe-unique</t>
         </is>
       </c>
       <c r="K180" s="5" t="inlineStr">
@@ -11696,39 +11696,39 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:36</t>
+          <t>2026-08-02 08:11:51</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="inlineStr">
         <is>
-          <t>Office notarial KLIF Notaire, SELAS à associé unique à LYON (69006) | 49 cours Vitton</t>
+          <t>Office notarial KONSTELL, SELARL à LYON (69002) | 4 rue de la Charité</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>melanie.klif@notaires.fr</t>
+          <t>camille.michaud@notaires.fr</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>melanie.klif@notaires.fr</t>
+          <t>camille.michaud@notaires.fr</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>0478174702</t>
+          <t>0472775340</t>
         </is>
       </c>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>0478174702</t>
+          <t>0472775340</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 49 cours Vitton 69006 LYON France</t>
+          <t>Bureau principal 4 rue de la Charité 69002 LYON France</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="J181" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/klif-notaire-selas-associe-unique</t>
+          <t>https://www.notaires.fr/fr/office/konstell-selarl</t>
         </is>
       </c>
       <c r="K181" s="7" t="inlineStr">
@@ -11758,39 +11758,39 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:39</t>
+          <t>2026-08-02 08:11:54</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="5" t="inlineStr">
         <is>
-          <t>Office notarial KONSTELL, SELARL à LYON (69002) | 4 rue de la Charité</t>
+          <t>Office notarial LAGREVOL Edouard à LIMONEST (69760) | 4 Place du Griffon</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>camille.michaud@notaires.fr</t>
+          <t>edouard.lagrevol@notaires.fr</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>camille.michaud@notaires.fr</t>
+          <t>edouard.lagrevol@notaires.fr</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>0472775340</t>
+          <t>0451262403</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>0472775340</t>
+          <t>0451262403</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 4 rue de la Charité 69002 LYON France</t>
+          <t>Bureau principal 4 Place du Griffon 69760 LIMONEST France</t>
         </is>
       </c>
       <c r="G182" s="5" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Limonest</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/konstell-selarl</t>
+          <t>https://www.notaires.fr/fr/office/lagrevol-edouard</t>
         </is>
       </c>
       <c r="K182" s="5" t="inlineStr">
@@ -11820,39 +11820,39 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:41</t>
+          <t>2026-08-02 08:11:57</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="inlineStr">
         <is>
-          <t>Office notarial LAGREVOL Edouard à LIMONEST (69760) | 4 Place du Griffon</t>
+          <t>Office notarial LAITHIER Céline à LYON (69002) | 41 rue de la Bourse</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>edouard.lagrevol@notaires.fr</t>
+          <t>celine.laithier@notaires.fr</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>edouard.lagrevol@notaires.fr</t>
+          <t>celine.laithier@notaires.fr</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>0451262403</t>
+          <t>0478921000</t>
         </is>
       </c>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>0451262403</t>
+          <t>0478921000</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 4 Place du Griffon 69760 LIMONEST France</t>
+          <t>Bureau principal 41 rue de la Bourse 69002 LYON France</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
@@ -11867,12 +11867,12 @@
       </c>
       <c r="I183" s="7" t="inlineStr">
         <is>
-          <t>Limonest</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J183" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lagrevol-edouard</t>
+          <t>https://www.notaires.fr/fr/office/laithier-celine</t>
         </is>
       </c>
       <c r="K183" s="7" t="inlineStr">
@@ -11882,39 +11882,39 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:43</t>
+          <t>2026-08-02 08:11:58</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Office notarial LAITHIER Céline à LYON (69002) | 41 rue de la Bourse</t>
+          <t>Office notarial LAMAMRA Terec à NEUVILLE-SUR-SAÔNE (69250) | 11 Avenue Carnot</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>celine.laithier@notaires.fr</t>
+          <t>terec.lamamra@lamamra.notaires.fr</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>celine.laithier@notaires.fr</t>
+          <t>terec.lamamra@lamamra.notaires.fr</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>0478921000</t>
+          <t>0469470098</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>0478921000</t>
+          <t>0469470098</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 41 rue de la Bourse 69002 LYON France</t>
+          <t>Bureau principal 11 Avenue Carnot 69250 NEUVILLE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G184" s="5" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Neuville-Sur-Saône</t>
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/laithier-celine</t>
+          <t>https://www.notaires.fr/fr/office/lamamra-terec</t>
         </is>
       </c>
       <c r="K184" s="5" t="inlineStr">
@@ -11944,39 +11944,39 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:44</t>
+          <t>2026-08-02 08:12:00</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>Office notarial LAMAMRA Terec à NEUVILLE-SUR-SAÔNE (69250) | 11 Avenue Carnot</t>
+          <t>Office notarial LAMOTHE Damien à LYON (69007) | 193 rue Marcel Mérieux</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>terec.lamamra@lamamra.notaires.fr</t>
+          <t>damien.lamothe@notaires.fr</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>terec.lamamra@lamamra.notaires.fr</t>
+          <t>damien.lamothe@notaires.fr</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>0469470098</t>
+          <t>0481912650</t>
         </is>
       </c>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>0469470098</t>
+          <t>0481912650</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 11 Avenue Carnot 69250 NEUVILLE-SUR-SAÔNE France</t>
+          <t>Bureau principal 193 rue Marcel Mérieux 69007 LYON France</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="I185" s="7" t="inlineStr">
         <is>
-          <t>Neuville-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J185" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lamamra-terec</t>
+          <t>https://www.notaires.fr/fr/office/lamothe-damien</t>
         </is>
       </c>
       <c r="K185" s="7" t="inlineStr">
@@ -12006,39 +12006,39 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:46</t>
+          <t>2026-08-02 08:12:02</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="5" t="inlineStr">
         <is>
-          <t>Office notarial LAMOTHE Damien à LYON (69007) | 193 rue Marcel Mérieux</t>
+          <t>Office notarial LANGARD-NOTAIRE, SELARL à LYON (69008) | 11, rue Berchet</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>damien.lamothe@notaires.fr</t>
+          <t>jean-baptiste.langard@notaires.fr</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>damien.lamothe@notaires.fr</t>
+          <t>jean-baptiste.langard@notaires.fr</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>0481912650</t>
+          <t>0437905470</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
         <is>
-          <t>0481912650</t>
+          <t>0437905470</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 193 rue Marcel Mérieux 69007 LYON France</t>
+          <t>Bureau principal 11, rue Berchet 69008 LYON France</t>
         </is>
       </c>
       <c r="G186" s="5" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lamothe-damien</t>
+          <t>https://www.notaires.fr/fr/office/langard-notaire-selarl</t>
         </is>
       </c>
       <c r="K186" s="5" t="inlineStr">
@@ -12068,39 +12068,39 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:48</t>
+          <t>2026-08-02 08:12:04</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="7" t="inlineStr">
         <is>
-          <t>Office notarial LANGARD-NOTAIRE, SELARL à LYON (69008) | 11, rue Berchet</t>
+          <t>Office notarial LAUTREY et associée, SELARL à VINDRY-SUR-TURDINE - PONTCHARRA SUR TURDINE (69490) | 4 allée Henri Dunant</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>jean-baptiste.langard@notaires.fr</t>
+          <t>julie.lautrey@notaires.fr</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>jean-baptiste.langard@notaires.fr</t>
+          <t>julie.lautrey@notaires.fr</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>0437905470</t>
+          <t>0474056119</t>
         </is>
       </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>0437905470</t>
+          <t>0474056119</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 11, rue Berchet 69008 LYON France</t>
+          <t>Bureau principal 4 allée Henri Dunant 69490 VINDRY-SUR-TURDINE - PONTCHARRA SUR TURDINE France</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="I187" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Vindry-Sur-Turdine - Pontcharra Sur Turdine</t>
         </is>
       </c>
       <c r="J187" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/langard-notaire-selarl</t>
+          <t>https://www.notaires.fr/fr/office/lautrey-et-associee-selarl</t>
         </is>
       </c>
       <c r="K187" s="7" t="inlineStr">
@@ -12130,39 +12130,39 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:49</t>
+          <t>2026-08-02 08:12:06</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
         <is>
-          <t>Office notarial LAUTREY et associée, SELARL à VINDRY-SUR-TURDINE - PONTCHARRA SUR TURDINE (69490) | 4 allée Henri Dunant</t>
+          <t>Office notarial LAVOREL Amaury à LYON (69005) | 13 place Benoit Crépu</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>julie.lautrey@notaires.fr</t>
+          <t>amaury.lavorel@69060.notaires.fr</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>julie.lautrey@notaires.fr</t>
+          <t>amaury.lavorel@69060.notaires.fr</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>0474056119</t>
+          <t>0478620672</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>0474056119</t>
+          <t>0478620672</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 4 allée Henri Dunant 69490 VINDRY-SUR-TURDINE - PONTCHARRA SUR TURDINE France</t>
+          <t>Bureau principal 13 place Benoit Crépu 69005 LYON France</t>
         </is>
       </c>
       <c r="G188" s="5" t="inlineStr">
@@ -12177,12 +12177,12 @@
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>Vindry-Sur-Turdine - Pontcharra Sur Turdine</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J188" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lautrey-et-associee-selarl</t>
+          <t>https://www.notaires.fr/fr/office/lavorel-amaury</t>
         </is>
       </c>
       <c r="K188" s="5" t="inlineStr">
@@ -12192,39 +12192,39 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:51</t>
+          <t>2026-08-02 08:12:07</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="inlineStr">
         <is>
-          <t>Office notarial LAVOREL Amaury à LYON (69005) | 13 place Benoit Crépu</t>
+          <t>Office notarial LES NOUVEAUX NOTAIRES, SELAS à LYON (69006) | 10 rue Malesherbes</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>amaury.lavorel@69060.notaires.fr</t>
+          <t>pierre.benayoun@notaires.fr</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>amaury.lavorel@69060.notaires.fr</t>
+          <t>pierre.benayoun@notaires.fr</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>0478620672</t>
+          <t>0478898865</t>
         </is>
       </c>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>0478620672</t>
+          <t>0478898865</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 13 place Benoit Crépu 69005 LYON France</t>
+          <t>Bureau principal 10 rue Malesherbes 69006 LYON France</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="J189" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lavorel-amaury</t>
+          <t>https://www.notaires.fr/fr/office/les-nouveaux-notaires-selas</t>
         </is>
       </c>
       <c r="K189" s="7" t="inlineStr">
@@ -12254,39 +12254,39 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:52</t>
+          <t>2026-08-02 08:12:09</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
         <is>
-          <t>Office notarial LES NOUVEAUX NOTAIRES, SELAS à LYON (69006) | 10 rue Malesherbes</t>
+          <t>Office notarial LINK NOTAIRES, SARL à CALUIRE-ET-CUIRE (69300) | 71 Rue François Peissel</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>pierre.benayoun@notaires.fr</t>
+          <t>aymeric.depont@notaires.fr</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>pierre.benayoun@notaires.fr</t>
+          <t>aymeric.depont@notaires.fr</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>0478898865</t>
+          <t>0428298050</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>0478898865</t>
+          <t>0428298050</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 rue Malesherbes 69006 LYON France</t>
+          <t>Bureau principal 71 Rue François Peissel 69300 CALUIRE-ET-CUIRE France</t>
         </is>
       </c>
       <c r="G190" s="5" t="inlineStr">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Caluire-Et-Cuire</t>
         </is>
       </c>
       <c r="J190" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/les-nouveaux-notaires-selas</t>
+          <t>https://www.notaires.fr/fr/office/link-notaires-sarl-0</t>
         </is>
       </c>
       <c r="K190" s="5" t="inlineStr">
@@ -12316,39 +12316,39 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:54</t>
+          <t>2026-08-02 08:12:11</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="inlineStr">
         <is>
-          <t>Office notarial LINK NOTAIRES, SARL à CALUIRE-ET-CUIRE (69300) | 71 Rue François Peissel</t>
+          <t>Office notarial LOMBARD Wafae à LIMONEST (69760) | 334 chemin de Champivost</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>aymeric.depont@notaires.fr</t>
+          <t>wafae.lombard@69198.notaires.fr</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>aymeric.depont@notaires.fr</t>
+          <t>wafae.lombard@69198.notaires.fr</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>0428298050</t>
+          <t>0428298489</t>
         </is>
       </c>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>0428298050</t>
+          <t>0428298489</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 71 Rue François Peissel 69300 CALUIRE-ET-CUIRE France</t>
+          <t>Bureau principal 334 chemin de Champivost 69760 LIMONEST France</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
@@ -12363,12 +12363,12 @@
       </c>
       <c r="I191" s="7" t="inlineStr">
         <is>
-          <t>Caluire-Et-Cuire</t>
+          <t>Limonest</t>
         </is>
       </c>
       <c r="J191" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/link-notaires-sarl-0</t>
+          <t>https://www.notaires.fr/fr/office/lombard-wafae</t>
         </is>
       </c>
       <c r="K191" s="7" t="inlineStr">
@@ -12378,39 +12378,39 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:56</t>
+          <t>2026-08-02 08:12:13</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="5" t="inlineStr">
         <is>
-          <t>Office notarial LOMBARD Wafae à LIMONEST (69760) | 334 chemin de Champivost</t>
+          <t>Office notarial LUMEN NOTAIRES, SELARL à LYON (69008) | 2 Avenue des Frères Lumière</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>wafae.lombard@69198.notaires.fr</t>
+          <t>greco.ph@notaires.fr</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>wafae.lombard@69198.notaires.fr</t>
+          <t>greco.ph@notaires.fr</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>0428298489</t>
+          <t>0428299700</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>0428298489</t>
+          <t>0428299700</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 334 chemin de Champivost 69760 LIMONEST France</t>
+          <t>Bureau principal 2 Avenue des Frères Lumière 69008 LYON France</t>
         </is>
       </c>
       <c r="G192" s="5" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>Limonest</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lombard-wafae</t>
+          <t>https://www.notaires.fr/fr/office/lumen-notaires-selarl</t>
         </is>
       </c>
       <c r="K192" s="5" t="inlineStr">
@@ -12440,39 +12440,39 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:57</t>
+          <t>2026-08-02 08:12:14</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="inlineStr">
         <is>
-          <t>Office notarial LUMEN NOTAIRES, SELARL à LYON (69008) | 2 Avenue des Frères Lumière</t>
+          <t>Office notarial Maître MILESI Notaire, SARL à SATHONAY-CAMP (69580) | 9 Avenue Félix Faure</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>greco.ph@notaires.fr</t>
+          <t>officenotarial@69214.notaires.fr</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>greco.ph@notaires.fr</t>
+          <t>officenotarial@69214.notaires.fr</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>0428299700</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>0428299700</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 Avenue des Frères Lumière 69008 LYON France</t>
+          <t>Bureau principal 9 Avenue Félix Faure 69580 SATHONAY-CAMP France</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="I193" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Sathonay-Camp</t>
         </is>
       </c>
       <c r="J193" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/lumen-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/maitre-milesi-notaire-sarl</t>
         </is>
       </c>
       <c r="K193" s="7" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:14:59</t>
+          <t>2026-08-02 08:12:15</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:08</t>
+          <t>2026-08-02 08:09:18</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:10</t>
+          <t>2026-08-02 08:09:19</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:12</t>
+          <t>2026-08-02 08:09:21</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:13</t>
+          <t>2026-08-02 08:09:22</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:15</t>
+          <t>2026-08-02 08:09:24</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:16</t>
+          <t>2026-08-02 08:09:26</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:18</t>
+          <t>2026-08-02 08:09:28</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:20</t>
+          <t>2026-08-02 08:09:30</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:22</t>
+          <t>2026-08-02 08:09:32</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:23</t>
+          <t>2026-08-02 08:09:34</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:25</t>
+          <t>2026-08-02 08:09:36</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:27</t>
+          <t>2026-08-02 08:09:37</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:29</t>
+          <t>2026-08-02 08:09:38</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:31</t>
+          <t>2026-08-02 08:09:40</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:33</t>
+          <t>2026-08-02 08:09:41</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:34</t>
+          <t>2026-08-02 08:09:43</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:36</t>
+          <t>2026-08-02 08:09:45</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:38</t>
+          <t>2026-08-02 08:09:47</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:40</t>
+          <t>2026-08-02 08:09:49</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:42</t>
+          <t>2026-08-02 08:09:51</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:43</t>
+          <t>2026-08-02 08:09:52</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:45</t>
+          <t>2026-08-02 08:09:54</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13928,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:46</t>
+          <t>2026-08-02 08:09:56</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:48</t>
+          <t>2026-08-02 08:09:57</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:50</t>
+          <t>2026-08-02 08:10:00</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:52</t>
+          <t>2026-08-02 08:10:01</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:54</t>
+          <t>2026-08-02 08:10:03</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:55</t>
+          <t>2026-08-02 08:10:05</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:57</t>
+          <t>2026-08-02 08:10:06</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:12:59</t>
+          <t>2026-08-02 08:10:08</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:01</t>
+          <t>2026-08-02 08:10:09</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:03</t>
+          <t>2026-08-02 08:10:11</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:05</t>
+          <t>2026-08-02 08:10:13</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:06</t>
+          <t>2026-08-02 08:10:15</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:09</t>
+          <t>2026-08-02 08:10:17</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:10</t>
+          <t>2026-08-02 08:10:19</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:12</t>
+          <t>2026-08-02 08:10:21</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:14</t>
+          <t>2026-08-02 08:10:23</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:15</t>
+          <t>2026-08-02 08:10:24</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:17</t>
+          <t>2026-08-02 08:10:26</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:18</t>
+          <t>2026-08-02 08:10:27</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:19</t>
+          <t>2026-08-02 08:10:29</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:21</t>
+          <t>2026-08-02 08:10:31</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:23</t>
+          <t>2026-08-02 08:10:33</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:24</t>
+          <t>2026-08-02 08:10:35</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:26</t>
+          <t>2026-08-02 08:10:37</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:27</t>
+          <t>2026-08-02 08:10:39</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:29</t>
+          <t>2026-08-02 08:10:41</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:31</t>
+          <t>2026-08-02 08:10:42</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26 08:13:34</t>
+          <t>2026-08-02 08:10:44</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:33</t>
+          <t>2026-08-16 06:30:53</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:34</t>
+          <t>2026-08-16 06:30:54</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:36</t>
+          <t>2026-08-16 06:30:56</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:38</t>
+          <t>2026-08-16 06:30:57</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:39</t>
+          <t>2026-08-16 06:30:59</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:41</t>
+          <t>2026-08-16 06:31:01</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:42</t>
+          <t>2026-08-16 06:31:03</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:43</t>
+          <t>2026-08-16 06:31:04</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:45</t>
+          <t>2026-08-16 06:31:06</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:46</t>
+          <t>2026-08-16 06:31:09</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:47</t>
+          <t>2026-08-16 06:31:11</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:48</t>
+          <t>2026-08-16 06:31:13</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:50</t>
+          <t>2026-08-16 06:31:15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:52</t>
+          <t>2026-08-16 06:31:17</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:54</t>
+          <t>2026-08-16 06:31:19</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:56</t>
+          <t>2026-08-16 06:31:22</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:57</t>
+          <t>2026-08-16 06:31:24</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:59</t>
+          <t>2026-08-16 06:31:25</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:59</t>
+          <t>2026-08-16 06:31:27</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:01</t>
+          <t>2026-08-16 06:31:28</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:03</t>
+          <t>2026-08-16 06:31:30</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:05</t>
+          <t>2026-08-16 06:31:31</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:07</t>
+          <t>2026-08-16 06:31:33</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:08</t>
+          <t>2026-08-16 06:31:35</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:10</t>
+          <t>2026-08-16 06:31:37</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:12</t>
+          <t>2026-08-16 06:31:39</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:14</t>
+          <t>2026-08-16 06:31:40</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:15</t>
+          <t>2026-08-16 06:31:43</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:17</t>
+          <t>2026-08-16 06:31:45</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:17</t>
+          <t>2026-08-16 06:31:47</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:19</t>
+          <t>2026-08-16 06:31:48</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:20</t>
+          <t>2026-08-16 06:31:50</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:22</t>
+          <t>2026-08-16 06:31:51</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:24</t>
+          <t>2026-08-16 06:31:53</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:25</t>
+          <t>2026-08-16 06:31:55</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:27</t>
+          <t>2026-08-16 06:31:56</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:29</t>
+          <t>2026-08-16 06:31:58</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:30</t>
+          <t>2026-08-16 06:32:00</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:32</t>
+          <t>2026-08-16 06:32:01</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:33</t>
+          <t>2026-08-16 06:32:03</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:47:35</t>
+          <t>2026-08-16 06:32:05</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:56</t>
+          <t>2026-08-16 06:31:21</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:14</t>
+          <t>2026-08-16 06:29:30</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:16</t>
+          <t>2026-08-16 06:29:32</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:18</t>
+          <t>2026-08-16 06:29:33</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:20</t>
+          <t>2026-08-16 06:29:35</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:21</t>
+          <t>2026-08-16 06:29:37</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:22</t>
+          <t>2026-08-16 06:29:39</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:24</t>
+          <t>2026-08-16 06:29:40</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:25</t>
+          <t>2026-08-16 06:29:42</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:26</t>
+          <t>2026-08-16 06:29:43</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:27</t>
+          <t>2026-08-16 06:29:45</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:28</t>
+          <t>2026-08-16 06:29:47</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:30</t>
+          <t>2026-08-16 06:29:48</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:32</t>
+          <t>2026-08-16 06:29:50</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:33</t>
+          <t>2026-08-16 06:29:52</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:34</t>
+          <t>2026-08-16 06:29:53</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:36</t>
+          <t>2026-08-16 06:29:55</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:37</t>
+          <t>2026-08-16 06:29:56</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:39</t>
+          <t>2026-08-16 06:29:58</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:40</t>
+          <t>2026-08-16 06:30:00</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:42</t>
+          <t>2026-08-16 06:30:02</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:43</t>
+          <t>2026-08-16 06:30:04</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:44</t>
+          <t>2026-08-16 06:30:04</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:45</t>
+          <t>2026-08-16 06:30:07</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:46</t>
+          <t>2026-08-16 06:30:08</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:48</t>
+          <t>2026-08-16 06:30:11</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:50</t>
+          <t>2026-08-16 06:30:12</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:52</t>
+          <t>2026-08-16 06:30:14</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:54</t>
+          <t>2026-08-16 06:30:15</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:55</t>
+          <t>2026-08-16 06:30:17</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:01</t>
+          <t>2026-08-16 06:30:21</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:03</t>
+          <t>2026-08-16 06:30:23</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:05</t>
+          <t>2026-08-16 06:30:27</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:07</t>
+          <t>2026-08-16 06:30:29</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:09</t>
+          <t>2026-08-16 06:30:30</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:10</t>
+          <t>2026-08-16 06:30:32</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:12</t>
+          <t>2026-08-16 06:30:34</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:14</t>
+          <t>2026-08-16 06:30:35</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:16</t>
+          <t>2026-08-16 06:30:37</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:17</t>
+          <t>2026-08-16 06:30:39</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:19</t>
+          <t>2026-08-16 06:30:41</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:20</t>
+          <t>2026-08-16 06:30:42</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:25</t>
+          <t>2026-08-16 06:30:48</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:27</t>
+          <t>2026-08-16 06:30:49</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:59</t>
+          <t>2026-08-16 06:30:19</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:22</t>
+          <t>2026-08-16 06:30:44</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:23</t>
+          <t>2026-08-16 06:30:46</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:05</t>
+          <t>2026-08-16 06:30:25</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:29</t>
+          <t>2026-08-16 06:30:51</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:46:31</t>
+          <t>2026-08-16 06:30:52</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:57</t>
+          <t>2026-08-16 06:30:18</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:50</t>
+          <t>2026-08-16 06:28:13</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:52</t>
+          <t>2026-08-16 06:28:14</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:54</t>
+          <t>2026-08-16 06:28:16</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:56</t>
+          <t>2026-08-16 06:28:18</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:57</t>
+          <t>2026-08-16 06:28:19</t>
         </is>
       </c>
     </row>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:59</t>
+          <t>2026-08-16 06:28:21</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:00</t>
+          <t>2026-08-16 06:28:22</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:02</t>
+          <t>2026-08-16 06:28:24</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:04</t>
+          <t>2026-08-16 06:28:25</t>
         </is>
       </c>
     </row>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:05</t>
+          <t>2026-08-16 06:28:27</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:08</t>
+          <t>2026-08-16 06:28:28</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7062,7 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:09</t>
+          <t>2026-08-16 06:28:30</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:11</t>
+          <t>2026-08-16 06:28:32</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:13</t>
+          <t>2026-08-16 06:28:33</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:15</t>
+          <t>2026-08-16 06:28:35</t>
         </is>
       </c>
     </row>
@@ -7310,7 +7310,7 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:17</t>
+          <t>2026-08-16 06:28:37</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:19</t>
+          <t>2026-08-16 06:28:38</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:20</t>
+          <t>2026-08-16 06:28:40</t>
         </is>
       </c>
     </row>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:22</t>
+          <t>2026-08-16 06:28:41</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:24</t>
+          <t>2026-08-16 06:28:43</t>
         </is>
       </c>
     </row>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:25</t>
+          <t>2026-08-16 06:28:44</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:26</t>
+          <t>2026-08-16 06:28:46</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:28</t>
+          <t>2026-08-16 06:28:47</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:29</t>
+          <t>2026-08-16 06:28:49</t>
         </is>
       </c>
     </row>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:32</t>
+          <t>2026-08-16 06:28:50</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7930,7 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:33</t>
+          <t>2026-08-16 06:28:52</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:35</t>
+          <t>2026-08-16 06:28:54</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:37</t>
+          <t>2026-08-16 06:28:56</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:38</t>
+          <t>2026-08-16 06:28:57</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:40</t>
+          <t>2026-08-16 06:28:59</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:42</t>
+          <t>2026-08-16 06:29:00</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:43</t>
+          <t>2026-08-16 06:29:02</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:45</t>
+          <t>2026-08-16 06:29:03</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:46</t>
+          <t>2026-08-16 06:29:05</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:48</t>
+          <t>2026-08-16 06:29:06</t>
         </is>
       </c>
     </row>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:49</t>
+          <t>2026-08-16 06:29:08</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:51</t>
+          <t>2026-08-16 06:29:08</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8666,7 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:51</t>
+          <t>2026-08-16 06:29:10</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:53</t>
+          <t>2026-08-16 06:29:12</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:55</t>
+          <t>2026-08-16 06:29:13</t>
         </is>
       </c>
     </row>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:56</t>
+          <t>2026-08-16 06:29:15</t>
         </is>
       </c>
     </row>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:44:58</t>
+          <t>2026-08-16 06:29:17</t>
         </is>
       </c>
     </row>
@@ -8976,7 +8976,7 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:00</t>
+          <t>2026-08-16 06:29:18</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:02</t>
+          <t>2026-08-16 06:29:19</t>
         </is>
       </c>
     </row>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:04</t>
+          <t>2026-08-16 06:29:20</t>
         </is>
       </c>
     </row>
@@ -9162,7 +9162,7 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:05</t>
+          <t>2026-08-16 06:29:22</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:07</t>
+          <t>2026-08-16 06:29:23</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:09</t>
+          <t>2026-08-16 06:29:25</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:11</t>
+          <t>2026-08-16 06:29:27</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:45:12</t>
+          <t>2026-08-16 06:29:28</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:31</t>
+          <t>2026-08-16 06:26:51</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:32</t>
+          <t>2026-08-16 06:26:53</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:34</t>
+          <t>2026-08-16 06:26:55</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:36</t>
+          <t>2026-08-16 06:26:56</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:37</t>
+          <t>2026-08-16 06:26:58</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:38</t>
+          <t>2026-08-16 06:26:59</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:40</t>
+          <t>2026-08-16 06:27:01</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:42</t>
+          <t>2026-08-16 06:27:02</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:44</t>
+          <t>2026-08-16 06:27:04</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:45</t>
+          <t>2026-08-16 06:27:06</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:47</t>
+          <t>2026-08-16 06:27:08</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:48</t>
+          <t>2026-08-16 06:27:09</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:50</t>
+          <t>2026-08-16 06:27:11</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:52</t>
+          <t>2026-08-16 06:27:13</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:53</t>
+          <t>2026-08-16 06:27:14</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:55</t>
+          <t>2026-08-16 06:27:15</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:56</t>
+          <t>2026-08-16 06:27:17</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:58</t>
+          <t>2026-08-16 06:27:19</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:59</t>
+          <t>2026-08-16 06:27:21</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:01</t>
+          <t>2026-08-16 06:27:22</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:03</t>
+          <t>2026-08-16 06:27:24</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:05</t>
+          <t>2026-08-16 06:27:26</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:06</t>
+          <t>2026-08-16 06:27:27</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:08</t>
+          <t>2026-08-16 06:27:29</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:10</t>
+          <t>2026-08-16 06:27:30</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:12</t>
+          <t>2026-08-16 06:27:32</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:13</t>
+          <t>2026-08-16 06:27:34</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:15</t>
+          <t>2026-08-16 06:27:35</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:16</t>
+          <t>2026-08-16 06:27:37</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:17</t>
+          <t>2026-08-16 06:27:39</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:19</t>
+          <t>2026-08-16 06:27:41</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:20</t>
+          <t>2026-08-16 06:27:42</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:22</t>
+          <t>2026-08-16 06:27:44</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:23</t>
+          <t>2026-08-16 06:27:46</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:25</t>
+          <t>2026-08-16 06:27:47</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:26</t>
+          <t>2026-08-16 06:27:49</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:28</t>
+          <t>2026-08-16 06:27:51</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:29</t>
+          <t>2026-08-16 06:27:53</t>
         </is>
       </c>
     </row>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:30</t>
+          <t>2026-08-16 06:27:54</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:33</t>
+          <t>2026-08-16 06:27:56</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:34</t>
+          <t>2026-08-16 06:27:57</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:36</t>
+          <t>2026-08-16 06:27:58</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:37</t>
+          <t>2026-08-16 06:28:00</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:39</t>
+          <t>2026-08-16 06:28:01</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:41</t>
+          <t>2026-08-16 06:28:03</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:42</t>
+          <t>2026-08-16 06:28:05</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:44</t>
+          <t>2026-08-16 06:28:06</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:45</t>
+          <t>2026-08-16 06:28:08</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:47</t>
+          <t>2026-08-16 06:28:10</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:43:49</t>
+          <t>2026-08-16 06:28:11</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:14</t>
+          <t>2026-08-16 06:25:34</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:16</t>
+          <t>2026-08-16 06:25:35</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:17</t>
+          <t>2026-08-16 06:25:36</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:19</t>
+          <t>2026-08-16 06:25:37</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:21</t>
+          <t>2026-08-16 06:25:39</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:23</t>
+          <t>2026-08-16 06:25:41</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:25</t>
+          <t>2026-08-16 06:25:42</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:27</t>
+          <t>2026-08-16 06:25:44</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:29</t>
+          <t>2026-08-16 06:25:45</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:30</t>
+          <t>2026-08-16 06:25:47</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:31</t>
+          <t>2026-08-16 06:25:49</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:33</t>
+          <t>2026-08-16 06:25:50</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:34</t>
+          <t>2026-08-16 06:25:52</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:35</t>
+          <t>2026-08-16 06:25:54</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:37</t>
+          <t>2026-08-16 06:25:55</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:39</t>
+          <t>2026-08-16 06:25:57</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:40</t>
+          <t>2026-08-16 06:25:58</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:42</t>
+          <t>2026-08-16 06:26:00</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:44</t>
+          <t>2026-08-16 06:26:01</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:45</t>
+          <t>2026-08-16 06:26:03</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:46</t>
+          <t>2026-08-16 06:26:04</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:47</t>
+          <t>2026-08-16 06:26:05</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13928,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:49</t>
+          <t>2026-08-16 06:26:07</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:51</t>
+          <t>2026-08-16 06:26:08</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:52</t>
+          <t>2026-08-16 06:26:09</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:53</t>
+          <t>2026-08-16 06:26:11</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:55</t>
+          <t>2026-08-16 06:26:12</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:56</t>
+          <t>2026-08-16 06:26:14</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:58</t>
+          <t>2026-08-16 06:26:15</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:41:59</t>
+          <t>2026-08-16 06:26:17</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:01</t>
+          <t>2026-08-16 06:26:19</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:02</t>
+          <t>2026-08-16 06:26:21</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:03</t>
+          <t>2026-08-16 06:26:23</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:05</t>
+          <t>2026-08-16 06:26:25</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:06</t>
+          <t>2026-08-16 06:26:27</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:08</t>
+          <t>2026-08-16 06:26:29</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:09</t>
+          <t>2026-08-16 06:26:31</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:11</t>
+          <t>2026-08-16 06:26:32</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:13</t>
+          <t>2026-08-16 06:26:33</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:14</t>
+          <t>2026-08-16 06:26:35</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:16</t>
+          <t>2026-08-16 06:26:36</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:17</t>
+          <t>2026-08-16 06:26:37</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:19</t>
+          <t>2026-08-16 06:26:39</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:20</t>
+          <t>2026-08-16 06:26:40</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:22</t>
+          <t>2026-08-16 06:26:42</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:23</t>
+          <t>2026-08-16 06:26:43</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:24</t>
+          <t>2026-08-16 06:26:45</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:26</t>
+          <t>2026-08-16 06:26:47</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:27</t>
+          <t>2026-08-16 06:26:48</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09 06:42:29</t>
+          <t>2026-08-16 06:26:50</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -692,7 +692,7 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:53</t>
+          <t>2026-08-23 06:32:29</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:54</t>
+          <t>2026-08-23 06:32:30</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:56</t>
+          <t>2026-08-23 06:32:32</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:57</t>
+          <t>2026-08-23 06:32:33</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:59</t>
+          <t>2026-08-23 06:32:35</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:01</t>
+          <t>2026-08-23 06:32:36</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:03</t>
+          <t>2026-08-23 06:32:38</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:04</t>
+          <t>2026-08-23 06:32:39</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:06</t>
+          <t>2026-08-23 06:32:41</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:09</t>
+          <t>2026-08-23 06:32:43</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:11</t>
+          <t>2026-08-23 06:32:44</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:13</t>
+          <t>2026-08-23 06:32:45</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:15</t>
+          <t>2026-08-23 06:32:47</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:17</t>
+          <t>2026-08-23 06:32:48</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:19</t>
+          <t>2026-08-23 06:32:50</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:22</t>
+          <t>2026-08-23 06:32:53</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:24</t>
+          <t>2026-08-23 06:32:55</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:25</t>
+          <t>2026-08-23 06:32:56</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:27</t>
+          <t>2026-08-23 06:32:58</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:28</t>
+          <t>2026-08-23 06:32:59</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:30</t>
+          <t>2026-08-23 06:33:01</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:31</t>
+          <t>2026-08-23 06:33:03</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:33</t>
+          <t>2026-08-23 06:33:05</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:35</t>
+          <t>2026-08-23 06:33:05</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:37</t>
+          <t>2026-08-23 06:33:07</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:39</t>
+          <t>2026-08-23 06:33:09</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:40</t>
+          <t>2026-08-23 06:33:11</t>
         </is>
       </c>
     </row>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:43</t>
+          <t>2026-08-23 06:33:13</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:45</t>
+          <t>2026-08-23 06:33:14</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:47</t>
+          <t>2026-08-23 06:33:16</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:48</t>
+          <t>2026-08-23 06:33:18</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:50</t>
+          <t>2026-08-23 06:33:20</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:51</t>
+          <t>2026-08-23 06:33:21</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:53</t>
+          <t>2026-08-23 06:33:23</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:55</t>
+          <t>2026-08-23 06:33:25</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:56</t>
+          <t>2026-08-23 06:33:27</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:58</t>
+          <t>2026-08-23 06:33:28</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2978,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:32:00</t>
+          <t>2026-08-23 06:33:29</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:32:01</t>
+          <t>2026-08-23 06:33:31</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:32:03</t>
+          <t>2026-08-23 06:33:31</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:32:05</t>
+          <t>2026-08-23 06:33:33</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:31:21</t>
+          <t>2026-08-23 06:32:51</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:30</t>
+          <t>2026-08-23 06:31:09</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:32</t>
+          <t>2026-08-23 06:31:11</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:33</t>
+          <t>2026-08-23 06:31:12</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:35</t>
+          <t>2026-08-23 06:31:14</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:37</t>
+          <t>2026-08-23 06:31:15</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:39</t>
+          <t>2026-08-23 06:31:17</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:40</t>
+          <t>2026-08-23 06:31:19</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:42</t>
+          <t>2026-08-23 06:31:20</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:43</t>
+          <t>2026-08-23 06:31:22</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:45</t>
+          <t>2026-08-23 06:31:23</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:47</t>
+          <t>2026-08-23 06:31:25</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:48</t>
+          <t>2026-08-23 06:31:26</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:50</t>
+          <t>2026-08-23 06:31:28</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:52</t>
+          <t>2026-08-23 06:31:31</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:53</t>
+          <t>2026-08-23 06:31:32</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:55</t>
+          <t>2026-08-23 06:31:34</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:56</t>
+          <t>2026-08-23 06:31:36</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:58</t>
+          <t>2026-08-23 06:31:37</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:00</t>
+          <t>2026-08-23 06:31:39</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:02</t>
+          <t>2026-08-23 06:31:40</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:04</t>
+          <t>2026-08-23 06:31:42</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:04</t>
+          <t>2026-08-23 06:31:44</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:07</t>
+          <t>2026-08-23 06:31:46</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4706,7 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:08</t>
+          <t>2026-08-23 06:31:48</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4768,7 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:11</t>
+          <t>2026-08-23 06:31:50</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:12</t>
+          <t>2026-08-23 06:31:50</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:14</t>
+          <t>2026-08-23 06:31:52</t>
         </is>
       </c>
     </row>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:15</t>
+          <t>2026-08-23 06:31:53</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:17</t>
+          <t>2026-08-23 06:31:55</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:21</t>
+          <t>2026-08-23 06:32:00</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:23</t>
+          <t>2026-08-23 06:32:02</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:27</t>
+          <t>2026-08-23 06:32:05</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:29</t>
+          <t>2026-08-23 06:32:07</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:30</t>
+          <t>2026-08-23 06:32:09</t>
         </is>
       </c>
     </row>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:32</t>
+          <t>2026-08-23 06:32:10</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:34</t>
+          <t>2026-08-23 06:32:12</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:35</t>
+          <t>2026-08-23 06:32:14</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:37</t>
+          <t>2026-08-23 06:32:15</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:39</t>
+          <t>2026-08-23 06:32:16</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:41</t>
+          <t>2026-08-23 06:32:18</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:42</t>
+          <t>2026-08-23 06:32:20</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:48</t>
+          <t>2026-08-23 06:32:24</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:49</t>
+          <t>2026-08-23 06:32:25</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:19</t>
+          <t>2026-08-23 06:31:59</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:44</t>
+          <t>2026-08-23 06:32:21</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:46</t>
+          <t>2026-08-23 06:32:22</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:25</t>
+          <t>2026-08-23 06:32:03</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:51</t>
+          <t>2026-08-23 06:32:27</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:52</t>
+          <t>2026-08-23 06:32:28</t>
         </is>
       </c>
     </row>
@@ -6318,39 +6318,39 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:30:18</t>
+          <t>2026-08-23 06:31:57</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MARIOTTE Stéphanie à LYON (69006) | 10 Boulevard Jules Favre</t>
+          <t>Office notarial Office Notarial des Jacobins, SAS à LYON (69002) | 8 place des Jacobins</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>stephanie.mariotte@notaires.fr</t>
+          <t>office.jacobins.lyon@69004.notaires.fr</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>stephanie.mariotte@notaires.fr</t>
+          <t>office.jacobins.lyon@69004.notaires.fr</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>0481060795</t>
+          <t>0478371744</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>0481060795</t>
+          <t>0478371744</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 Boulevard Jules Favre 69006 LYON France</t>
+          <t>Bureau principal 8 place des Jacobins 69002 LYON France</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mariotte-stephanie</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-des-jacobins-sas</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
@@ -6380,39 +6380,39 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:13</t>
+          <t>2026-08-23 06:30:20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MATA Victoria à LYON (69008) | 310 Avenue Berthelot</t>
+          <t>Office notarial OFFICE NOTARIAL DU PAYS ARBRESLOIS, SELARL à L'ARBRESLE (69210) | 54, rue Claude Terrasse</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>victoria.mata@notaires.fr</t>
+          <t>office.larbresle@onpa.notaires.fr</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>victoria.mata@notaires.fr</t>
+          <t>office.larbresle@onpa.notaires.fr</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>0472780290</t>
+          <t>0474010014</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>0472780290</t>
+          <t>0474010014</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 310 Avenue Berthelot 69008 LYON France</t>
+          <t>Bureau principal 54, rue Claude Terrasse 69210 L'ARBRESLE France</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>L'arbresle</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mata-victoria</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-du-pays-arbreslois-selarl</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -6442,39 +6442,39 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:14</t>
+          <t>2026-08-23 06:30:22</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MAUGAIN NOTAIRES, SELARL à LYON (69003) | 34 cours Lafayette</t>
+          <t>Office notarial OFFICE ROOSEVELT et associés, SELARL à LYON (69006) | 24 Cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>bertram.julienne@notaires.fr</t>
+          <t>scp.bronnert@notaires.fr</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>bertram.julienne@notaires.fr</t>
+          <t>scp.bronnert@notaires.fr</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>0472130397</t>
+          <t>0472838080</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>0472130397</t>
+          <t>0472838080</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 34 cours Lafayette 69003 LYON France</t>
+          <t>Bureau principal 24 Cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/maugain-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/office-roosevelt-et-associes-selarl</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -6504,39 +6504,39 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:16</t>
+          <t>2026-08-23 06:30:23</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MERMET Pierre à LIMAS (69400) | 84 rue Henri Dépagneux</t>
+          <t>Office notarial ONPC NOTAIRES, SELARL à LYON (69006) | 58 rue Tête d'Or</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>pierre.mermet@notaires.fr</t>
+          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>pierre.mermet@notaires.fr</t>
+          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>0474045153</t>
+          <t>0481098330</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>0474045153</t>
+          <t>0481098330</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 84 rue Henri Dépagneux 69400 LIMAS France</t>
+          <t>Bureau principal 58 rue Tête d'Or 69006 LYON France</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>Limas</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mermet-pierre</t>
+          <t>https://www.notaires.fr/fr/office/onpc-notaires-selarl</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -6566,39 +6566,39 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:18</t>
+          <t>2026-08-23 06:30:25</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MESSERI Aurore à LYON (69003) | 6 cours de la Liberté</t>
+          <t>Office notarial PARISET, Notaire, SARL à LYON (69001) | 2 rue de Provence</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>aurore.messeri@notaires.fr</t>
+          <t>scp.paillard-pariset@notaires.fr</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>aurore.messeri@notaires.fr</t>
+          <t>scp.paillard-pariset@notaires.fr</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>0481061360</t>
+          <t>0472982798</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>0481061360</t>
+          <t>0472982798</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 6 cours de la Liberté 69003 LYON France</t>
+          <t>Bureau principal 2 rue de Provence 69001 LYON France</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/messeri-aurore</t>
+          <t>https://www.notaires.fr/fr/office/pariset-notaire-sarl</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -6628,39 +6628,39 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:19</t>
+          <t>2026-08-23 06:30:26</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MONTEL Hélène à VERNAISON (69390) | 336 rue de la Fée des Eaux</t>
+          <t>Office notarial PARTOUCHE Sébastien à LISSIEU (69380) | 101 Route Nationale 6</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>h.montel@notaires.fr</t>
+          <t>sebastien.partouche@notaires.fr</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>h.montel@notaires.fr</t>
+          <t>sebastien.partouche@notaires.fr</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>0482531832</t>
+          <t>0472599128</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>0482531832</t>
+          <t>0472599128</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 336 rue de la Fée des Eaux 69390 VERNAISON France</t>
+          <t>Bureau principal 101 Route Nationale 6 69380 LISSIEU France</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Vernaison</t>
+          <t>Lissieu</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/montel-helene</t>
+          <t>https://www.notaires.fr/fr/office/partouche-sebastien</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
@@ -6690,39 +6690,39 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:21</t>
+          <t>2026-08-23 06:30:27</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MOREL Laetitia à LYON (69003) | 127 cours du Docteur Long</t>
+          <t>Office notarial PAUL &amp; associés – Notaires Lyon, SELAS à LYON (69009) | 28 rue Joannès Carret</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>morel.laetitia@notaires.fr</t>
+          <t>corinne.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>morel.laetitia@notaires.fr</t>
+          <t>corinne.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>0481061095</t>
+          <t>0412054740</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>0481061095</t>
+          <t>0412054740</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 127 cours du Docteur Long 69003 LYON France</t>
+          <t>Bureau principal 28 rue Joannès Carret 69009 LYON France</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/morel-laetitia</t>
+          <t>https://www.notaires.fr/fr/office/paul-associes-notaires-lyon-selas</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -6752,39 +6752,39 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:22</t>
+          <t>2026-08-23 06:30:29</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MURANA-CHARLUET Raphaëlle à SAINT-DIDIER-AU-MONT-D'OR (69370) | 11 rue Voie Lactée</t>
+          <t>Office notarial PCMV NOTAIRES, SARL à LYON (69004) | 18/19 Place de la Croix Rousse</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>r.murana@notaires.fr</t>
+          <t>office@pcmv.notaires.fr</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>r.murana@notaires.fr</t>
+          <t>office@pcmv.notaires.fr</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>0485680145</t>
+          <t>0437408084</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>0485680145</t>
+          <t>0437408084</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 11 rue Voie Lactée 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
+          <t>Bureau principal 18/19 Place de la Croix Rousse 69004 LYON France</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Saint-Didier-Au-Mont-D'or</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/murana-charluet-raphaelle</t>
+          <t>https://www.notaires.fr/fr/office/pcmv-notaires-sarl</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
@@ -6814,39 +6814,31 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:24</t>
+          <t>2026-08-23 06:30:31</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MURAT Marie-Pierre à VILLEURBANNE (69100) | 109 Cours Emile Zola</t>
+          <t>Office notarial PERRAUD &amp; Associés - Notaires, SAS à LYON (69003) | 19 boulevard Eugène Deruelle</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>office.murat@notaires.fr</t>
+          <t>perraud.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>office.murat@notaires.fr</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>0437431922</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>0437431922</t>
-        </is>
-      </c>
+          <t>perraud.lyon@notaires.fr</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr"/>
+      <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 109 Cours Emile Zola 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 19 boulevard Eugène Deruelle 69003 LYON France</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -6861,12 +6853,12 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/murat-marie-pierre</t>
+          <t>https://www.notaires.fr/fr/office/perraud-associes-notaires-sas-0</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -6876,39 +6868,39 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:25</t>
+          <t>2026-08-23 06:30:32</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NARDINI Magali à CHAZAY-D'AZERGUES (69380) | 9 rue Marius Berliet</t>
+          <t>Office notarial PESSIA Faustine à DOMMARTIN (69380) | 1702 route des Bois</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>office.nardini@notaires.fr</t>
+          <t>faustine.pessia@69072.notaires.fr</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>office.nardini@notaires.fr</t>
+          <t>faustine.pessia@69072.notaires.fr</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>04.86.11.05.15</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>04.86.11.05.15</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue Marius Berliet 69380 CHAZAY-D'AZERGUES France</t>
+          <t>Bureau principal 1702 route des Bois 69380 DOMMARTIN France</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -6923,12 +6915,12 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Chazay-D'azergues</t>
+          <t>Dommartin</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/nardini-magali</t>
+          <t>https://www.notaires.fr/fr/office/pessia-faustine</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr">
@@ -6938,39 +6930,39 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:27</t>
+          <t>2026-08-23 06:30:34</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NICOLLE et associés à LYON (69003) | 90 rue Paul Bert</t>
+          <t>Office notarial PICOT Laura à LYON (69006) | 63 rue Boileau</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>christian.nicolle@notaires.fr</t>
+          <t>laura.picot@69212.notaires.fr</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>christian.nicolle@notaires.fr</t>
+          <t>laura.picot@69212.notaires.fr</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>0492309230</t>
+          <t>0478133758</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>0492309230</t>
+          <t>0478133758</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 90 rue Paul Bert 69003 LYON France</t>
+          <t>Bureau principal 63 rue Boileau 69006 LYON France</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6990,7 +6982,7 @@
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/nicolle-et-associes-0</t>
+          <t>https://www.notaires.fr/fr/office/picot-laura</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -7000,39 +6992,39 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:28</t>
+          <t>2026-08-23 06:30:36</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOHARET Françoise à LYON (69007) | 200 AVENUE JEAN JAURES</t>
+          <t>Office notarial PROUVOST-CLAEYS, SAS à associé unique à L'ARBRESLE (69210) | 193 Route de Sain-Bel</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>office.noharet@notaires.fr</t>
+          <t>louise.prouvost@69209.notaires.fr</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>office.noharet@notaires.fr</t>
+          <t>louise.prouvost@69209.notaires.fr</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>0437376850</t>
+          <t>0428299066</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>0437376850</t>
+          <t>0428299066</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 200 AVENUE JEAN JAURES 69007 LYON France</t>
+          <t>Bureau principal 193 Route de Sain-Bel 69210 L'ARBRESLE France</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -7047,12 +7039,12 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>L'arbresle</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/noharet-francoise</t>
+          <t>https://www.notaires.fr/fr/office/prouvost-claeys-sas-associe-unique</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
@@ -7062,39 +7054,39 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:30</t>
+          <t>2026-08-23 06:30:38</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOT’ACTES MARCY à MARCY (69480) | 20, Rue de la Tour</t>
+          <t>Office notarial RAY et associé, SELARL à SAINT-FONS (69190) | 1 Avenue Jean Jaurès</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>renaud.fontaine@69169.notaires.fr</t>
+          <t>ray.sassard@notaires.fr</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>renaud.fontaine@69169.notaires.fr</t>
+          <t>ray.sassard@notaires.fr</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>0437552285</t>
+          <t>0478700047</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>0437552285</t>
+          <t>0478700047</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 20, Rue de la Tour 69480 MARCY France</t>
+          <t>Bureau principal 1 Avenue Jean Jaurès 69190 SAINT-FONS France</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -7109,12 +7101,12 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Marcy</t>
+          <t>Saint-Fons</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notactes-marcy</t>
+          <t>https://www.notaires.fr/fr/office/ray-et-associe-selarl</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr">
@@ -7124,39 +7116,39 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:32</t>
+          <t>2026-08-23 06:30:39</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOTAEM et associés à SAINT-CYR-AU-MONT-D'OR (69450) | 1 rue Reynier</t>
+          <t>Office notarial REAL LEX Notaires à CRAPONNE (69290) | 123 AVENUE PIERRE DUMOND</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>notaem@notaem.notaires.fr</t>
+          <t>office69066.craponne@notaires.fr</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>notaem@notaem.notaires.fr</t>
+          <t>office69066.craponne@notaires.fr</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>0478472483</t>
+          <t>0478578039</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>0478472483</t>
+          <t>0478578039</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Reynier 69450 SAINT-CYR-AU-MONT-D'OR France</t>
+          <t>Bureau principal 123 AVENUE PIERRE DUMOND 69290 CRAPONNE France</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -7171,12 +7163,12 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>Saint-Cyr-Au-Mont-D'or</t>
+          <t>Craponne</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notaem-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/real-lex-notaires</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
@@ -7186,39 +7178,39 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:33</t>
+          <t>2026-08-23 06:30:41</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOTAIRES GAMBETTA à VILLEFRANCHE-SUR-SAÔNE (69400) | 257 rue Boiron</t>
+          <t>Office notarial REBOTIER PERET LEVRAULT ET MERLE NOTAIRES ASSOCIES, SELARL à LYON (69009) | 2 boulevard Antoine de Saint Exupéry</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>secretariat@etudegambetta.notaires.fr</t>
+          <t>notaires.vaise@notaires.fr</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>secretariat@etudegambetta.notaires.fr</t>
+          <t>notaires.vaise@notaires.fr</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>0474029910</t>
+          <t>0478646749</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>0474029910</t>
+          <t>0478646749</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 257 rue Boiron 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 2 boulevard Antoine de Saint Exupéry 69009 LYON France</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -7233,12 +7225,12 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notaires-gambetta</t>
+          <t>https://www.notaires.fr/fr/office/rebotier-peret-levrault-et-merle-notaires-associes-selarl</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -7248,39 +7240,39 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:35</t>
+          <t>2026-08-23 06:30:43</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOTARA à LYON (69007) | 152 Grande Rue de la Guillotière</t>
+          <t>Office notarial RENETEAU Anaïs à CHAPONOST (69630) | 1 Route des Troques</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>notara.lyon@notaires.fr</t>
+          <t>anais.reneteau@reneteau.notaires.fr</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>notara.lyon@notaires.fr</t>
+          <t>anais.reneteau@reneteau.notaires.fr</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>0983211434</t>
+          <t>0478563572</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>0983211434</t>
+          <t>0478563572</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 152 Grande Rue de la Guillotière 69007 LYON France</t>
+          <t>Bureau principal 1 Route des Troques 69630 CHAPONOST France</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -7295,12 +7287,12 @@
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chaponost</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notara</t>
+          <t>https://www.notaires.fr/fr/office/reneteau-anais</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -7310,39 +7302,39 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:37</t>
+          <t>2026-08-23 06:30:44</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ODO, notaire à THIZY-LES-BOURGS (69240) | 47 RUE JEAN JAURES</t>
+          <t>Office notarial REY Karyne à LYON (69002) | 3 rue Victor Hugo</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>notaires.thizy@notaires.fr</t>
+          <t>etude.rey@notaires.fr</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>notaires.thizy@notaires.fr</t>
+          <t>etude.rey@notaires.fr</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>0474640048</t>
+          <t>0472162590</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>0474640048</t>
+          <t>0472162590</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 47 RUE JEAN JAURES 69240 THIZY-LES-BOURGS France</t>
+          <t>Bureau principal 3 rue Victor Hugo 69002 LYON France</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -7357,12 +7349,12 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Thizy-Les-Bourgs</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/odo-notaire</t>
+          <t>https://www.notaires.fr/fr/office/rey-karyne</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -7372,39 +7364,39 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:38</t>
+          <t>2026-08-23 06:30:45</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DE PRESSENSE, SELARL à VILLEURBANNE (69100) | 46 rue Francis de Pressensé</t>
+          <t>Office notarial ROBIN Axel à LYON (69003) | 123 cours Albert Thomas</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>helene.geraud@notaires.fr</t>
+          <t>etude@69047.notaires.fr</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>helene.geraud@notaires.fr</t>
+          <t>etude@69047.notaires.fr</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>0437482561</t>
+          <t>0449232420</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>0437482561</t>
+          <t>0449232420</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 46 rue Francis de Pressensé 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 123 cours Albert Thomas 69003 LYON France</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -7419,12 +7411,12 @@
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-de-pressense-selarl</t>
+          <t>https://www.notaires.fr/fr/office/robin-axel</t>
         </is>
       </c>
       <c r="K111" s="7" t="inlineStr">
@@ -7434,39 +7426,39 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:40</t>
+          <t>2026-08-23 06:30:47</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DES CHARPENNES-VILLEURBANNE, SELARL à VILLEURBANNE (69100) | 50 A Cours Emile Zola</t>
+          <t>Office notarial ROCHELOIS LYON, SELAS à LYON (69003) | 10-12 boulevard Marius Vivier Merle</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>oncv@69136.notaires.fr</t>
+          <t>contact@rocheloislyon.notaires.fr</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>oncv@69136.notaires.fr</t>
+          <t>contact@rocheloislyon.notaires.fr</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>0472759396</t>
+          <t>0487658201</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>0472759396</t>
+          <t>0487658201</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 50 A Cours Emile Zola 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 10-12 boulevard Marius Vivier Merle 69003 LYON France</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -7481,12 +7473,12 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-des-charpennes-villeurbanne-selarl</t>
+          <t>https://www.notaires.fr/fr/office/rochelois-lyon-selas</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -7496,39 +7488,39 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:41</t>
+          <t>2026-08-23 06:30:48</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Office notarial Office Notarial des Jacobins, SAS à LYON (69002) | 8 place des Jacobins</t>
+          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à LYON (69003) | 40 Rue Antoine Charial</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>office.jacobins.lyon@69004.notaires.fr</t>
+          <t>corine.mussio@notaires.fr</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>office.jacobins.lyon@69004.notaires.fr</t>
+          <t>corine.mussio@notaires.fr</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>0478371744</t>
+          <t>0472459539</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>0478371744</t>
+          <t>0472459539</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 8 place des Jacobins 69002 LYON France</t>
+          <t>Bureau principal 40 Rue Antoine Charial 69003 LYON France</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -7548,7 +7540,7 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-des-jacobins-sas</t>
+          <t>https://www.notaires.fr/fr/office/rostaing-mussio-et-associee-selarl-0</t>
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr">
@@ -7558,39 +7550,39 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:43</t>
+          <t>2026-08-23 06:30:49</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DU PAYS ARBRESLOIS, SELARL à L'ARBRESLE (69210) | 54, rue Claude Terrasse</t>
+          <t>Office notarial RUCHON Edouard à LYON (69005) | 60 avenue du Point du Jour</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>office.larbresle@onpa.notaires.fr</t>
+          <t>edouard.ruchon@notaires.fr</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>office.larbresle@onpa.notaires.fr</t>
+          <t>edouard.ruchon@notaires.fr</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>0474010014</t>
+          <t>0472544808</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>0474010014</t>
+          <t>0472544808</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 54, rue Claude Terrasse 69210 L'ARBRESLE France</t>
+          <t>Bureau principal 60 avenue du Point du Jour 69005 LYON France</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -7605,12 +7597,12 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>L'arbresle</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-du-pays-arbreslois-selarl</t>
+          <t>https://www.notaires.fr/fr/office/ruchon-edouard</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -7620,39 +7612,39 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:44</t>
+          <t>2026-08-23 06:30:50</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE ROOSEVELT et associés, SELARL à LYON (69006) | 24 Cours Franklin Roosevelt</t>
+          <t>Office notarial S2R NOTAIRES CONSEILS, SELARL à LYON (69006) | 50 boulevard des Belges</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>scp.bronnert@notaires.fr</t>
+          <t>simon.reboul@69225.notaires.fr</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>scp.bronnert@notaires.fr</t>
+          <t>simon.reboul@69225.notaires.fr</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>0472838080</t>
+          <t>0437479982</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>0472838080</t>
+          <t>0437479982</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 24 Cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 50 boulevard des Belges 69006 LYON France</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
@@ -7672,7 +7664,7 @@
       </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-roosevelt-et-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/s2r-notaires-conseils-selarl</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr">
@@ -7682,39 +7674,39 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:46</t>
+          <t>2026-08-23 06:30:52</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ONPC NOTAIRES, SELARL à LYON (69006) | 58 rue Tête d'Or</t>
+          <t>Office notarial SALAGNAT Frédéric à CHASSIEU (69680) | 56 route de Genas</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
+          <t>salagnat@notaires.fr</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
+          <t>salagnat@notaires.fr</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>0481098330</t>
+          <t>0472797470</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>0481098330</t>
+          <t>0472797470</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 58 rue Tête d'Or 69006 LYON France</t>
+          <t>Bureau principal 56 route de Genas 69680 CHASSIEU France</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -7729,12 +7721,12 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chassieu</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/onpc-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/salagnat-frederic</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -7744,39 +7736,39 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:47</t>
+          <t>2026-08-23 06:30:54</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PARISET, Notaire, SARL à LYON (69001) | 2 rue de Provence</t>
+          <t>Office notarial SALICHON &amp; ASSOCIES, SARL à LYON (69006) | 3 Cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>scp.paillard-pariset@notaires.fr</t>
+          <t>salichonetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>scp.paillard-pariset@notaires.fr</t>
+          <t>salichonetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>0472982798</t>
+          <t>0478931098</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>0472982798</t>
+          <t>0478931098</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 rue de Provence 69001 LYON France</t>
+          <t>Bureau principal 3 Cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -7796,7 +7788,7 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pariset-notaire-sarl</t>
+          <t>https://www.notaires.fr/fr/office/salichon-associes-sarl</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
@@ -7806,39 +7798,39 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:49</t>
+          <t>2026-08-23 06:30:56</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PARTOUCHE Sébastien à LISSIEU (69380) | 101 Route Nationale 6</t>
+          <t>Office notarial SARL à associé unique GONDRAN, notaire associée à BELLEVILLE (69220) | 19 rue des Remparts</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>sebastien.partouche@notaires.fr</t>
+          <t>anne.gondran@69248.notaires.fr</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>sebastien.partouche@notaires.fr</t>
+          <t>anne.gondran@69248.notaires.fr</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>0472599128</t>
+          <t>04 87 01 02 10</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>0472599128</t>
+          <t>04 87 01 02 10</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 101 Route Nationale 6 69380 LISSIEU France</t>
+          <t>Bureau principal 19 rue des Remparts 69220 BELLEVILLE France</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -7853,12 +7845,12 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Lissieu</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/partouche-sebastien</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-gondran-notaire-associee</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
@@ -7868,39 +7860,39 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:50</t>
+          <t>2026-08-23 06:30:58</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PAUL &amp; associés – Notaires Lyon, SELAS à LYON (69009) | 28 rue Joannès Carret</t>
+          <t>Office notarial SARL à associé unique Notaires du Promenoir à VILLEFRANCHE-SUR-SAÔNE (69400) | 61 rue d'Anse</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>corinne.nicolle@notaires.fr</t>
+          <t>etude@promenoir.notaires.fr</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>corinne.nicolle@notaires.fr</t>
+          <t>etude@promenoir.notaires.fr</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>0412054740</t>
+          <t>0474654500</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>0412054740</t>
+          <t>0474654500</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 28 rue Joannès Carret 69009 LYON France</t>
+          <t>Bureau principal 61 rue d'Anse 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -7915,12 +7907,12 @@
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/paul-associes-notaires-lyon-selas</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-notaires-du-promenoir</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
@@ -7930,39 +7922,39 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:52</t>
+          <t>2026-08-23 06:31:00</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PCMV NOTAIRES, SARL à LYON (69004) | 18/19 Place de la Croix Rousse</t>
+          <t>Office notarial SARL à associé unique OFFICE NOTARIAL DE LA TABLE DE PIERRE à FRANCHEVILLE (69340) | 26 Avenue de la Table de Pierre</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>office@pcmv.notaires.fr</t>
+          <t>christelle.farce@69220.notaires.fr</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>office@pcmv.notaires.fr</t>
+          <t>christelle.farce@69220.notaires.fr</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>0437408084</t>
+          <t>0437202524</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>0437408084</t>
+          <t>0437202524</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 18/19 Place de la Croix Rousse 69004 LYON France</t>
+          <t>Bureau principal 26 Avenue de la Table de Pierre 69340 FRANCHEVILLE France</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -7977,12 +7969,12 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Francheville</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pcmv-notaires-sarl</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-office-notarial-de-la-table-de-pierre</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -7992,31 +7984,39 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:54</t>
+          <t>2026-08-23 06:31:01</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PERRAUD &amp; Associés - Notaires, SAS à LYON (69003) | 19 boulevard Eugène Deruelle</t>
+          <t>Office notarial SARL à associée unique NOTAIRE VALLE D'AZERGUES à LAMURE-SUR-AZERGUES (69870) | 10 impasse Chavanet</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>perraud.lyon@notaires.fr</t>
+          <t>office@69095.notaires.fr</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>perraud.lyon@notaires.fr</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr"/>
-      <c r="E121" s="7" t="inlineStr"/>
+          <t>office@69095.notaires.fr</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>0474030522</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>0474030522</t>
+        </is>
+      </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 19 boulevard Eugène Deruelle 69003 LYON France</t>
+          <t>Bureau principal 10 impasse Chavanet 69870 LAMURE-SUR-AZERGUES France</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lamure-Sur-Azergues</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/perraud-associes-notaires-sas-0</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associee-unique-notaire-valle-dazergues</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr">
@@ -8046,39 +8046,39 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:56</t>
+          <t>2026-08-23 06:31:03</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PESSIA Faustine à DOMMARTIN (69380) | 1702 route des Bois</t>
+          <t>Office notarial SARL CADRAN Notaires Conseils à LYON (69007) | 75 rue Chevreul</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>faustine.pessia@69072.notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>faustine.pessia@69072.notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0437261144</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0437261144</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1702 route des Bois 69380 DOMMARTIN France</t>
+          <t>Bureau principal 75 rue Chevreul 69007 LYON France</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Dommartin</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pessia-faustine</t>
+          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -8108,39 +8108,39 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:57</t>
+          <t>2026-08-23 06:31:05</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PICOT Laura à LYON (69006) | 63 rue Boileau</t>
+          <t>Office notarial SARL CADRAN Notaires Conseils à TASSIN-LA-DEMI-LUNE (69160) | 3 avenue de Lauterbourg</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>laura.picot@69212.notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>laura.picot@69212.notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>0478133758</t>
+          <t>0478343602</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>0478133758</t>
+          <t>0478343602</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 63 rue Boileau 69006 LYON France</t>
+          <t>Bureau principal 3 avenue de Lauterbourg 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/picot-laura</t>
+          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils-0</t>
         </is>
       </c>
       <c r="K123" s="7" t="inlineStr">
@@ -8170,39 +8170,39 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:59</t>
+          <t>2026-08-23 06:31:06</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PROUVOST-CLAEYS, SAS à associé unique à L'ARBRESLE (69210) | 193 Route de Sain-Bel</t>
+          <t>Office notarial SARL CHAINE ET ASSOCIES NOTAIRES à LYON (69006) | 139 rue Vendôme</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>louise.prouvost@69209.notaires.fr</t>
+          <t>etude.chaine@notaires.fr</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>louise.prouvost@69209.notaires.fr</t>
+          <t>etude.chaine@notaires.fr</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>0428299066</t>
+          <t>0472757600</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>0428299066</t>
+          <t>0472757600</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 193 Route de Sain-Bel 69210 L'ARBRESLE France</t>
+          <t>Bureau principal 139 rue Vendôme 69006 LYON France</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>L'arbresle</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/prouvost-claeys-sas-associe-unique</t>
+          <t>https://www.notaires.fr/fr/office/sarl-chaine-et-associes-notaires</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -8232,39 +8232,39 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:00</t>
+          <t>2026-08-23 06:31:07</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Office notarial RAY et associé, SELARL à SAINT-FONS (69190) | 1 Avenue Jean Jaurès</t>
+          <t>Office notarial MARIOTTE Stéphanie à LYON (69006) | 10 Boulevard Jules Favre</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>ray.sassard@notaires.fr</t>
+          <t>stephanie.mariotte@notaires.fr</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>ray.sassard@notaires.fr</t>
+          <t>stephanie.mariotte@notaires.fr</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>0478700047</t>
+          <t>0481060795</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>0478700047</t>
+          <t>0481060795</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Avenue Jean Jaurès 69190 SAINT-FONS France</t>
+          <t>Bureau principal 10 Boulevard Jules Favre 69006 LYON France</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Saint-Fons</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/ray-et-associe-selarl</t>
+          <t>https://www.notaires.fr/fr/office/mariotte-stephanie</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr">
@@ -8294,39 +8294,39 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:02</t>
+          <t>2026-08-23 06:29:47</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Office notarial REAL LEX Notaires à CRAPONNE (69290) | 123 AVENUE PIERRE DUMOND</t>
+          <t>Office notarial MATA Victoria à LYON (69008) | 310 Avenue Berthelot</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>office69066.craponne@notaires.fr</t>
+          <t>victoria.mata@notaires.fr</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>office69066.craponne@notaires.fr</t>
+          <t>victoria.mata@notaires.fr</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>0478578039</t>
+          <t>0472780290</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>0478578039</t>
+          <t>0472780290</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 123 AVENUE PIERRE DUMOND 69290 CRAPONNE France</t>
+          <t>Bureau principal 310 Avenue Berthelot 69008 LYON France</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Craponne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/real-lex-notaires</t>
+          <t>https://www.notaires.fr/fr/office/mata-victoria</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -8356,39 +8356,39 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:03</t>
+          <t>2026-08-23 06:29:49</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Office notarial REBOTIER PERET LEVRAULT ET MERLE NOTAIRES ASSOCIES, SELARL à LYON (69009) | 2 boulevard Antoine de Saint Exupéry</t>
+          <t>Office notarial MAUGAIN NOTAIRES, SELARL à LYON (69003) | 34 cours Lafayette</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>notaires.vaise@notaires.fr</t>
+          <t>bertram.julienne@notaires.fr</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>notaires.vaise@notaires.fr</t>
+          <t>bertram.julienne@notaires.fr</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>0478646749</t>
+          <t>0472130397</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>0478646749</t>
+          <t>0472130397</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 boulevard Antoine de Saint Exupéry 69009 LYON France</t>
+          <t>Bureau principal 34 cours Lafayette 69003 LYON France</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rebotier-peret-levrault-et-merle-notaires-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/maugain-notaires-selarl</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
@@ -8418,39 +8418,39 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:05</t>
+          <t>2026-08-23 06:29:50</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Office notarial RENETEAU Anaïs à CHAPONOST (69630) | 1 Route des Troques</t>
+          <t>Office notarial MERMET Pierre à LIMAS (69400) | 84 rue Henri Dépagneux</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>anais.reneteau@reneteau.notaires.fr</t>
+          <t>pierre.mermet@notaires.fr</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>anais.reneteau@reneteau.notaires.fr</t>
+          <t>pierre.mermet@notaires.fr</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>0478563572</t>
+          <t>0474045153</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>0478563572</t>
+          <t>0474045153</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Route des Troques 69630 CHAPONOST France</t>
+          <t>Bureau principal 84 rue Henri Dépagneux 69400 LIMAS France</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Chaponost</t>
+          <t>Limas</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/reneteau-anais</t>
+          <t>https://www.notaires.fr/fr/office/mermet-pierre</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
@@ -8480,39 +8480,39 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:06</t>
+          <t>2026-08-23 06:29:51</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Office notarial REY Karyne à LYON (69002) | 3 rue Victor Hugo</t>
+          <t>Office notarial MESSERI Aurore à LYON (69003) | 6 cours de la Liberté</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>etude.rey@notaires.fr</t>
+          <t>aurore.messeri@notaires.fr</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>etude.rey@notaires.fr</t>
+          <t>aurore.messeri@notaires.fr</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>0472162590</t>
+          <t>0481061360</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>0472162590</t>
+          <t>0481061360</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 3 rue Victor Hugo 69002 LYON France</t>
+          <t>Bureau principal 6 cours de la Liberté 69003 LYON France</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rey-karyne</t>
+          <t>https://www.notaires.fr/fr/office/messeri-aurore</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
@@ -8542,39 +8542,39 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:08</t>
+          <t>2026-08-23 06:29:53</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ROBIN Axel à LYON (69003) | 123 cours Albert Thomas</t>
+          <t>Office notarial MONTEL Hélène à VERNAISON (69390) | 336 rue de la Fée des Eaux</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>etude@69047.notaires.fr</t>
+          <t>h.montel@notaires.fr</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>etude@69047.notaires.fr</t>
+          <t>h.montel@notaires.fr</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>0449232420</t>
+          <t>0482531832</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>0449232420</t>
+          <t>0482531832</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 123 cours Albert Thomas 69003 LYON France</t>
+          <t>Bureau principal 336 rue de la Fée des Eaux 69390 VERNAISON France</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Vernaison</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/robin-axel</t>
+          <t>https://www.notaires.fr/fr/office/montel-helene</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -8604,39 +8604,39 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:08</t>
+          <t>2026-08-23 06:29:55</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Office notarial ROCHELOIS LYON, SELAS à LYON (69003) | 10-12 boulevard Marius Vivier Merle</t>
+          <t>Office notarial MOREL Laetitia à LYON (69003) | 127 cours du Docteur Long</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>contact@rocheloislyon.notaires.fr</t>
+          <t>morel.laetitia@notaires.fr</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>contact@rocheloislyon.notaires.fr</t>
+          <t>morel.laetitia@notaires.fr</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>0487658201</t>
+          <t>0481061095</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>0487658201</t>
+          <t>0481061095</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 10-12 boulevard Marius Vivier Merle 69003 LYON France</t>
+          <t>Bureau principal 127 cours du Docteur Long 69003 LYON France</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="J131" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rochelois-lyon-selas</t>
+          <t>https://www.notaires.fr/fr/office/morel-laetitia</t>
         </is>
       </c>
       <c r="K131" s="7" t="inlineStr">
@@ -8666,39 +8666,39 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:10</t>
+          <t>2026-08-23 06:29:57</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à LYON (69003) | 40 Rue Antoine Charial</t>
+          <t>Office notarial MURANA-CHARLUET Raphaëlle à SAINT-DIDIER-AU-MONT-D'OR (69370) | 11 rue Voie Lactée</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>corine.mussio@notaires.fr</t>
+          <t>r.murana@notaires.fr</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>corine.mussio@notaires.fr</t>
+          <t>r.murana@notaires.fr</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>0472459539</t>
+          <t>0485680145</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>0472459539</t>
+          <t>0485680145</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 40 Rue Antoine Charial 69003 LYON France</t>
+          <t>Bureau principal 11 rue Voie Lactée 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Didier-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rostaing-mussio-et-associee-selarl-0</t>
+          <t>https://www.notaires.fr/fr/office/murana-charluet-raphaelle</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -8728,39 +8728,39 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:12</t>
+          <t>2026-08-23 06:29:59</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Office notarial RUCHON Edouard à LYON (69005) | 60 avenue du Point du Jour</t>
+          <t>Office notarial MURAT Marie-Pierre à VILLEURBANNE (69100) | 109 Cours Emile Zola</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>edouard.ruchon@notaires.fr</t>
+          <t>office.murat@notaires.fr</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>edouard.ruchon@notaires.fr</t>
+          <t>office.murat@notaires.fr</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>0472544808</t>
+          <t>0437431922</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>0472544808</t>
+          <t>0437431922</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 60 avenue du Point du Jour 69005 LYON France</t>
+          <t>Bureau principal 109 Cours Emile Zola 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="I133" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/ruchon-edouard</t>
+          <t>https://www.notaires.fr/fr/office/murat-marie-pierre</t>
         </is>
       </c>
       <c r="K133" s="7" t="inlineStr">
@@ -8790,39 +8790,39 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:13</t>
+          <t>2026-08-23 06:30:01</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Office notarial S2R NOTAIRES CONSEILS, SELARL à LYON (69006) | 50 boulevard des Belges</t>
+          <t>Office notarial NARDINI Magali à CHAZAY-D'AZERGUES (69380) | 9 rue Marius Berliet</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>simon.reboul@69225.notaires.fr</t>
+          <t>office.nardini@notaires.fr</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>simon.reboul@69225.notaires.fr</t>
+          <t>office.nardini@notaires.fr</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>0437479982</t>
+          <t>04.86.11.05.15</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>0437479982</t>
+          <t>04.86.11.05.15</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 50 boulevard des Belges 69006 LYON France</t>
+          <t>Bureau principal 9 rue Marius Berliet 69380 CHAZAY-D'AZERGUES France</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chazay-D'azergues</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/s2r-notaires-conseils-selarl</t>
+          <t>https://www.notaires.fr/fr/office/nardini-magali</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -8852,39 +8852,39 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:15</t>
+          <t>2026-08-23 06:30:03</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SALAGNAT Frédéric à CHASSIEU (69680) | 56 route de Genas</t>
+          <t>Office notarial NICOLLE et associés à LYON (69003) | 90 rue Paul Bert</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>salagnat@notaires.fr</t>
+          <t>christian.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>salagnat@notaires.fr</t>
+          <t>christian.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>0472797470</t>
+          <t>0492309230</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>0472797470</t>
+          <t>0492309230</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 56 route de Genas 69680 CHASSIEU France</t>
+          <t>Bureau principal 90 rue Paul Bert 69003 LYON France</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="I135" s="7" t="inlineStr">
         <is>
-          <t>Chassieu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/salagnat-frederic</t>
+          <t>https://www.notaires.fr/fr/office/nicolle-et-associes-0</t>
         </is>
       </c>
       <c r="K135" s="7" t="inlineStr">
@@ -8914,39 +8914,39 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:17</t>
+          <t>2026-08-23 06:30:05</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SALICHON &amp; ASSOCIES, SARL à LYON (69006) | 3 Cours Franklin Roosevelt</t>
+          <t>Office notarial NOHARET Françoise à LYON (69007) | 200 AVENUE JEAN JAURES</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>salichonetassocies@notaires.fr</t>
+          <t>office.noharet@notaires.fr</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>salichonetassocies@notaires.fr</t>
+          <t>office.noharet@notaires.fr</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>0478931098</t>
+          <t>0437376850</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>0478931098</t>
+          <t>0437376850</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 3 Cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 200 AVENUE JEAN JAURES 69007 LYON France</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/salichon-associes-sarl</t>
+          <t>https://www.notaires.fr/fr/office/noharet-francoise</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -8976,39 +8976,39 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:18</t>
+          <t>2026-08-23 06:30:07</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique GONDRAN, notaire associée à BELLEVILLE (69220) | 19 rue des Remparts</t>
+          <t>Office notarial NOT’ACTES MARCY à MARCY (69480) | 20, Rue de la Tour</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>anne.gondran@69248.notaires.fr</t>
+          <t>renaud.fontaine@69169.notaires.fr</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>anne.gondran@69248.notaires.fr</t>
+          <t>renaud.fontaine@69169.notaires.fr</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>04 87 01 02 10</t>
+          <t>0437552285</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>04 87 01 02 10</t>
+          <t>0437552285</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 19 rue des Remparts 69220 BELLEVILLE France</t>
+          <t>Bureau principal 20, Rue de la Tour 69480 MARCY France</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Marcy</t>
         </is>
       </c>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-gondran-notaire-associee</t>
+          <t>https://www.notaires.fr/fr/office/notactes-marcy</t>
         </is>
       </c>
       <c r="K137" s="7" t="inlineStr">
@@ -9038,39 +9038,39 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:19</t>
+          <t>2026-08-23 06:30:09</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique Notaires du Promenoir à VILLEFRANCHE-SUR-SAÔNE (69400) | 61 rue d'Anse</t>
+          <t>Office notarial NOTAEM et associés à SAINT-CYR-AU-MONT-D'OR (69450) | 1 rue Reynier</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>etude@promenoir.notaires.fr</t>
+          <t>notaem@notaem.notaires.fr</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>etude@promenoir.notaires.fr</t>
+          <t>notaem@notaem.notaires.fr</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>0474654500</t>
+          <t>0478472483</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>0474654500</t>
+          <t>0478472483</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 61 rue d'Anse 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 1 rue Reynier 69450 SAINT-CYR-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Saint-Cyr-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-notaires-du-promenoir</t>
+          <t>https://www.notaires.fr/fr/office/notaem-et-associes</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -9100,39 +9100,39 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:20</t>
+          <t>2026-08-23 06:30:11</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique OFFICE NOTARIAL DE LA TABLE DE PIERRE à FRANCHEVILLE (69340) | 26 Avenue de la Table de Pierre</t>
+          <t>Office notarial NOTAIRES GAMBETTA à VILLEFRANCHE-SUR-SAÔNE (69400) | 257 rue Boiron</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>christelle.farce@69220.notaires.fr</t>
+          <t>secretariat@etudegambetta.notaires.fr</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>christelle.farce@69220.notaires.fr</t>
+          <t>secretariat@etudegambetta.notaires.fr</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>0437202524</t>
+          <t>0474029910</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>0437202524</t>
+          <t>0474029910</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 26 Avenue de la Table de Pierre 69340 FRANCHEVILLE France</t>
+          <t>Bureau principal 257 rue Boiron 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>Francheville</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J139" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-office-notarial-de-la-table-de-pierre</t>
+          <t>https://www.notaires.fr/fr/office/notaires-gambetta</t>
         </is>
       </c>
       <c r="K139" s="7" t="inlineStr">
@@ -9162,39 +9162,39 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:22</t>
+          <t>2026-08-23 06:30:11</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associée unique NOTAIRE VALLE D'AZERGUES à LAMURE-SUR-AZERGUES (69870) | 10 impasse Chavanet</t>
+          <t>Office notarial NOTARA à LYON (69007) | 152 Grande Rue de la Guillotière</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>office@69095.notaires.fr</t>
+          <t>notara.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>office@69095.notaires.fr</t>
+          <t>notara.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>0474030522</t>
+          <t>0983211434</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>0474030522</t>
+          <t>0983211434</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 impasse Chavanet 69870 LAMURE-SUR-AZERGUES France</t>
+          <t>Bureau principal 152 Grande Rue de la Guillotière 69007 LYON France</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Lamure-Sur-Azergues</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associee-unique-notaire-valle-dazergues</t>
+          <t>https://www.notaires.fr/fr/office/notara</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
@@ -9224,39 +9224,39 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:23</t>
+          <t>2026-08-23 06:30:13</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL CADRAN Notaires Conseils à LYON (69007) | 75 rue Chevreul</t>
+          <t>Office notarial ODO, notaire à THIZY-LES-BOURGS (69240) | 47 RUE JEAN JAURES</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>notaires.thizy@notaires.fr</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>notaires.thizy@notaires.fr</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>0437261144</t>
+          <t>0474640048</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>0437261144</t>
+          <t>0474640048</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 75 rue Chevreul 69007 LYON France</t>
+          <t>Bureau principal 47 RUE JEAN JAURES 69240 THIZY-LES-BOURGS France</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Thizy-Les-Bourgs</t>
         </is>
       </c>
       <c r="J141" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils</t>
+          <t>https://www.notaires.fr/fr/office/odo-notaire</t>
         </is>
       </c>
       <c r="K141" s="7" t="inlineStr">
@@ -9286,39 +9286,39 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:25</t>
+          <t>2026-08-23 06:30:15</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL CADRAN Notaires Conseils à TASSIN-LA-DEMI-LUNE (69160) | 3 avenue de Lauterbourg</t>
+          <t>Office notarial OFFICE NOTARIAL DE PRESSENSE, SELARL à VILLEURBANNE (69100) | 46 rue Francis de Pressensé</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>helene.geraud@notaires.fr</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>helene.geraud@notaires.fr</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>0478343602</t>
+          <t>0437482561</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>0478343602</t>
+          <t>0437482561</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 3 avenue de Lauterbourg 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 46 rue Francis de Pressensé 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils-0</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-de-pressense-selarl</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -9348,39 +9348,39 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:27</t>
+          <t>2026-08-23 06:30:17</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL CHAINE ET ASSOCIES NOTAIRES à LYON (69006) | 139 rue Vendôme</t>
+          <t>Office notarial OFFICE NOTARIAL DES CHARPENNES-VILLEURBANNE, SELARL à VILLEURBANNE (69100) | 50 A Cours Emile Zola</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>etude.chaine@notaires.fr</t>
+          <t>oncv@69136.notaires.fr</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>etude.chaine@notaires.fr</t>
+          <t>oncv@69136.notaires.fr</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>0472757600</t>
+          <t>0472759396</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>0472757600</t>
+          <t>0472759396</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 139 rue Vendôme 69006 LYON France</t>
+          <t>Bureau principal 50 A Cours Emile Zola 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-chaine-et-associes-notaires</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-des-charpennes-villeurbanne-selarl</t>
         </is>
       </c>
       <c r="K143" s="7" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:29:28</t>
+          <t>2026-08-23 06:30:18</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:51</t>
+          <t>2026-08-23 06:28:28</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:53</t>
+          <t>2026-08-23 06:28:30</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:55</t>
+          <t>2026-08-23 06:28:31</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:56</t>
+          <t>2026-08-23 06:28:33</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:58</t>
+          <t>2026-08-23 06:28:34</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:59</t>
+          <t>2026-08-23 06:28:36</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:01</t>
+          <t>2026-08-23 06:28:38</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:02</t>
+          <t>2026-08-23 06:28:39</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:04</t>
+          <t>2026-08-23 06:28:40</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:06</t>
+          <t>2026-08-23 06:28:42</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:08</t>
+          <t>2026-08-23 06:28:44</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:09</t>
+          <t>2026-08-23 06:28:45</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:11</t>
+          <t>2026-08-23 06:28:47</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:13</t>
+          <t>2026-08-23 06:28:49</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:14</t>
+          <t>2026-08-23 06:28:51</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:15</t>
+          <t>2026-08-23 06:28:52</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:17</t>
+          <t>2026-08-23 06:28:55</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:19</t>
+          <t>2026-08-23 06:28:56</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:21</t>
+          <t>2026-08-23 06:28:58</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:22</t>
+          <t>2026-08-23 06:29:00</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:24</t>
+          <t>2026-08-23 06:29:01</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:26</t>
+          <t>2026-08-23 06:29:03</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:27</t>
+          <t>2026-08-23 06:29:05</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:29</t>
+          <t>2026-08-23 06:29:07</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:30</t>
+          <t>2026-08-23 06:29:08</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:32</t>
+          <t>2026-08-23 06:29:10</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:34</t>
+          <t>2026-08-23 06:29:12</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:35</t>
+          <t>2026-08-23 06:29:13</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:37</t>
+          <t>2026-08-23 06:29:15</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:39</t>
+          <t>2026-08-23 06:29:16</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:41</t>
+          <t>2026-08-23 06:29:18</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:42</t>
+          <t>2026-08-23 06:29:20</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:44</t>
+          <t>2026-08-23 06:29:21</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:46</t>
+          <t>2026-08-23 06:29:22</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:47</t>
+          <t>2026-08-23 06:29:23</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:49</t>
+          <t>2026-08-23 06:29:24</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:51</t>
+          <t>2026-08-23 06:29:26</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:53</t>
+          <t>2026-08-23 06:29:28</t>
         </is>
       </c>
     </row>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:54</t>
+          <t>2026-08-23 06:29:29</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:56</t>
+          <t>2026-08-23 06:29:31</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:57</t>
+          <t>2026-08-23 06:29:32</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:27:58</t>
+          <t>2026-08-23 06:29:34</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:00</t>
+          <t>2026-08-23 06:29:35</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:01</t>
+          <t>2026-08-23 06:29:37</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:03</t>
+          <t>2026-08-23 06:29:38</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:05</t>
+          <t>2026-08-23 06:29:40</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:06</t>
+          <t>2026-08-23 06:29:41</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:08</t>
+          <t>2026-08-23 06:29:43</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:10</t>
+          <t>2026-08-23 06:29:44</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:28:11</t>
+          <t>2026-08-23 06:29:46</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:34</t>
+          <t>2026-08-23 06:27:04</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:35</t>
+          <t>2026-08-23 06:27:04</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:36</t>
+          <t>2026-08-23 06:27:05</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:37</t>
+          <t>2026-08-23 06:27:07</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:39</t>
+          <t>2026-08-23 06:27:08</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:41</t>
+          <t>2026-08-23 06:27:10</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:42</t>
+          <t>2026-08-23 06:27:12</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:44</t>
+          <t>2026-08-23 06:27:13</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:45</t>
+          <t>2026-08-23 06:27:16</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:47</t>
+          <t>2026-08-23 06:27:18</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:49</t>
+          <t>2026-08-23 06:27:20</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:50</t>
+          <t>2026-08-23 06:27:21</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:52</t>
+          <t>2026-08-23 06:27:23</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:54</t>
+          <t>2026-08-23 06:27:25</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:55</t>
+          <t>2026-08-23 06:27:27</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:57</t>
+          <t>2026-08-23 06:27:29</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:25:58</t>
+          <t>2026-08-23 06:27:31</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:00</t>
+          <t>2026-08-23 06:27:32</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:01</t>
+          <t>2026-08-23 06:27:34</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:03</t>
+          <t>2026-08-23 06:27:36</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:04</t>
+          <t>2026-08-23 06:27:38</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:05</t>
+          <t>2026-08-23 06:27:39</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13928,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:07</t>
+          <t>2026-08-23 06:27:41</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:08</t>
+          <t>2026-08-23 06:27:43</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:09</t>
+          <t>2026-08-23 06:27:44</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:11</t>
+          <t>2026-08-23 06:27:46</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:12</t>
+          <t>2026-08-23 06:27:47</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:14</t>
+          <t>2026-08-23 06:27:49</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:15</t>
+          <t>2026-08-23 06:27:51</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:17</t>
+          <t>2026-08-23 06:27:52</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:19</t>
+          <t>2026-08-23 06:27:54</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:21</t>
+          <t>2026-08-23 06:27:55</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:23</t>
+          <t>2026-08-23 06:27:57</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:25</t>
+          <t>2026-08-23 06:27:59</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:27</t>
+          <t>2026-08-23 06:28:00</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:29</t>
+          <t>2026-08-23 06:28:02</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:31</t>
+          <t>2026-08-23 06:28:04</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:32</t>
+          <t>2026-08-23 06:28:06</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:33</t>
+          <t>2026-08-23 06:28:07</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:35</t>
+          <t>2026-08-23 06:28:09</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:36</t>
+          <t>2026-08-23 06:28:11</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:37</t>
+          <t>2026-08-23 06:28:13</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:39</t>
+          <t>2026-08-23 06:28:14</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:40</t>
+          <t>2026-08-23 06:28:16</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:42</t>
+          <t>2026-08-23 06:28:18</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:43</t>
+          <t>2026-08-23 06:28:20</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:45</t>
+          <t>2026-08-23 06:28:21</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:47</t>
+          <t>2026-08-23 06:28:23</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:48</t>
+          <t>2026-08-23 06:28:24</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16 06:26:50</t>
+          <t>2026-08-23 06:28:26</t>
         </is>
       </c>
     </row>

--- a/exports/notaires/annuaire_notaires_france.xlsx
+++ b/exports/notaires/annuaire_notaires_france.xlsx
@@ -637,32 +637,32 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTAIRES CONDRIEU à CONDRIEU (69420) | 40 rue des Granges</t>
+          <t>Office notarial SELARL NOTAIRES, Familles et Patrimoines à ARNAS (69400) | 61 route d’Herbain</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>notairescondrieu@69036.notaires.fr</t>
+          <t>notnfp@notaires.fr</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>notairescondrieu@69036.notaires.fr</t>
+          <t>notnfp@notaires.fr</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>0474595233</t>
+          <t>0474048562</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>0474595233</t>
+          <t>0474048562</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 40 rue des Granges 69420 CONDRIEU France</t>
+          <t>Bureau principal 61 route d’Herbain 69400 ARNAS France</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Condrieu</t>
+          <t>Arnas</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notaires-condrieu</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notaires-familles-et-patrimoines</t>
         </is>
       </c>
       <c r="K2" s="5" t="inlineStr">
@@ -692,14 +692,14 @@
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:29</t>
+          <t>2026-08-30 11:05:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTAIRES, Familles et Patrimoines à ARNAS (69400) | 61 route d’Herbain</t>
+          <t>Office notarial SELARL NOTAIRES, Familles et Patrimoines à BEAUJEU (69430) | 35 rue du Général Leclerc</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 61 route d’Herbain 69400 ARNAS France</t>
+          <t>Bureau principal 35 rue du Général Leclerc 69430 BEAUJEU France</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -739,12 +739,12 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Arnas</t>
+          <t>Beaujeu</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notaires-familles-et-patrimoines</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notaires-familles-et-patrimoines-0</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -754,39 +754,39 @@
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:30</t>
+          <t>2026-08-30 11:05:46</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTAIRES, Familles et Patrimoines à BEAUJEU (69430) | 35 rue du Général Leclerc</t>
+          <t>Office notarial SELARL NOTAIRES LYON CONFLUENCE à LYON (69002) | 72 Cours Charlemagne</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>notnfp@notaires.fr</t>
+          <t>confluence@notaires.fr</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>notnfp@notaires.fr</t>
+          <t>confluence@notaires.fr</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>0474048562</t>
+          <t>0428299179</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>0474048562</t>
+          <t>0428299179</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 35 rue du Général Leclerc 69430 BEAUJEU France</t>
+          <t>Bureau principal 72 Cours Charlemagne 69002 LYON France</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Beaujeu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notaires-familles-et-patrimoines-0</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notaires-lyon-confluence</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -816,39 +816,39 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:32</t>
+          <t>2026-08-30 11:05:48</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTAIRES LYON CONFLUENCE à LYON (69002) | 72 Cours Charlemagne</t>
+          <t>Office notarial SELARL NOTAIRES LYON HOTEL-DIEU à LYON (69002) | 26 rue Bellecordière</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>confluence@notaires.fr</t>
+          <t>blanche-marie.vincent@vincent-hotel-dieu.notaires.fr</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>confluence@notaires.fr</t>
+          <t>blanche-marie.vincent@vincent-hotel-dieu.notaires.fr</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>0428299179</t>
+          <t>0478058920</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>0428299179</t>
+          <t>0478058920</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 72 Cours Charlemagne 69002 LYON France</t>
+          <t>Bureau principal 26 rue Bellecordière 69002 LYON France</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notaires-lyon-confluence</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notaires-lyon-hotel-dieu</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -878,39 +878,39 @@
       </c>
       <c r="L5" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:33</t>
+          <t>2026-08-30 11:05:50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTAIRES LYON HOTEL-DIEU à LYON (69002) | 26 rue Bellecordière</t>
+          <t>Office notarial SELARL NOTASOL - NOTAIRES DU SUD OUEST LYONNAIS à BRIGNAIS (69530) | 2 A boulevard André Lassagne</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>blanche-marie.vincent@vincent-hotel-dieu.notaires.fr</t>
+          <t>notaires.brignais69055@notaires.fr</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>blanche-marie.vincent@vincent-hotel-dieu.notaires.fr</t>
+          <t>notaires.brignais69055@notaires.fr</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>0478058920</t>
+          <t>0478051231</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>0478058920</t>
+          <t>0478051231</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 26 rue Bellecordière 69002 LYON France</t>
+          <t>Bureau principal 2 A boulevard André Lassagne 69530 BRIGNAIS France</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Brignais</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notaires-lyon-hotel-dieu</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notasol-notaires-du-sud-ouest-lyonnais</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -940,39 +940,39 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:35</t>
+          <t>2026-08-30 11:05:52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL NOTASOL - NOTAIRES DU SUD OUEST LYONNAIS à BRIGNAIS (69530) | 2 A boulevard André Lassagne</t>
+          <t>Office notarial SELARL OFFICE DE LA COLLINE à LYON (69004) | 57 rue Hénon</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>notaires.brignais69055@notaires.fr</t>
+          <t>luc.bertholon@69132.notaires.fr</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>notaires.brignais69055@notaires.fr</t>
+          <t>luc.bertholon@69132.notaires.fr</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>0478051231</t>
+          <t>0478290380</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>0478051231</t>
+          <t>0478290380</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 A boulevard André Lassagne 69530 BRIGNAIS France</t>
+          <t>Bureau principal 57 rue Hénon 69004 LYON France</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -987,12 +987,12 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Brignais</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-notasol-notaires-du-sud-ouest-lyonnais</t>
+          <t>https://www.notaires.fr/fr/office/selarl-office-de-la-colline</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1002,39 +1002,39 @@
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:36</t>
+          <t>2026-08-30 11:05:54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL OFFICE DE LA COLLINE à LYON (69004) | 57 rue Hénon</t>
+          <t>Office notarial SELARL OFFICE DES LUMIERES à LYON (69004) | 84, quai Joseph Gillet</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>luc.bertholon@69132.notaires.fr</t>
+          <t>contact@officedeslumieres.com</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>luc.bertholon@69132.notaires.fr</t>
+          <t>contact@officedeslumieres.com</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>0478290380</t>
+          <t>0472411565</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>0478290380</t>
+          <t>0472411565</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 57 rue Hénon 69004 LYON France</t>
+          <t>Bureau principal 84, quai Joseph Gillet 69004 LYON France</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-office-de-la-colline</t>
+          <t>https://www.notaires.fr/fr/office/selarl-office-des-lumieres</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -1064,39 +1064,39 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:38</t>
+          <t>2026-08-30 11:05:56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL OFFICE DES LUMIERES à LYON (69004) | 84, quai Joseph Gillet</t>
+          <t>Office notarial SELARL Office notarial de Chaponost à CHAPONOST (69630) | 3 rue des Viollières</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>contact@officedeslumieres.com</t>
+          <t>etude@tacussel.notaires.fr</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>contact@officedeslumieres.com</t>
+          <t>etude@tacussel.notaires.fr</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>0472411565</t>
+          <t>0478446778</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>0472411565</t>
+          <t>0478446778</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 84, quai Joseph Gillet 69004 LYON France</t>
+          <t>Bureau principal 3 rue des Viollières 69630 CHAPONOST France</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chaponost</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-office-des-lumieres</t>
+          <t>https://www.notaires.fr/fr/office/selarl-office-notarial-de-chaponost</t>
         </is>
       </c>
       <c r="K9" s="7" t="inlineStr">
@@ -1126,39 +1126,39 @@
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:39</t>
+          <t>2026-08-30 11:05:57</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Office notarial de Chaponost à CHAPONOST (69630) | 3 rue des Viollières</t>
+          <t>Office notarial SELARL OFFICE NOTARIAL DE L'EUROPE à LYON (69003) | 62 rue de Bonnel</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>etude@tacussel.notaires.fr</t>
+          <t>officedeleurope@notaires.fr</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>etude@tacussel.notaires.fr</t>
+          <t>officedeleurope@notaires.fr</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>0478446778</t>
+          <t>0478958140</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>0478446778</t>
+          <t>0478958140</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 3 rue des Viollières 69630 CHAPONOST France</t>
+          <t>Bureau principal 62 rue de Bonnel 69003 LYON France</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Chaponost</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-office-notarial-de-chaponost</t>
+          <t>https://www.notaires.fr/fr/office/selarl-office-notarial-de-leurope</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
@@ -1188,39 +1188,39 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:41</t>
+          <t>2026-08-30 11:05:59</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL OFFICE NOTARIAL DE L'EUROPE à LYON (69003) | 62 rue de Bonnel</t>
+          <t>Office notarial SELARL OFFICE NOTARIAL LA CALADE à VILLEFRANCHE-SUR-SAÔNE (69400) | 596 Boulevard Albert Camus</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>officedeleurope@notaires.fr</t>
+          <t>marion.pelletier@notaires.fr</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>officedeleurope@notaires.fr</t>
+          <t>marion.pelletier@notaires.fr</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>0478958140</t>
+          <t>0474042183</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>0478958140</t>
+          <t>0474042183</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 62 rue de Bonnel 69003 LYON France</t>
+          <t>Bureau principal 596 Boulevard Albert Camus 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-office-notarial-de-leurope</t>
+          <t>https://www.notaires.fr/fr/office/selarl-office-notarial-la-calade</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
@@ -1250,39 +1250,39 @@
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:43</t>
+          <t>2026-08-30 11:06:01</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL OFFICE NOTARIAL LA CALADE à VILLEFRANCHE-SUR-SAÔNE (69400) | 596 Boulevard Albert Camus</t>
+          <t>Office notarial SELARL ONE NOTAIRES à ÉCULLY (69130) | 4 allée des Tullistes</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>marion.pelletier@notaires.fr</t>
+          <t>notaires.ecully@notaires.fr</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>marion.pelletier@notaires.fr</t>
+          <t>notaires.ecully@notaires.fr</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>0474042183</t>
+          <t>0478339260</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>0474042183</t>
+          <t>0478339260</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 596 Boulevard Albert Camus 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 4 allée des Tullistes 69130 ÉCULLY France</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Ecully</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-office-notarial-la-calade</t>
+          <t>https://www.notaires.fr/fr/office/selarl-one-notaires</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
@@ -1312,39 +1312,39 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:44</t>
+          <t>2026-08-30 11:06:03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ONE NOTAIRES à ÉCULLY (69130) | 4 allée des Tullistes</t>
+          <t>Office notarial SELARL Pascale BERTONI-OLMO, Jérôme GUILLARME, Gauthier DOLIGEZ à CHAZAY-D'AZERGUES (69380) | Allée Benoît Raclet</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>notaires.ecully@notaires.fr</t>
+          <t>office69129.chazay@69129.notaires.fr</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>notaires.ecully@notaires.fr</t>
+          <t>office69129.chazay@69129.notaires.fr</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>0478339260</t>
+          <t>0478436166</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>0478339260</t>
+          <t>0478436166</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 4 allée des Tullistes 69130 ÉCULLY France</t>
+          <t>Bureau principal Allée Benoît Raclet 69380 CHAZAY-D'AZERGUES France</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Ecully</t>
+          <t>Chazay-D'azergues</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-one-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-pascale-bertoni-olmo-jerome-guillarme-gauthier-doligez</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1374,39 +1374,39 @@
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:45</t>
+          <t>2026-08-30 11:06:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Pascale BERTONI-OLMO, Jérôme GUILLARME, Gauthier DOLIGEZ à CHAZAY-D'AZERGUES (69380) | Allée Benoît Raclet</t>
+          <t>Office notarial SELARL Rémy SAMSON - Philippe DAVID - Catherine GASIOT-DAVID - Paul LEUFFLEN - Office notarial de la Passerelle à LYON (69002) | 36 quai Saint Antoine</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>office69129.chazay@69129.notaires.fr</t>
+          <t>officenotarialdelapasserelle@notaires.fr</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>office69129.chazay@69129.notaires.fr</t>
+          <t>officenotarialdelapasserelle@notaires.fr</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>0478436166</t>
+          <t>0478427830</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>0478436166</t>
+          <t>0478427830</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal Allée Benoît Raclet 69380 CHAZAY-D'AZERGUES France</t>
+          <t>Bureau principal 36 quai Saint Antoine 69002 LYON France</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Chazay-D'azergues</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-pascale-bertoni-olmo-jerome-guillarme-gauthier-doligez</t>
+          <t>https://www.notaires.fr/fr/office/selarl-remy-samson-philippe-david-catherine-gasiot-david-paul-leufflen-office-notarial-de-la-passerelle</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
@@ -1436,39 +1436,39 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:47</t>
+          <t>2026-08-30 11:06:12</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Rémy SAMSON - Philippe DAVID - Catherine GASIOT-DAVID - Paul LEUFFLEN - Office notarial de la Passerelle à LYON (69002) | 36 quai Saint Antoine</t>
+          <t>Office notarial SELARL ROUSSEAU-BRETON NOTAIRE à LYON (69002) | 32 rue de la République</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>officenotarialdelapasserelle@notaires.fr</t>
+          <t>etude.69001@notaires.fr</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>officenotarialdelapasserelle@notaires.fr</t>
+          <t>etude.69001@notaires.fr</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>0478427830</t>
+          <t>0478381949</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>0478427830</t>
+          <t>0478381949</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 36 quai Saint Antoine 69002 LYON France</t>
+          <t>Bureau principal 32 rue de la République 69002 LYON France</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-remy-samson-philippe-david-catherine-gasiot-david-paul-leufflen-office-notarial-de-la-passerelle</t>
+          <t>https://www.notaires.fr/fr/office/selarl-rousseau-breton-notaire</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1498,39 +1498,39 @@
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:48</t>
+          <t>2026-08-30 11:06:27</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ROUSSEAU-BRETON NOTAIRE à LYON (69002) | 32 rue de la République</t>
+          <t>Office notarial SELARL YOHAN BURNICHON, NOTAIRE ET ASSOCIES à LYON (69001) | 9 rue Constantine</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>etude.69001@notaires.fr</t>
+          <t>burnichon-dubois@notaires.fr</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>etude.69001@notaires.fr</t>
+          <t>burnichon-dubois@notaires.fr</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>0478381949</t>
+          <t>0478280657</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>0478381949</t>
+          <t>0478280657</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 32 rue de la République 69002 LYON France</t>
+          <t>Bureau principal 9 rue Constantine 69001 LYON France</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-rousseau-breton-notaire</t>
+          <t>https://www.notaires.fr/fr/office/selarl-yohan-burnichon-notaire-et-associes</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1560,39 +1560,39 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:50</t>
+          <t>2026-08-30 11:06:36</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL YOHAN BURNICHON, NOTAIRE ET ASSOCIES à LYON (69001) | 9 rue Constantine</t>
+          <t>Office notarial SELAS ALCAIX à LYON (69006) | 91 Cours Lafayette</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>burnichon-dubois@notaires.fr</t>
+          <t>notaires@alcaix.notaires.fr</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>burnichon-dubois@notaires.fr</t>
+          <t>notaires@alcaix.notaires.fr</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>0478280657</t>
+          <t>0472745340</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>0478280657</t>
+          <t>0472745340</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue Constantine 69001 LYON France</t>
+          <t>Bureau principal 91 Cours Lafayette 69006 LYON France</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-yohan-burnichon-notaire-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/selas-alcaix</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
@@ -1622,39 +1622,39 @@
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:53</t>
+          <t>2026-08-30 11:06:40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELAS ALCAIX à LYON (69006) | 91 Cours Lafayette</t>
+          <t>Office notarial SELAS Althémis Lyon - Rhône-Alpes à LYON (69002) | 105 rue du Président Edouard Herriot</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>notaires@alcaix.notaires.fr</t>
+          <t>althemis.lyon@althemis.notaires.fr</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>notaires@alcaix.notaires.fr</t>
+          <t>althemis.lyon@althemis.notaires.fr</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>0472745340</t>
+          <t>0472760370</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>0472745340</t>
+          <t>0472760370</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 91 Cours Lafayette 69006 LYON France</t>
+          <t>Bureau principal 105 rue du Président Edouard Herriot 69002 LYON France</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-alcaix</t>
+          <t>https://www.notaires.fr/fr/office/selas-althemis-lyon-rhone-alpes</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
@@ -1684,39 +1684,39 @@
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:55</t>
+          <t>2026-08-30 11:06:43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELAS Althémis Lyon - Rhône-Alpes à LYON (69002) | 105 rue du Président Edouard Herriot</t>
+          <t>Office notarial SELAS BONNIE AOUN NOTAIRE ASSOCIÉ à LYON (69001) | 21 rue d'Algérie</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>althemis.lyon@althemis.notaires.fr</t>
+          <t>bonnie.aoun@69277.notaires.fr</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>althemis.lyon@althemis.notaires.fr</t>
+          <t>bonnie.aoun@69277.notaires.fr</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>0472760370</t>
+          <t>04 28 29 21 21</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>0472760370</t>
+          <t>04 28 29 21 21</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 105 rue du Président Edouard Herriot 69002 LYON France</t>
+          <t>Bureau principal 21 rue d'Algérie 69001 LYON France</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-althemis-lyon-rhone-alpes</t>
+          <t>https://www.notaires.fr/fr/office/selas-bonnie-aoun-notaire-associe</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
@@ -1746,39 +1746,39 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:56</t>
+          <t>2026-08-30 11:06:46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELAS BONNIE AOUN NOTAIRE ASSOCIÉ à LYON (69001) | 21 rue d'Algérie</t>
+          <t>Office notarial SELAS FIDAL NOTAIRES à LYON (69009) | 18 rue Félix Mangini</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>bonnie.aoun@69277.notaires.fr</t>
+          <t>ophelie.fevre@fidal.notaires.fr</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>bonnie.aoun@69277.notaires.fr</t>
+          <t>ophelie.fevre@fidal.notaires.fr</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>04 28 29 21 21</t>
+          <t>0487915500</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>04 28 29 21 21</t>
+          <t>0487915500</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 21 rue d'Algérie 69001 LYON France</t>
+          <t>Bureau principal 18 rue Félix Mangini 69009 LYON France</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-bonnie-aoun-notaire-associe</t>
+          <t>https://www.notaires.fr/fr/office/selas-fidal-notaires-2</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
@@ -1808,39 +1808,39 @@
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:58</t>
+          <t>2026-08-30 11:06:50</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELAS FIDAL NOTAIRES à LYON (69009) | 18 rue Félix Mangini</t>
+          <t>Office notarial SELAS GAGNAIRE ASSOCIES NOTAIRES à MEYZIEU (69330) | 7 C rue de la République</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>ophelie.fevre@fidal.notaires.fr</t>
+          <t>gagnaire-associes@gagnaire.notaires.fr</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>ophelie.fevre@fidal.notaires.fr</t>
+          <t>gagnaire-associes@gagnaire.notaires.fr</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>0487915500</t>
+          <t>0478314009</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>0487915500</t>
+          <t>0478314009</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 18 rue Félix Mangini 69009 LYON France</t>
+          <t>Bureau principal 7 C rue de la République 69330 MEYZIEU France</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Meyzieu</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-fidal-notaires-2</t>
+          <t>https://www.notaires.fr/fr/office/selas-gagnaire-associes-notaires</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
@@ -1870,39 +1870,39 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:59</t>
+          <t>2026-08-30 11:06:52</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELAS GAGNAIRE ASSOCIES NOTAIRES à MEYZIEU (69330) | 7 C rue de la République</t>
+          <t>Office notarial SELAS GAGNAIRE ASSOCIES NOTAIRES à SAINT-PRIEST (69800) | 8 rue Aristide Briand</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>gagnaire-associes@gagnaire.notaires.fr</t>
+          <t>gagnairesaintpriest@gagnaire.notaires.fr</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>gagnaire-associes@gagnaire.notaires.fr</t>
+          <t>gagnairesaintpriest@gagnaire.notaires.fr</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>0478314009</t>
+          <t>0472592814</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>0478314009</t>
+          <t>0472592814</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 7 C rue de la République 69330 MEYZIEU France</t>
+          <t>Bureau principal 8 rue Aristide Briand 69800 SAINT-PRIEST France</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Meyzieu</t>
+          <t>Saint-Priest</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-gagnaire-associes-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selas-gagnaire-associes-notaires-0</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
@@ -1932,39 +1932,39 @@
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:01</t>
+          <t>2026-08-30 11:06:54</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELAS GAGNAIRE ASSOCIES NOTAIRES à SAINT-PRIEST (69800) | 8 rue Aristide Briand</t>
+          <t>Office notarial SELAS Implid Notaires à LYON (69006) | 79 Cours Vitton</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>gagnairesaintpriest@gagnaire.notaires.fr</t>
+          <t>arthur.sch@notaires.fr</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>gagnairesaintpriest@gagnaire.notaires.fr</t>
+          <t>arthur.sch@notaires.fr</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>0472592814</t>
+          <t>0428298198</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>0472592814</t>
+          <t>0428298198</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 8 rue Aristide Briand 69800 SAINT-PRIEST France</t>
+          <t>Bureau principal 79 Cours Vitton 69006 LYON France</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -1979,12 +1979,12 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Saint-Priest</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-gagnaire-associes-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/selas-implid-notaires</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
@@ -1994,39 +1994,39 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:03</t>
+          <t>2026-08-30 11:06:55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELAS Implid Notaires à LYON (69006) | 79 Cours Vitton</t>
+          <t>Office notarial SELAS UP NOTAIRES à DÉCINES-CHARPIEU (69150) | 2 avenue Silvin</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>arthur.sch@notaires.fr</t>
+          <t>upnotaires@notaires.fr</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>arthur.sch@notaires.fr</t>
+          <t>upnotaires@notaires.fr</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>0428298198</t>
+          <t>0472056280</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>0428298198</t>
+          <t>0472056280</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 79 Cours Vitton 69006 LYON France</t>
+          <t>Bureau principal 2 avenue Silvin 69150 DÉCINES-CHARPIEU France</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Décines-Charpieu</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-implid-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selas-notaires</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -2056,39 +2056,39 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:05</t>
+          <t>2026-08-30 11:06:57</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELAS UP NOTAIRES à DÉCINES-CHARPIEU (69150) | 2 avenue Silvin</t>
+          <t>Office notarial SELAS NOTAIRES DU VAL D'OUEST à VAUGNERAY (69670) | 2 Chemin des Vignes</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>upnotaires@notaires.fr</t>
+          <t>etude69065.vaugneray@notaires.fr</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>upnotaires@notaires.fr</t>
+          <t>etude69065.vaugneray@notaires.fr</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>0472056280</t>
+          <t>0478458484</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>0472056280</t>
+          <t>0478458484</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 avenue Silvin 69150 DÉCINES-CHARPIEU France</t>
+          <t>Bureau principal 2 Chemin des Vignes 69670 VAUGNERAY France</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Décines-Charpieu</t>
+          <t>Vaugneray</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selas-notaires-du-val-douest</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
@@ -2118,39 +2118,39 @@
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:05</t>
+          <t>2026-08-30 11:07:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELAS NOTAIRES DU VAL D'OUEST à VAUGNERAY (69670) | 2 Chemin des Vignes</t>
+          <t>Office notarial SELAS NOTAIRES DU VAL D'OUEST à BRINDAS (69126) | 20 Chemin des Sauzes</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>etude69065.vaugneray@notaires.fr</t>
+          <t>martin.hacquard@notaires.fr</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>etude69065.vaugneray@notaires.fr</t>
+          <t>martin.hacquard@notaires.fr</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>0478458484</t>
+          <t>0487950105</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>0478458484</t>
+          <t>0487950105</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 2 Chemin des Vignes 69670 VAUGNERAY France</t>
+          <t>Bureau principal 20 Chemin des Sauzes 69126 BRINDAS France</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Vaugneray</t>
+          <t>Brindas</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-notaires-du-val-douest</t>
+          <t>https://www.notaires.fr/fr/office/selas-notaires-du-val-douest-0</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
@@ -2180,39 +2180,39 @@
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:07</t>
+          <t>2026-08-30 11:07:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELAS NOTAIRES DU VAL D'OUEST à BRINDAS (69126) | 20 Chemin des Sauzes</t>
+          <t>Office notarial SELAS NOTALMA à LYON (69002) | 6 place Carnot</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>martin.hacquard@notaires.fr</t>
+          <t>godefroy.richard@notaires.fr</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>martin.hacquard@notaires.fr</t>
+          <t>godefroy.richard@notaires.fr</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>0487950105</t>
+          <t>0481091118</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>0487950105</t>
+          <t>0481091118</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 20 Chemin des Sauzes 69126 BRINDAS France</t>
+          <t>Bureau principal 6 place Carnot 69002 LYON France</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
@@ -2227,12 +2227,12 @@
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>Brindas</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-notaires-du-val-douest-0</t>
+          <t>https://www.notaires.fr/fr/office/selas-notalma</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
@@ -2242,39 +2242,39 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:09</t>
+          <t>2026-08-30 11:07:03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELAS NOTALMA à LYON (69002) | 6 place Carnot</t>
+          <t>Office notarial SIDI-BOULENOUAR Dounia à LYON (69007) | 17 rue Crépet</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>godefroy.richard@notaires.fr</t>
+          <t>dounia.sidi@notaires.fr</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>godefroy.richard@notaires.fr</t>
+          <t>dounia.sidi@notaires.fr</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>0481091118</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>0481091118</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 6 place Carnot 69002 LYON France</t>
+          <t>Bureau principal 17 rue Crépet 69007 LYON France</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selas-notalma</t>
+          <t>https://www.notaires.fr/fr/office/sidi-boulenouar-dounia</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
@@ -2304,39 +2304,39 @@
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:11</t>
+          <t>2026-08-30 11:07:06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SIDI-BOULENOUAR Dounia à LYON (69007) | 17 rue Crépet</t>
+          <t>Office notarial SIMON et associés, SELARL à LYON (69005) | 49 avenue du Point du Jour</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>dounia.sidi@notaires.fr</t>
+          <t>etude@sdm.notaires.fr</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>dounia.sidi@notaires.fr</t>
+          <t>etude@sdm.notaires.fr</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0478252638</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>0478252638</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 17 rue Crépet 69007 LYON France</t>
+          <t>Bureau principal 49 avenue du Point du Jour 69005 LYON France</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sidi-boulenouar-dounia</t>
+          <t>https://www.notaires.fr/fr/office/simon-et-associes-selarl</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
@@ -2366,39 +2366,39 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:13</t>
+          <t>2026-08-30 11:07:08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SIMON et associés, SELARL à LYON (69005) | 49 avenue du Point du Jour</t>
+          <t>Office notarial SOCIETE BNO, SELARL à ÉCULLY (69130) | 1 Chemin Jean-Marie Vianney</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>etude@sdm.notaires.fr</t>
+          <t>beatrice.novel@notaires.fr</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>etude@sdm.notaires.fr</t>
+          <t>beatrice.novel@notaires.fr</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>0478252638</t>
+          <t>0487254848</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>0478252638</t>
+          <t>0487254848</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 49 avenue du Point du Jour 69005 LYON France</t>
+          <t>Bureau principal 1 Chemin Jean-Marie Vianney 69130 ÉCULLY France</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Ecully</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/simon-et-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/societe-bno-selarl</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -2428,39 +2428,39 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:14</t>
+          <t>2026-08-30 11:07:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SOCIETE BNO, SELARL à ÉCULLY (69130) | 1 Chemin Jean-Marie Vianney</t>
+          <t>Office notarial SOUBEYRAN et associés, SELARL à LYON (69008) | 33 RUE DES TUILIERS</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>beatrice.novel@notaires.fr</t>
+          <t>etude.soubeyran@notaires.fr</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>beatrice.novel@notaires.fr</t>
+          <t>etude.soubeyran@notaires.fr</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>0487254848</t>
+          <t>0481682010</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>0487254848</t>
+          <t>0481682010</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Chemin Jean-Marie Vianney 69130 ÉCULLY France</t>
+          <t>Bureau principal 33 RUE DES TUILIERS 69008 LYON France</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>Ecully</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/societe-bno-selarl</t>
+          <t>https://www.notaires.fr/fr/office/soubeyran-et-associes-selarl</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:16</t>
+          <t>2026-08-30 11:07:12</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SOUBEYRAN et associés, SELARL à LYON (69008) | 33 RUE DES TUILIERS</t>
+          <t>Office notarial SPE SAS Quante à LYON (69001) | 21 rue d'Algérie</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>etude.soubeyran@notaires.fr</t>
+          <t>claire.pellegrin@notaires.fr</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>etude.soubeyran@notaires.fr</t>
+          <t>claire.pellegrin@notaires.fr</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>0481682010</t>
+          <t>0428292121</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>0481682010</t>
+          <t>0428292121</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 33 RUE DES TUILIERS 69008 LYON France</t>
+          <t>Bureau principal 21 rue d'Algérie 69001 LYON France</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/soubeyran-et-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/spe-sas-quante</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
@@ -2552,39 +2552,39 @@
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:18</t>
+          <t>2026-08-30 11:07:14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SPE SAS Quante à LYON (69001) | 21 rue d'Algérie</t>
+          <t>Office notarial THEVENON Eric à LYON (69004) | 17 Place Tabareau</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>claire.pellegrin@notaires.fr</t>
+          <t>eric.thevenon@notaires.fr</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>claire.pellegrin@notaires.fr</t>
+          <t>eric.thevenon@notaires.fr</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>0428292121</t>
+          <t>0478588060</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>0428292121</t>
+          <t>0478588060</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 21 rue d'Algérie 69001 LYON France</t>
+          <t>Bureau principal 17 Place Tabareau 69004 LYON France</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/spe-sas-quante</t>
+          <t>https://www.notaires.fr/fr/office/thevenon-eric</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
@@ -2614,39 +2614,31 @@
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:20</t>
+          <t>2026-08-30 11:07:17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Office notarial THEVENON Eric à LYON (69004) | 17 Place Tabareau</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>eric.thevenon@notaires.fr</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>eric.thevenon@notaires.fr</t>
-        </is>
-      </c>
+          <t>Office notarial THIOLLIER Associés, SARL à SAINT-SYMPHORIEN-SUR-COISE (69590) | 16 PLACE DE LA REPUBLIQUE</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>0478588060</t>
+          <t>0478484039</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>0478588060</t>
+          <t>0478484039</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 17 Place Tabareau 69004 LYON France</t>
+          <t>Bureau principal 16 PLACE DE LA REPUBLIQUE 69590 SAINT-SYMPHORIEN-SUR-COISE France</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
@@ -2661,12 +2653,12 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Symphorien-Sur-Coise</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/thevenon-eric</t>
+          <t>https://www.notaires.fr/fr/office/thiollier-associes-sarl</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
@@ -2676,31 +2668,39 @@
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:21</t>
+          <t>2026-08-30 11:07:19</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Office notarial THIOLLIER Associés, SARL à SAINT-SYMPHORIEN-SUR-COISE (69590) | 16 PLACE DE LA REPUBLIQUE</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr"/>
-      <c r="C35" s="7" t="inlineStr"/>
+          <t>Office notarial TOLLET &amp; VIENNET NOTAIRES à IRIGNY (69540) | 10 Bis Rue Baudrand</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>accueil@oni.notaires.fr</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>accueil@oni.notaires.fr</t>
+        </is>
+      </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>0478484039</t>
+          <t>0478462105</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>0478484039</t>
+          <t>0478462105</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 16 PLACE DE LA REPUBLIQUE 69590 SAINT-SYMPHORIEN-SUR-COISE France</t>
+          <t>Bureau principal 10 Bis Rue Baudrand 69540 IRIGNY France</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>Saint-Symphorien-Sur-Coise</t>
+          <t>Irigny</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/thiollier-associes-sarl</t>
+          <t>https://www.notaires.fr/fr/office/tollet-viennet-notaires</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
@@ -2730,39 +2730,39 @@
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:23</t>
+          <t>2026-08-30 11:07:23</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Office notarial TOLLET &amp; VIENNET NOTAIRES à IRIGNY (69540) | 10 Bis Rue Baudrand</t>
+          <t>Office notarial TRICHET Sarah à LYON (69009) | 20 rue Louis Loucheur</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>accueil@oni.notaires.fr</t>
+          <t>sarah.trichet@notaires.fr</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>accueil@oni.notaires.fr</t>
+          <t>sarah.trichet@notaires.fr</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>0478462105</t>
+          <t>0478472701</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>0478462105</t>
+          <t>0478472701</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 Bis Rue Baudrand 69540 IRIGNY France</t>
+          <t>Bureau principal 20 rue Louis Loucheur 69009 LYON France</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Irigny</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/tollet-viennet-notaires</t>
+          <t>https://www.notaires.fr/fr/office/trichet-sarah</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
@@ -2792,39 +2792,39 @@
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:25</t>
+          <t>2026-08-30 11:07:25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Office notarial TRICHET Sarah à LYON (69009) | 20 rue Louis Loucheur</t>
+          <t>Office notarial VAUDO Johan à DÉCINES-CHARPIEU (69150) | 32 rue de la République</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>sarah.trichet@notaires.fr</t>
+          <t>johan.vaudo@noctua.notaires.fr</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>sarah.trichet@notaires.fr</t>
+          <t>johan.vaudo@noctua.notaires.fr</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>0478472701</t>
+          <t>0422580175</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>0478472701</t>
+          <t>0422580175</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 20 rue Louis Loucheur 69009 LYON France</t>
+          <t>Bureau principal 32 rue de la République 69150 DÉCINES-CHARPIEU France</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Décines-Charpieu</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/trichet-sarah</t>
+          <t>https://www.notaires.fr/fr/office/vaudo-johan</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
@@ -2854,39 +2854,39 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:27</t>
+          <t>2026-08-30 11:07:27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Office notarial VAUDO Johan à DÉCINES-CHARPIEU (69150) | 32 rue de la République</t>
+          <t>Office notarial VICARI, SARL à associé unique à SAINT GERMAIN AU MONT D'OR (69650) | 9 rue de la Combe</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>johan.vaudo@noctua.notaires.fr</t>
+          <t>accueilvicarinotaires@69053.notaires.fr</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>johan.vaudo@noctua.notaires.fr</t>
+          <t>accueilvicarinotaires@69053.notaires.fr</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>0422580175</t>
+          <t>0478912502</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>0422580175</t>
+          <t>0478912502</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 32 rue de la République 69150 DÉCINES-CHARPIEU France</t>
+          <t>Bureau principal 9 rue de la Combe 69650 SAINT GERMAIN AU MONT D'OR France</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Décines-Charpieu</t>
+          <t>Saint Germain Au Mont D'or</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/vaudo-johan</t>
+          <t>https://www.notaires.fr/fr/office/vicari-sarl-associe-unique</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -2916,39 +2916,39 @@
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:28</t>
+          <t>2026-08-30 11:07:29</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Office notarial VICARI, SARL à associé unique à SAINT GERMAIN AU MONT D'OR (69650) | 9 rue de la Combe</t>
+          <t>Office notarial VRIGNAUD Antoine à CHAMPAGNE-AU-MONT-D'OR (69410) | 18 rue Dominique Vincent</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>accueilvicarinotaires@69053.notaires.fr</t>
+          <t>vrignaud.antoine@notaires.fr</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>accueilvicarinotaires@69053.notaires.fr</t>
+          <t>vrignaud.antoine@notaires.fr</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>0478912502</t>
+          <t>0477574535</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>0478912502</t>
+          <t>0477574535</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue de la Combe 69650 SAINT GERMAIN AU MONT D'OR France</t>
+          <t>Bureau principal 18 rue Dominique Vincent 69410 CHAMPAGNE-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>Saint Germain Au Mont D'or</t>
+          <t>Champagne-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/vicari-sarl-associe-unique</t>
+          <t>https://www.notaires.fr/fr/office/vrignaud-antoine</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -2978,39 +2978,39 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:29</t>
+          <t>2026-08-30 11:07:31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Office notarial VRIGNAUD Antoine à CHAMPAGNE-AU-MONT-D'OR (69410) | 18 rue Dominique Vincent</t>
+          <t>Office notarial VULPAT Catherine à LYON (69003) | 53 Cours Richard Vitton</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>vrignaud.antoine@notaires.fr</t>
+          <t>etude.vulpat@notaires.fr</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>vrignaud.antoine@notaires.fr</t>
+          <t>etude.vulpat@notaires.fr</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>0477574535</t>
+          <t>0474705821</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>0477574535</t>
+          <t>0474705821</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 18 rue Dominique Vincent 69410 CHAMPAGNE-AU-MONT-D'OR France</t>
+          <t>Bureau principal 53 Cours Richard Vitton 69003 LYON France</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Champagne-Au-Mont-D'or</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/vrignaud-antoine</t>
+          <t>https://www.notaires.fr/fr/office/vulpat-catherine</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
@@ -3040,39 +3040,39 @@
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:31</t>
+          <t>2026-08-30 11:07:33</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Office notarial VULPAT Catherine à LYON (69003) | 53 Cours Richard Vitton</t>
+          <t>Office notarial WAGENHEIM Adeline à LYON (69001) | 14 rue de l'Arbre Sec</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>etude.vulpat@notaires.fr</t>
+          <t>adeline.wagenheim@gmail.com</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>etude.vulpat@notaires.fr</t>
+          <t>adeline.wagenheim@gmail.com</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>0474705821</t>
+          <t>0618608767</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>0474705821</t>
+          <t>0618608767</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 53 Cours Richard Vitton 69003 LYON France</t>
+          <t>Bureau principal 14 rue de l'Arbre Sec 69001 LYON France</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/vulpat-catherine</t>
+          <t>https://www.notaires.fr/fr/office/wagenheim-adeline</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
@@ -3102,39 +3102,39 @@
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:31</t>
+          <t>2026-08-30 11:07:35</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Office notarial WAGENHEIM Adeline à LYON (69001) | 14 rue de l'Arbre Sec</t>
+          <t>Office notarial SELARL SIMON &amp; CHAMBON-PERUS, NOTAIRES ASSOCIES à LYON (69002) | 6 rue Emile Zola</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>adeline.wagenheim@gmail.com</t>
+          <t>sevane.cazarian@notaires.fr</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>adeline.wagenheim@gmail.com</t>
+          <t>sevane.cazarian@notaires.fr</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>0618608767</t>
+          <t>0478389273</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>0618608767</t>
+          <t>0478389273</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 14 rue de l'Arbre Sec 69001 LYON France</t>
+          <t>Bureau principal 6 rue Emile Zola 69002 LYON France</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/wagenheim-adeline</t>
+          <t>https://www.notaires.fr/fr/office/selarl-simon-chambon-perus-notaires-associes</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
@@ -3164,39 +3164,39 @@
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:33:33</t>
+          <t>2026-08-30 11:06:32</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL SIMON &amp; CHAMBON-PERUS, NOTAIRES ASSOCIES à LYON (69002) | 6 rue Emile Zola</t>
+          <t>Office notarial SELAS BREMENS NOTAIRES à LYON (69006) | 45 quai Charles de Gaulle</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>sevane.cazarian@notaires.fr</t>
+          <t>accueil@groupebremens.notaires.fr</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>sevane.cazarian@notaires.fr</t>
+          <t>accueil@groupebremens.notaires.fr</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>0478389273</t>
+          <t>0472406900</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>0478389273</t>
+          <t>0472406900</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 6 rue Emile Zola 69002 LYON France</t>
+          <t>Bureau principal 45 quai Charles de Gaulle 69006 LYON France</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-simon-chambon-perus-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/selas-bremens-notaires-0</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:51</t>
+          <t>2026-08-30 11:06:48</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:09</t>
+          <t>2026-08-30 11:03:54</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:11</t>
+          <t>2026-08-30 11:03:56</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:12</t>
+          <t>2026-08-30 11:03:58</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:14</t>
+          <t>2026-08-30 11:03:59</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:15</t>
+          <t>2026-08-30 11:04:02</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:17</t>
+          <t>2026-08-30 11:04:04</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:19</t>
+          <t>2026-08-30 11:04:06</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:20</t>
+          <t>2026-08-30 11:04:08</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:22</t>
+          <t>2026-08-30 11:04:10</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:23</t>
+          <t>2026-08-30 11:04:12</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:25</t>
+          <t>2026-08-30 11:04:15</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:26</t>
+          <t>2026-08-30 11:04:18</t>
         </is>
       </c>
     </row>
@@ -4032,39 +4032,39 @@
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:28</t>
+          <t>2026-08-30 11:04:22</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS BREMENS NOTAIRES à LYON (69006) | 45 quai Charles de Gaulle</t>
+          <t>Office notarial SAS a contrario à LYON (69002) | 21 rue Ferrandière</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>accueil@groupebremens.notaires.fr</t>
+          <t>lmancion@acontrario.notaires.fr</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>accueil@groupebremens.notaires.fr</t>
+          <t>lmancion@acontrario.notaires.fr</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>0472406900</t>
+          <t>0478626501</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>0472406900</t>
+          <t>0478626501</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 45 quai Charles de Gaulle 69006 LYON France</t>
+          <t>Bureau principal 21 rue Ferrandière 69002 LYON France</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-bremens-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/sas-contrario-0</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
@@ -4094,39 +4094,39 @@
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:31</t>
+          <t>2026-08-30 11:04:24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS a contrario à LYON (69002) | 21 rue Ferrandière</t>
+          <t>Office notarial SAS des CEDRES à TASSIN-LA-DEMI-LUNE (69160) | 93 avenue du 11 Novembre 1918</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>lmancion@acontrario.notaires.fr</t>
+          <t>etude.69182@notaires.fr</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>lmancion@acontrario.notaires.fr</t>
+          <t>etude.69182@notaires.fr</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>0478626501</t>
+          <t>0437584277</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>0478626501</t>
+          <t>0437584277</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 21 rue Ferrandière 69002 LYON France</t>
+          <t>Bureau principal 93 avenue du 11 Novembre 1918 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-contrario-0</t>
+          <t>https://www.notaires.fr/fr/office/sas-des-cedres</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
@@ -4156,39 +4156,39 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:32</t>
+          <t>2026-08-30 11:04:27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS des CEDRES à TASSIN-LA-DEMI-LUNE (69160) | 93 avenue du 11 Novembre 1918</t>
+          <t>Office notarial SAS EFFICIENCE LYON à LYON (69002) | 50 rue de la République</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>etude.69182@notaires.fr</t>
+          <t>jerome.roche@efficience.notaires.fr</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>etude.69182@notaires.fr</t>
+          <t>jerome.roche@efficience.notaires.fr</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>0437584277</t>
+          <t>0457584348</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>0437584277</t>
+          <t>0457584348</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 93 avenue du 11 Novembre 1918 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 50 rue de la République 69002 LYON France</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-des-cedres</t>
+          <t>https://www.notaires.fr/fr/office/sas-efficience-lyon</t>
         </is>
       </c>
       <c r="K59" s="7" t="inlineStr">
@@ -4218,39 +4218,31 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:34</t>
+          <t>2026-08-30 11:04:29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS EFFICIENCE LYON à LYON (69002) | 50 rue de la République</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>jerome.roche@efficience.notaires.fr</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>jerome.roche@efficience.notaires.fr</t>
-        </is>
-      </c>
+          <t>Office notarial SAS MOREL-VULLIEZ et associées à LYON (69006) | 13 bis place Jules Ferry</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr"/>
+      <c r="C60" s="5" t="inlineStr"/>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>0457584348</t>
+          <t>0481132999</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>0457584348</t>
+          <t>0481132999</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 50 rue de la République 69002 LYON France</t>
+          <t>Bureau principal 13 bis place Jules Ferry 69006 LYON France</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -4270,7 +4262,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-efficience-lyon</t>
+          <t>https://www.notaires.fr/fr/office/sas-morel-vulliez-et-associees</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
@@ -4280,31 +4272,39 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:36</t>
+          <t>2026-08-30 11:04:32</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS MOREL-VULLIEZ et associées à LYON (69006) | 13 bis place Jules Ferry</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr"/>
-      <c r="C61" s="7" t="inlineStr"/>
+          <t>Office notarial SAS NOTAIRES DU VAL DU RHONE à VERNAISON (69390) | 1 Square Cardinal</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>office69041.vernaison@notaires.fr</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>office69041.vernaison@notaires.fr</t>
+        </is>
+      </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>0481132999</t>
+          <t>0478461033</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>0481132999</t>
+          <t>0478461033</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 13 bis place Jules Ferry 69006 LYON France</t>
+          <t>Bureau principal 1 Square Cardinal 69390 VERNAISON France</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Vernaison</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-morel-vulliez-et-associees</t>
+          <t>https://www.notaires.fr/fr/office/sas-notaires-du-val-du-rhone</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
@@ -4334,39 +4334,39 @@
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:37</t>
+          <t>2026-08-30 11:04:34</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SAS NOTAIRES DU VAL DU RHONE à VERNAISON (69390) | 1 Square Cardinal</t>
+          <t>Office notarial SAS NOTLEX à LYON (69003) | 41 rue de Bonnel</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>office69041.vernaison@notaires.fr</t>
+          <t>hugo.rassion@notlex.notaires.fr</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>office69041.vernaison@notaires.fr</t>
+          <t>hugo.rassion@notlex.notaires.fr</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>0478461033</t>
+          <t>0481132385</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>0478461033</t>
+          <t>0481132385</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Square Cardinal 69390 VERNAISON France</t>
+          <t>Bureau principal 41 rue de Bonnel 69003 LYON France</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Vernaison</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-notaires-du-val-du-rhone</t>
+          <t>https://www.notaires.fr/fr/office/sas-notlex-1</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
@@ -4396,39 +4396,39 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:39</t>
+          <t>2026-08-30 11:04:36</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SAS NOTLEX à LYON (69003) | 41 rue de Bonnel</t>
+          <t>Office notarial SCHIBLER-JACQUET et associée à SAINT-PIERRE-DE-CHANDIEU (69780) | 23 place Charles de Gaulle</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>hugo.rassion@notlex.notaires.fr</t>
+          <t>etude.69112@notaires.fr</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>hugo.rassion@notlex.notaires.fr</t>
+          <t>etude.69112@notaires.fr</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>0481132385</t>
+          <t>0478403333</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>0481132385</t>
+          <t>0478403333</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 41 rue de Bonnel 69003 LYON France</t>
+          <t>Bureau principal 23 place Charles de Gaulle 69780 SAINT-PIERRE-DE-CHANDIEU France</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Pierre-De-Chandieu</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sas-notlex-1</t>
+          <t>https://www.notaires.fr/fr/office/schibler-jacquet-et-associee</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
@@ -4458,39 +4458,39 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:40</t>
+          <t>2026-08-30 11:04:37</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SCHIBLER-JACQUET et associée à SAINT-PIERRE-DE-CHANDIEU (69780) | 23 place Charles de Gaulle</t>
+          <t>Office notarial SCP Carole POULAIN-CHARPENTIER, Guillaume BONFILS, Romain THOLON et Caroline SALANSON-BOTTAZZI, notaires associés à LYON (69003) | 144 avenue Maréchal de Saxe</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>etude.69112@notaires.fr</t>
+          <t>notasaxe.69017@notaires.fr</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>etude.69112@notaires.fr</t>
+          <t>notasaxe.69017@notaires.fr</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>0478403333</t>
+          <t>0472847200</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>0478403333</t>
+          <t>0472847200</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 23 place Charles de Gaulle 69780 SAINT-PIERRE-DE-CHANDIEU France</t>
+          <t>Bureau principal 144 avenue Maréchal de Saxe 69003 LYON France</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Saint-Pierre-De-Chandieu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/schibler-jacquet-et-associee</t>
+          <t>https://www.notaires.fr/fr/office/scp-carole-poulain-charpentier-guillaume-bonfils-romain-tholon-et-caroline-salanson-bottazzi-notaires-associes</t>
         </is>
       </c>
       <c r="K64" s="5" t="inlineStr">
@@ -4520,39 +4520,39 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:42</t>
+          <t>2026-08-30 11:04:39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SCP Carole POULAIN-CHARPENTIER, Guillaume BONFILS, Romain THOLON et Caroline SALANSON-BOTTAZZI, notaires associés à LYON (69003) | 144 avenue Maréchal de Saxe</t>
+          <t>Office notarial SCP Emmanuel de BAILLIENCOURT, Christophe RICHARD, Dimitri JANIN et Baptiste FRANCOIS Notaires, associés à LYON (69006) | 10 rue Boileau</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>notasaxe.69017@notaires.fr</t>
+          <t>notaires9republique@notaires.fr</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>notasaxe.69017@notaires.fr</t>
+          <t>notaires9republique@notaires.fr</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>0472847200</t>
+          <t>0478281577</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>0472847200</t>
+          <t>0478281577</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 144 avenue Maréchal de Saxe 69003 LYON France</t>
+          <t>Bureau principal 10 rue Boileau 69006 LYON France</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/scp-carole-poulain-charpentier-guillaume-bonfils-romain-tholon-et-caroline-salanson-bottazzi-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/scp-emmanuel-de-bailliencourt-christophe-richard-dimitri-janin-et-baptiste-francois-notaires-associes</t>
         </is>
       </c>
       <c r="K65" s="7" t="inlineStr">
@@ -4582,39 +4582,39 @@
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:44</t>
+          <t>2026-08-30 11:04:42</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SCP Emmanuel de BAILLIENCOURT, Christophe RICHARD, Dimitri JANIN et Baptiste FRANCOIS Notaires, associés à LYON (69006) | 10 rue Boileau</t>
+          <t>Office notarial SCP Lionel ROBIN et Florence BOACHON, Notaires associés à CALUIRE-ET-CUIRE (69300) | 2 RUE DE MARGNOLLES</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>notaires9republique@notaires.fr</t>
+          <t>etude.robinetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>notaires9republique@notaires.fr</t>
+          <t>etude.robinetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>0478281577</t>
+          <t>0478294310</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>0478281577</t>
+          <t>0478294310</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10 rue Boileau 69006 LYON France</t>
+          <t>Bureau principal 2 RUE DE MARGNOLLES 69300 CALUIRE-ET-CUIRE France</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Caluire-Et-Cuire</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/scp-emmanuel-de-bailliencourt-christophe-richard-dimitri-janin-et-baptiste-francois-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/scp-lionel-robin-et-florence-boachon-notaires-associes</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
@@ -4644,39 +4644,39 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:46</t>
+          <t>2026-08-30 11:04:44</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SCP Lionel ROBIN et Florence BOACHON, Notaires associés à CALUIRE-ET-CUIRE (69300) | 2 RUE DE MARGNOLLES</t>
+          <t>Office notarial SDV NOTAIRES, SELAS à LYON (69003) | 54 cours Lafayette</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>etude.robinetassocies@notaires.fr</t>
+          <t>s.selman@sdv.notaires.fr</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>etude.robinetassocies@notaires.fr</t>
+          <t>s.selman@sdv.notaires.fr</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>0478294310</t>
+          <t>0478793309</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>0478294310</t>
+          <t>0478793309</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2 RUE DE MARGNOLLES 69300 CALUIRE-ET-CUIRE France</t>
+          <t>Bureau principal 54 cours Lafayette 69003 LYON France</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
-          <t>Caluire-Et-Cuire</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/scp-lionel-robin-et-florence-boachon-notaires-associes</t>
+          <t>https://www.notaires.fr/fr/office/sdv-notaires-selas</t>
         </is>
       </c>
       <c r="K67" s="7" t="inlineStr">
@@ -4706,39 +4706,39 @@
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:48</t>
+          <t>2026-08-30 11:04:47</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SDV NOTAIRES, SELAS à LYON (69003) | 54 cours Lafayette</t>
+          <t>Office notarial SEL, NOTAIRES DE CHAPONNAY, SARL à CHAPONNAY (69970) | 22 rue de la Poste</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>s.selman@sdv.notaires.fr</t>
+          <t>notairesdechaponnay@notaires.fr</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>s.selman@sdv.notaires.fr</t>
+          <t>notairesdechaponnay@notaires.fr</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>0478793309</t>
+          <t>0478960403</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>0478793309</t>
+          <t>0478960403</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 54 cours Lafayette 69003 LYON France</t>
+          <t>Bureau principal 22 rue de la Poste 69970 CHAPONNAY France</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chaponnay</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sdv-notaires-selas</t>
+          <t>https://www.notaires.fr/fr/office/sel-notaires-de-chaponnay-sarl</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
@@ -4768,39 +4768,39 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:50</t>
+          <t>2026-08-30 11:04:48</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SEL, NOTAIRES DE CHAPONNAY, SARL à CHAPONNAY (69970) | 22 rue de la Poste</t>
+          <t>Office notarial SELARL 1629 NOTAIRES à LYON (69001) | 9 rue du Bât d'Argent</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>notairesdechaponnay@notaires.fr</t>
+          <t>accueil@1629.notaires.fr</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>notairesdechaponnay@notaires.fr</t>
+          <t>accueil@1629.notaires.fr</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>0478960403</t>
+          <t>0478270290</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>0478960403</t>
+          <t>0478270290</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 22 rue de la Poste 69970 CHAPONNAY France</t>
+          <t>Bureau principal 9 rue du Bât d'Argent 69001 LYON France</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
-          <t>Chaponnay</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sel-notaires-de-chaponnay-sarl</t>
+          <t>https://www.notaires.fr/fr/office/selarl-1629-notaires</t>
         </is>
       </c>
       <c r="K69" s="7" t="inlineStr">
@@ -4830,39 +4830,39 @@
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:50</t>
+          <t>2026-08-30 11:04:50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL 1629 NOTAIRES à LYON (69001) | 9 rue du Bât d'Argent</t>
+          <t>Office notarial SELARL 1979 NOT’ACTES, Notaires à LA MULATIERE à LA MULATIÈRE (69350) | 2A CHEMIN DE LA BASTERO</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>accueil@1629.notaires.fr</t>
+          <t>etude69125.lamulatiere@notaires.fr</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>accueil@1629.notaires.fr</t>
+          <t>etude69125.lamulatiere@notaires.fr</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>0478270290</t>
+          <t>0478500794</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>0478270290</t>
+          <t>0478500794</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue du Bât d'Argent 69001 LYON France</t>
+          <t>Bureau principal 2A CHEMIN DE LA BASTERO 69350 LA MULATIÈRE France</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>La Mulatière</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-1629-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-1979-notactes-notaires-la-mulatiere</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
@@ -4892,39 +4892,39 @@
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:52</t>
+          <t>2026-08-30 11:04:52</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL 1979 NOT’ACTES, Notaires à LA MULATIERE à LA MULATIÈRE (69350) | 2A CHEMIN DE LA BASTERO</t>
+          <t>Office notarial SELARL ACTALION Notaires à LYON (69003) | 1 rue Montébello</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>etude69125.lamulatiere@notaires.fr</t>
+          <t>actalion@notaires.fr</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>etude69125.lamulatiere@notaires.fr</t>
+          <t>actalion@notaires.fr</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>0478500794</t>
+          <t>0478606034</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>0478500794</t>
+          <t>0478606034</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 2A CHEMIN DE LA BASTERO 69350 LA MULATIÈRE France</t>
+          <t>Bureau principal 1 rue Montébello 69003 LYON France</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>La Mulatière</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-1979-notactes-notaires-la-mulatiere</t>
+          <t>https://www.notaires.fr/fr/office/selarl-actalion-notaires-1</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
@@ -4954,39 +4954,39 @@
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:53</t>
+          <t>2026-08-30 11:04:53</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ACTALION Notaires à LYON (69003) | 1 rue Montébello</t>
+          <t>Office notarial SELARL AJC NOTAIRES à CALUIRE-ET-CUIRE (69300) | 13 rue Jean Moulin</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>actalion@notaires.fr</t>
+          <t>alexia.juan@notaires.fr</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>actalion@notaires.fr</t>
+          <t>alexia.juan@notaires.fr</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>0478606034</t>
+          <t>0478088741</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>0478606034</t>
+          <t>0478088741</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Montébello 69003 LYON France</t>
+          <t>Bureau principal 13 rue Jean Moulin 69300 CALUIRE-ET-CUIRE France</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Caluire-Et-Cuire</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-actalion-notaires-1</t>
+          <t>https://www.notaires.fr/fr/office/selarl-ajc-notaires</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
@@ -5016,39 +5016,39 @@
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:55</t>
+          <t>2026-08-30 11:05:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL AJC NOTAIRES à CALUIRE-ET-CUIRE (69300) | 13 rue Jean Moulin</t>
+          <t>Office notarial SELARL ALEXANDRE BRUYERE ET THOMAS BOURLIERE à LYON (69007) | 287 rue de Créqui</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>alexia.juan@notaires.fr</t>
+          <t>accueil.69006@notaires.fr</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>alexia.juan@notaires.fr</t>
+          <t>accueil.69006@notaires.fr</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>0478088741</t>
+          <t>0478422186</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>0478088741</t>
+          <t>0478422186</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 13 rue Jean Moulin 69300 CALUIRE-ET-CUIRE France</t>
+          <t>Bureau principal 287 rue de Créqui 69007 LYON France</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>Caluire-Et-Cuire</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-ajc-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-alexandre-bruyere-et-thomas-bourliere</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
@@ -5078,39 +5078,39 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:00</t>
+          <t>2026-08-30 11:05:01</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ALEXANDRE BRUYERE ET THOMAS BOURLIERE à LYON (69007) | 287 rue de Créqui</t>
+          <t>Office notarial SELARL BCA NOTAIRES à LYON (69002) | 5 place Bellecour</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>accueil.69006@notaires.fr</t>
+          <t>contact.69205@bca.notaires.fr</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>accueil.69006@notaires.fr</t>
+          <t>contact.69205@bca.notaires.fr</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>0478422186</t>
+          <t>0428382030</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>0478422186</t>
+          <t>0428382030</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 287 rue de Créqui 69007 LYON France</t>
+          <t>Bureau principal 5 place Bellecour 69002 LYON France</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-alexandre-bruyere-et-thomas-bourliere</t>
+          <t>https://www.notaires.fr/fr/office/selarl-bca-notaires</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
@@ -5140,39 +5140,39 @@
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:02</t>
+          <t>2026-08-30 11:05:05</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL BCA NOTAIRES à LYON (69002) | 5 place Bellecour</t>
+          <t>Office notarial SELARL CARBONNEL &amp; FREMONT - Notaires à SAINTE-FOY-LÈS-LYON (69110) | 32 avenue Maréchal Foch</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>contact.69205@bca.notaires.fr</t>
+          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>contact.69205@bca.notaires.fr</t>
+          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>0428382030</t>
+          <t>0472413598</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>0428382030</t>
+          <t>0472413598</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 5 place Bellecour 69002 LYON France</t>
+          <t>Bureau principal 32 avenue Maréchal Foch 69110 SAINTE-FOY-LÈS-LYON France</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Sainte-Foy-Lès-Lyon</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-bca-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-carbonnel-fremont-notaires</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -5202,39 +5202,39 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:05</t>
+          <t>2026-08-30 11:05:07</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL CARBONNEL &amp; FREMONT - Notaires à SAINTE-FOY-LÈS-LYON (69110) | 32 avenue Maréchal Foch</t>
+          <t>Office notarial SELARL Caroline MARCHAIS-EPARVIER et Sylvain EPARVIER à TASSIN-LA-DEMI-LUNE (69160) | 169 Avenue Charles de Gaulle</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
+          <t>caroline.marchais-eparvier@notaires.fr</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>mathias.carbonnel@carbonnel-fremont.notaires.fr</t>
+          <t>caroline.marchais-eparvier@notaires.fr</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>0472413598</t>
+          <t>0437465199</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>0472413598</t>
+          <t>0437465199</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 32 avenue Maréchal Foch 69110 SAINTE-FOY-LÈS-LYON France</t>
+          <t>Bureau principal 169 Avenue Charles de Gaulle 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Sainte-Foy-Lès-Lyon</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-carbonnel-fremont-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-caroline-marchais-eparvier-et-sylvain-eparvier</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
@@ -5264,39 +5264,39 @@
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:07</t>
+          <t>2026-08-30 11:05:09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Caroline MARCHAIS-EPARVIER et Sylvain EPARVIER à TASSIN-LA-DEMI-LUNE (69160) | 169 Avenue Charles de Gaulle</t>
+          <t>Office notarial SELARL Des Paroles &amp; Des Actes à LYON (69006) | 111 rue Bugeaud</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>caroline.marchais-eparvier@notaires.fr</t>
+          <t>clement.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>caroline.marchais-eparvier@notaires.fr</t>
+          <t>clement.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>0437465199</t>
+          <t>0474531148</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>0437465199</t>
+          <t>0474531148</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 169 Avenue Charles de Gaulle 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 111 rue Bugeaud 69006 LYON France</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-caroline-marchais-eparvier-et-sylvain-eparvier</t>
+          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:09</t>
+          <t>2026-08-30 11:05:11</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Des Paroles &amp; Des Actes à LYON (69006) | 111 rue Bugeaud</t>
+          <t>Office notarial SELARL Des Paroles &amp; Des Actes à SAINTE-COLOMBE (69560) | 49 rue Paul Doumer</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>clement.janey@rhonactes.notaires.fr</t>
+          <t>eric.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>clement.janey@rhonactes.notaires.fr</t>
+          <t>eric.janey@rhonactes.notaires.fr</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 111 rue Bugeaud 69006 LYON France</t>
+          <t>Bureau principal 49 rue Paul Doumer 69560 SAINTE-COLOMBE France</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Sainte-Colombe</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes</t>
+          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes-0</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
@@ -5388,39 +5388,39 @@
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:10</t>
+          <t>2026-08-30 11:05:13</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Des Paroles &amp; Des Actes à SAINTE-COLOMBE (69560) | 49 rue Paul Doumer</t>
+          <t>Office notarial SELARL ENTANDEM NOTAIRES à SAINT-GERMAIN-AU-MONT-D'OR (69650) | 1 A Place de l'Esplanade</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>eric.janey@rhonactes.notaires.fr</t>
+          <t>s.vacher@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>eric.janey@rhonactes.notaires.fr</t>
+          <t>s.vacher@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>0474531148</t>
+          <t>0428380640</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>0474531148</t>
+          <t>0428380640</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 49 rue Paul Doumer 69560 SAINTE-COLOMBE France</t>
+          <t>Bureau principal 1 A Place de l'Esplanade 69650 SAINT-GERMAIN-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
@@ -5435,12 +5435,12 @@
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>Sainte-Colombe</t>
+          <t>Saint-Germain-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-des-paroles-des-actes-0</t>
+          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
@@ -5450,39 +5450,39 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:12</t>
+          <t>2026-08-30 11:05:15</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ENTANDEM NOTAIRES à SAINT-GERMAIN-AU-MONT-D'OR (69650) | 1 A Place de l'Esplanade</t>
+          <t>Office notarial SELARL ENTANDEM NOTAIRES à LYON (69006) | 50 cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>s.vacher@entandem.notaires.fr</t>
+          <t>office@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>s.vacher@entandem.notaires.fr</t>
+          <t>office@entandem.notaires.fr</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>0428380640</t>
+          <t>0428382230</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>0428380640</t>
+          <t>0428382230</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 A Place de l'Esplanade 69650 SAINT-GERMAIN-AU-MONT-D'OR France</t>
+          <t>Bureau principal 50 cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Saint-Germain-Au-Mont-D'or</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires-0</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -5512,39 +5512,39 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:14</t>
+          <t>2026-08-30 11:05:17</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ENTANDEM NOTAIRES à LYON (69006) | 50 cours Franklin Roosevelt</t>
+          <t>Office notarial SELARL ETUDE BLANC à OULLINS-PIERRE-BÉNITE - OULLINS (69600) | 1 boulevard Emile Zola</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>office@entandem.notaires.fr</t>
+          <t>etude.blanc@notaires.fr</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>office@entandem.notaires.fr</t>
+          <t>etude.blanc@notaires.fr</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>0428382230</t>
+          <t>0478513155</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>0428382230</t>
+          <t>0478513155</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 50 cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 1 boulevard Emile Zola 69600 OULLINS-PIERRE-BÉNITE - OULLINS France</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Oullins-Pierre-Bénite - Oullins</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-entandem-notaires-0</t>
+          <t>https://www.notaires.fr/fr/office/selarl-etude-blanc</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -5574,39 +5574,39 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:15</t>
+          <t>2026-08-30 11:05:20</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL ETUDE BLANC à OULLINS-PIERRE-BÉNITE - OULLINS (69600) | 1 boulevard Emile Zola</t>
+          <t>Office notarial SELARL Fideis Notaires à SAINTE-FOY-LÈS-LYON (69110) | 18 Place Xavier Ricard</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>etude.blanc@notaires.fr</t>
+          <t>contact@fideis.notaires.fr</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>etude.blanc@notaires.fr</t>
+          <t>contact@fideis.notaires.fr</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>0478513155</t>
+          <t>0472329065</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>0478513155</t>
+          <t>0472329065</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 boulevard Emile Zola 69600 OULLINS-PIERRE-BÉNITE - OULLINS France</t>
+          <t>Bureau principal 18 Place Xavier Ricard 69110 SAINTE-FOY-LÈS-LYON France</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
-          <t>Oullins-Pierre-Bénite - Oullins</t>
+          <t>Sainte-Foy-Lès-Lyon</t>
         </is>
       </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-etude-blanc</t>
+          <t>https://www.notaires.fr/fr/office/selarl-fideis-notaires</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
@@ -5636,39 +5636,39 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:16</t>
+          <t>2026-08-30 11:05:26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Fideis Notaires à SAINTE-FOY-LÈS-LYON (69110) | 18 Place Xavier Ricard</t>
+          <t>Office notarial SELARL GAUMIER NOTAIRES à LYON (69009) | 18 quai Jaÿr</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>contact@fideis.notaires.fr</t>
+          <t>matthieu.gaumier@notaires.fr</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>contact@fideis.notaires.fr</t>
+          <t>matthieu.gaumier@notaires.fr</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>0472329065</t>
+          <t>0472197508</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>0472329065</t>
+          <t>0472197508</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 18 Place Xavier Ricard 69110 SAINTE-FOY-LÈS-LYON France</t>
+          <t>Bureau principal 18 quai Jaÿr 69009 LYON France</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>Sainte-Foy-Lès-Lyon</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-fideis-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-gaumier-notaires</t>
         </is>
       </c>
       <c r="K83" s="7" t="inlineStr">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:18</t>
+          <t>2026-08-30 11:05:28</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL GAUMIER NOTAIRES à LYON (69009) | 18 quai Jaÿr</t>
+          <t>Office notarial SELARL Jean-Christophe HOCHE, Maxime CASTELLI et Denis MESTRALLET, Notaires des crus à VILLEFRANCHE-SUR-SAÔNE (69400) | 248 rue de la Paix</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>matthieu.gaumier@notaires.fr</t>
+          <t>notairesdescrus@ndc.notaires.fr</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>matthieu.gaumier@notaires.fr</t>
+          <t>notairesdescrus@ndc.notaires.fr</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>0472197508</t>
+          <t>0474042486</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>0472197508</t>
+          <t>0474042486</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 18 quai Jaÿr 69009 LYON France</t>
+          <t>Bureau principal 248 rue de la Paix 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-gaumier-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-jean-christophe-hoche-maxime-castelli-et-denis-mestrallet-notaires-des-crus</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
@@ -5760,39 +5760,39 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:20</t>
+          <t>2026-08-30 11:05:33</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SELARL Jean-Christophe HOCHE, Maxime CASTELLI et Denis MESTRALLET, Notaires des crus à VILLEFRANCHE-SUR-SAÔNE (69400) | 248 rue de la Paix</t>
+          <t>Office notarial SELARL LEMBREZ et Associés, Notaires à LYON (69004) | 5 rue Duviard</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>notairesdescrus@ndc.notaires.fr</t>
+          <t>simon.thiriat@lembrez.notaires.fr</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>notairesdescrus@ndc.notaires.fr</t>
+          <t>simon.thiriat@lembrez.notaires.fr</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>0474042486</t>
+          <t>0426316958</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>0474042486</t>
+          <t>0426316958</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 248 rue de la Paix 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 5 rue Duviard 69004 LYON France</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-jean-christophe-hoche-maxime-castelli-et-denis-mestrallet-notaires-des-crus</t>
+          <t>https://www.notaires.fr/fr/office/selarl-lembrez-et-associes-notaires</t>
         </is>
       </c>
       <c r="K85" s="7" t="inlineStr">
@@ -5822,39 +5822,39 @@
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:24</t>
+          <t>2026-08-30 11:05:35</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SELARL LEMBREZ et Associés, Notaires à LYON (69004) | 5 rue Duviard</t>
+          <t>Office notarial SELARL NOTAIRES CONDRIEU à CONDRIEU (69420) | 40 rue des Granges</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>simon.thiriat@lembrez.notaires.fr</t>
+          <t>notairescondrieu@69036.notaires.fr</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>simon.thiriat@lembrez.notaires.fr</t>
+          <t>notairescondrieu@69036.notaires.fr</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>0426316958</t>
+          <t>0474595233</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>0426316958</t>
+          <t>0474595233</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 5 rue Duviard 69004 LYON France</t>
+          <t>Bureau principal 40 rue des Granges 69420 CONDRIEU France</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Condrieu</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/selarl-lembrez-et-associes-notaires</t>
+          <t>https://www.notaires.fr/fr/office/selarl-notaires-condrieu</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:25</t>
+          <t>2026-08-30 11:05:42</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:59</t>
+          <t>2026-08-30 11:04:58</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:21</t>
+          <t>2026-08-30 11:05:29</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:22</t>
+          <t>2026-08-30 11:05:31</t>
         </is>
       </c>
     </row>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:03</t>
+          <t>2026-08-30 11:05:03</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:27</t>
+          <t>2026-08-30 11:05:37</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:32:28</t>
+          <t>2026-08-30 11:05:40</t>
         </is>
       </c>
     </row>
@@ -6318,39 +6318,39 @@
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:57</t>
+          <t>2026-08-30 11:04:55</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Office notarial Office Notarial des Jacobins, SAS à LYON (69002) | 8 place des Jacobins</t>
+          <t>Office notarial MARIOTTE Stéphanie à LYON (69006) | 10 Boulevard Jules Favre</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>office.jacobins.lyon@69004.notaires.fr</t>
+          <t>stephanie.mariotte@notaires.fr</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>office.jacobins.lyon@69004.notaires.fr</t>
+          <t>stephanie.mariotte@notaires.fr</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>0478371744</t>
+          <t>0481060795</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>0478371744</t>
+          <t>0481060795</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 8 place des Jacobins 69002 LYON France</t>
+          <t>Bureau principal 10 Boulevard Jules Favre 69006 LYON France</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-des-jacobins-sas</t>
+          <t>https://www.notaires.fr/fr/office/mariotte-stephanie</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
@@ -6380,39 +6380,39 @@
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:20</t>
+          <t>2026-08-30 11:02:15</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DU PAYS ARBRESLOIS, SELARL à L'ARBRESLE (69210) | 54, rue Claude Terrasse</t>
+          <t>Office notarial MATA Victoria à LYON (69008) | 310 Avenue Berthelot</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>office.larbresle@onpa.notaires.fr</t>
+          <t>victoria.mata@notaires.fr</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>office.larbresle@onpa.notaires.fr</t>
+          <t>victoria.mata@notaires.fr</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>0474010014</t>
+          <t>0472780290</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>0474010014</t>
+          <t>0472780290</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 54, rue Claude Terrasse 69210 L'ARBRESLE France</t>
+          <t>Bureau principal 310 Avenue Berthelot 69008 LYON France</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
-          <t>L'arbresle</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-du-pays-arbreslois-selarl</t>
+          <t>https://www.notaires.fr/fr/office/mata-victoria</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -6442,39 +6442,39 @@
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:22</t>
+          <t>2026-08-30 11:02:17</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE ROOSEVELT et associés, SELARL à LYON (69006) | 24 Cours Franklin Roosevelt</t>
+          <t>Office notarial MAUGAIN NOTAIRES, SELARL à LYON (69003) | 34 cours Lafayette</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>scp.bronnert@notaires.fr</t>
+          <t>bertram.julienne@notaires.fr</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>scp.bronnert@notaires.fr</t>
+          <t>bertram.julienne@notaires.fr</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>0472838080</t>
+          <t>0472130397</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>0472838080</t>
+          <t>0472130397</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 24 Cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 34 cours Lafayette 69003 LYON France</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="J96" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-roosevelt-et-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/maugain-notaires-selarl</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
@@ -6504,39 +6504,39 @@
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:23</t>
+          <t>2026-08-30 11:02:19</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Office notarial ONPC NOTAIRES, SELARL à LYON (69006) | 58 rue Tête d'Or</t>
+          <t>Office notarial MERMET Pierre à LIMAS (69400) | 84 rue Henri Dépagneux</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
+          <t>pierre.mermet@notaires.fr</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
+          <t>pierre.mermet@notaires.fr</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>0481098330</t>
+          <t>0474045153</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>0481098330</t>
+          <t>0474045153</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 58 rue Tête d'Or 69006 LYON France</t>
+          <t>Bureau principal 84 rue Henri Dépagneux 69400 LIMAS France</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Limas</t>
         </is>
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/onpc-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/mermet-pierre</t>
         </is>
       </c>
       <c r="K97" s="7" t="inlineStr">
@@ -6566,39 +6566,39 @@
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:25</t>
+          <t>2026-08-30 11:02:22</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PARISET, Notaire, SARL à LYON (69001) | 2 rue de Provence</t>
+          <t>Office notarial MESSERI Aurore à LYON (69003) | 6 cours de la Liberté</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>scp.paillard-pariset@notaires.fr</t>
+          <t>aurore.messeri@notaires.fr</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>scp.paillard-pariset@notaires.fr</t>
+          <t>aurore.messeri@notaires.fr</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>0472982798</t>
+          <t>0481061360</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>0472982798</t>
+          <t>0481061360</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 2 rue de Provence 69001 LYON France</t>
+          <t>Bureau principal 6 cours de la Liberté 69003 LYON France</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pariset-notaire-sarl</t>
+          <t>https://www.notaires.fr/fr/office/messeri-aurore</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
@@ -6628,39 +6628,39 @@
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:26</t>
+          <t>2026-08-30 11:02:24</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PARTOUCHE Sébastien à LISSIEU (69380) | 101 Route Nationale 6</t>
+          <t>Office notarial MONTEL Hélène à VERNAISON (69390) | 336 rue de la Fée des Eaux</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>sebastien.partouche@notaires.fr</t>
+          <t>h.montel@notaires.fr</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>sebastien.partouche@notaires.fr</t>
+          <t>h.montel@notaires.fr</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>0472599128</t>
+          <t>0482531832</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>0472599128</t>
+          <t>0482531832</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 101 Route Nationale 6 69380 LISSIEU France</t>
+          <t>Bureau principal 336 rue de la Fée des Eaux 69390 VERNAISON France</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
-          <t>Lissieu</t>
+          <t>Vernaison</t>
         </is>
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/partouche-sebastien</t>
+          <t>https://www.notaires.fr/fr/office/montel-helene</t>
         </is>
       </c>
       <c r="K99" s="7" t="inlineStr">
@@ -6690,39 +6690,39 @@
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:27</t>
+          <t>2026-08-30 11:02:27</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PAUL &amp; associés – Notaires Lyon, SELAS à LYON (69009) | 28 rue Joannès Carret</t>
+          <t>Office notarial MOREL Laetitia à LYON (69003) | 127 cours du Docteur Long</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>corinne.nicolle@notaires.fr</t>
+          <t>morel.laetitia@notaires.fr</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>corinne.nicolle@notaires.fr</t>
+          <t>morel.laetitia@notaires.fr</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>0412054740</t>
+          <t>0481061095</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>0412054740</t>
+          <t>0481061095</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 28 rue Joannès Carret 69009 LYON France</t>
+          <t>Bureau principal 127 cours du Docteur Long 69003 LYON France</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/paul-associes-notaires-lyon-selas</t>
+          <t>https://www.notaires.fr/fr/office/morel-laetitia</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
@@ -6752,39 +6752,39 @@
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:29</t>
+          <t>2026-08-30 11:02:29</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PCMV NOTAIRES, SARL à LYON (69004) | 18/19 Place de la Croix Rousse</t>
+          <t>Office notarial MURANA-CHARLUET Raphaëlle à SAINT-DIDIER-AU-MONT-D'OR (69370) | 11 rue Voie Lactée</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>office@pcmv.notaires.fr</t>
+          <t>r.murana@notaires.fr</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>office@pcmv.notaires.fr</t>
+          <t>r.murana@notaires.fr</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>0437408084</t>
+          <t>0485680145</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>0437408084</t>
+          <t>0485680145</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 18/19 Place de la Croix Rousse 69004 LYON France</t>
+          <t>Bureau principal 11 rue Voie Lactée 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Didier-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pcmv-notaires-sarl</t>
+          <t>https://www.notaires.fr/fr/office/murana-charluet-raphaelle</t>
         </is>
       </c>
       <c r="K101" s="7" t="inlineStr">
@@ -6814,31 +6814,39 @@
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:31</t>
+          <t>2026-08-30 11:02:31</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PERRAUD &amp; Associés - Notaires, SAS à LYON (69003) | 19 boulevard Eugène Deruelle</t>
+          <t>Office notarial MURAT Marie-Pierre à VILLEURBANNE (69100) | 109 Cours Emile Zola</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>perraud.lyon@notaires.fr</t>
+          <t>office.murat@notaires.fr</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>perraud.lyon@notaires.fr</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr"/>
-      <c r="E102" s="5" t="inlineStr"/>
+          <t>office.murat@notaires.fr</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>0437431922</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>0437431922</t>
+        </is>
+      </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 19 boulevard Eugène Deruelle 69003 LYON France</t>
+          <t>Bureau principal 109 Cours Emile Zola 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
@@ -6853,12 +6861,12 @@
       </c>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/perraud-associes-notaires-sas-0</t>
+          <t>https://www.notaires.fr/fr/office/murat-marie-pierre</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
@@ -6868,39 +6876,39 @@
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:32</t>
+          <t>2026-08-30 11:02:33</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PESSIA Faustine à DOMMARTIN (69380) | 1702 route des Bois</t>
+          <t>Office notarial NARDINI Magali à CHAZAY-D'AZERGUES (69380) | 9 rue Marius Berliet</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>faustine.pessia@69072.notaires.fr</t>
+          <t>office.nardini@notaires.fr</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>faustine.pessia@69072.notaires.fr</t>
+          <t>office.nardini@notaires.fr</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>04.86.11.05.15</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>0000000000</t>
+          <t>04.86.11.05.15</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1702 route des Bois 69380 DOMMARTIN France</t>
+          <t>Bureau principal 9 rue Marius Berliet 69380 CHAZAY-D'AZERGUES France</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
@@ -6915,12 +6923,12 @@
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
-          <t>Dommartin</t>
+          <t>Chazay-D'azergues</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/pessia-faustine</t>
+          <t>https://www.notaires.fr/fr/office/nardini-magali</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr">
@@ -6930,39 +6938,39 @@
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:34</t>
+          <t>2026-08-30 11:02:36</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Office notarial PICOT Laura à LYON (69006) | 63 rue Boileau</t>
+          <t>Office notarial NICOLLE et associés à LYON (69003) | 90 rue Paul Bert</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>laura.picot@69212.notaires.fr</t>
+          <t>christian.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>laura.picot@69212.notaires.fr</t>
+          <t>christian.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>0478133758</t>
+          <t>0492309230</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>0478133758</t>
+          <t>0492309230</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 63 rue Boileau 69006 LYON France</t>
+          <t>Bureau principal 90 rue Paul Bert 69003 LYON France</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
@@ -6982,7 +6990,7 @@
       </c>
       <c r="J104" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/picot-laura</t>
+          <t>https://www.notaires.fr/fr/office/nicolle-et-associes-0</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
@@ -6992,39 +7000,39 @@
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:36</t>
+          <t>2026-08-30 11:02:38</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Office notarial PROUVOST-CLAEYS, SAS à associé unique à L'ARBRESLE (69210) | 193 Route de Sain-Bel</t>
+          <t>Office notarial NOHARET Françoise à LYON (69007) | 200 AVENUE JEAN JAURES</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>louise.prouvost@69209.notaires.fr</t>
+          <t>office.noharet@notaires.fr</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>louise.prouvost@69209.notaires.fr</t>
+          <t>office.noharet@notaires.fr</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>0428299066</t>
+          <t>0437376850</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>0428299066</t>
+          <t>0437376850</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 193 Route de Sain-Bel 69210 L'ARBRESLE France</t>
+          <t>Bureau principal 200 AVENUE JEAN JAURES 69007 LYON France</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
@@ -7039,12 +7047,12 @@
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
-          <t>L'arbresle</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/prouvost-claeys-sas-associe-unique</t>
+          <t>https://www.notaires.fr/fr/office/noharet-francoise</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
@@ -7054,39 +7062,39 @@
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:38</t>
+          <t>2026-08-30 11:02:40</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Office notarial RAY et associé, SELARL à SAINT-FONS (69190) | 1 Avenue Jean Jaurès</t>
+          <t>Office notarial NOT’ACTES MARCY à MARCY (69480) | 20, Rue de la Tour</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>ray.sassard@notaires.fr</t>
+          <t>renaud.fontaine@69169.notaires.fr</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>ray.sassard@notaires.fr</t>
+          <t>renaud.fontaine@69169.notaires.fr</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>0478700047</t>
+          <t>0437552285</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>0478700047</t>
+          <t>0437552285</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Avenue Jean Jaurès 69190 SAINT-FONS France</t>
+          <t>Bureau principal 20, Rue de la Tour 69480 MARCY France</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
@@ -7101,12 +7109,12 @@
       </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
-          <t>Saint-Fons</t>
+          <t>Marcy</t>
         </is>
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/ray-et-associe-selarl</t>
+          <t>https://www.notaires.fr/fr/office/notactes-marcy</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr">
@@ -7116,39 +7124,39 @@
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:39</t>
+          <t>2026-08-30 11:02:42</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Office notarial REAL LEX Notaires à CRAPONNE (69290) | 123 AVENUE PIERRE DUMOND</t>
+          <t>Office notarial NOTAEM et associés à SAINT-CYR-AU-MONT-D'OR (69450) | 1 rue Reynier</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>office69066.craponne@notaires.fr</t>
+          <t>notaem@notaem.notaires.fr</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>office69066.craponne@notaires.fr</t>
+          <t>notaem@notaem.notaires.fr</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>0478578039</t>
+          <t>0478472483</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>0478578039</t>
+          <t>0478472483</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 123 AVENUE PIERRE DUMOND 69290 CRAPONNE France</t>
+          <t>Bureau principal 1 rue Reynier 69450 SAINT-CYR-AU-MONT-D'OR France</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
@@ -7163,12 +7171,12 @@
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>Craponne</t>
+          <t>Saint-Cyr-Au-Mont-D'or</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/real-lex-notaires</t>
+          <t>https://www.notaires.fr/fr/office/notaem-et-associes</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
@@ -7178,39 +7186,39 @@
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:41</t>
+          <t>2026-08-30 11:02:44</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>Office notarial REBOTIER PERET LEVRAULT ET MERLE NOTAIRES ASSOCIES, SELARL à LYON (69009) | 2 boulevard Antoine de Saint Exupéry</t>
+          <t>Office notarial NOTAIRES GAMBETTA à VILLEFRANCHE-SUR-SAÔNE (69400) | 257 rue Boiron</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>notaires.vaise@notaires.fr</t>
+          <t>secretariat@etudegambetta.notaires.fr</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>notaires.vaise@notaires.fr</t>
+          <t>secretariat@etudegambetta.notaires.fr</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>0478646749</t>
+          <t>0474029910</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>0478646749</t>
+          <t>0474029910</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 2 boulevard Antoine de Saint Exupéry 69009 LYON France</t>
+          <t>Bureau principal 257 rue Boiron 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
@@ -7225,12 +7233,12 @@
       </c>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rebotier-peret-levrault-et-merle-notaires-associes-selarl</t>
+          <t>https://www.notaires.fr/fr/office/notaires-gambetta</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
@@ -7240,39 +7248,39 @@
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:43</t>
+          <t>2026-08-30 11:02:47</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Office notarial RENETEAU Anaïs à CHAPONOST (69630) | 1 Route des Troques</t>
+          <t>Office notarial NOTARA à LYON (69007) | 152 Grande Rue de la Guillotière</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>anais.reneteau@reneteau.notaires.fr</t>
+          <t>notara.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>anais.reneteau@reneteau.notaires.fr</t>
+          <t>notara.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>0478563572</t>
+          <t>0983211434</t>
         </is>
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>0478563572</t>
+          <t>0983211434</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 1 Route des Troques 69630 CHAPONOST France</t>
+          <t>Bureau principal 152 Grande Rue de la Guillotière 69007 LYON France</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
@@ -7287,12 +7295,12 @@
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>Chaponost</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/reneteau-anais</t>
+          <t>https://www.notaires.fr/fr/office/notara</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -7302,39 +7310,39 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:44</t>
+          <t>2026-08-30 11:02:48</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>Office notarial REY Karyne à LYON (69002) | 3 rue Victor Hugo</t>
+          <t>Office notarial ODO, notaire à THIZY-LES-BOURGS (69240) | 47 RUE JEAN JAURES</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>etude.rey@notaires.fr</t>
+          <t>notaires.thizy@notaires.fr</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>etude.rey@notaires.fr</t>
+          <t>notaires.thizy@notaires.fr</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>0472162590</t>
+          <t>0474640048</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>0472162590</t>
+          <t>0474640048</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 3 rue Victor Hugo 69002 LYON France</t>
+          <t>Bureau principal 47 RUE JEAN JAURES 69240 THIZY-LES-BOURGS France</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
@@ -7349,12 +7357,12 @@
       </c>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Thizy-Les-Bourgs</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rey-karyne</t>
+          <t>https://www.notaires.fr/fr/office/odo-notaire</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
@@ -7364,39 +7372,39 @@
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:45</t>
+          <t>2026-08-30 11:02:49</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Office notarial ROBIN Axel à LYON (69003) | 123 cours Albert Thomas</t>
+          <t>Office notarial OFFICE NOTARIAL DE PRESSENSE, SELARL à VILLEURBANNE (69100) | 46 rue Francis de Pressensé</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>etude@69047.notaires.fr</t>
+          <t>helene.geraud@notaires.fr</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>etude@69047.notaires.fr</t>
+          <t>helene.geraud@notaires.fr</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>0449232420</t>
+          <t>0437482561</t>
         </is>
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>0449232420</t>
+          <t>0437482561</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 123 cours Albert Thomas 69003 LYON France</t>
+          <t>Bureau principal 46 rue Francis de Pressensé 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
@@ -7411,12 +7419,12 @@
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J111" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/robin-axel</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-de-pressense-selarl</t>
         </is>
       </c>
       <c r="K111" s="7" t="inlineStr">
@@ -7426,39 +7434,39 @@
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:47</t>
+          <t>2026-08-30 11:02:51</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>Office notarial ROCHELOIS LYON, SELAS à LYON (69003) | 10-12 boulevard Marius Vivier Merle</t>
+          <t>Office notarial OFFICE NOTARIAL DES CHARPENNES-VILLEURBANNE, SELARL à VILLEURBANNE (69100) | 50 A Cours Emile Zola</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>contact@rocheloislyon.notaires.fr</t>
+          <t>oncv@69136.notaires.fr</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>contact@rocheloislyon.notaires.fr</t>
+          <t>oncv@69136.notaires.fr</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>0487658201</t>
+          <t>0472759396</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>0487658201</t>
+          <t>0472759396</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 10-12 boulevard Marius Vivier Merle 69003 LYON France</t>
+          <t>Bureau principal 50 A Cours Emile Zola 69100 VILLEURBANNE France</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
@@ -7473,12 +7481,12 @@
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Villeurbanne</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rochelois-lyon-selas</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-des-charpennes-villeurbanne-selarl</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
@@ -7488,39 +7496,39 @@
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:48</t>
+          <t>2026-08-30 11:02:53</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à LYON (69003) | 40 Rue Antoine Charial</t>
+          <t>Office notarial Office Notarial des Jacobins, SAS à LYON (69002) | 8 place des Jacobins</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>corine.mussio@notaires.fr</t>
+          <t>office.jacobins.lyon@69004.notaires.fr</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>corine.mussio@notaires.fr</t>
+          <t>office.jacobins.lyon@69004.notaires.fr</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>0472459539</t>
+          <t>0478371744</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>0472459539</t>
+          <t>0478371744</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 40 Rue Antoine Charial 69003 LYON France</t>
+          <t>Bureau principal 8 place des Jacobins 69002 LYON France</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
@@ -7540,7 +7548,7 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/rostaing-mussio-et-associee-selarl-0</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-des-jacobins-sas</t>
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr">
@@ -7550,39 +7558,39 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:49</t>
+          <t>2026-08-30 11:02:54</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>Office notarial RUCHON Edouard à LYON (69005) | 60 avenue du Point du Jour</t>
+          <t>Office notarial OFFICE NOTARIAL DU PAYS ARBRESLOIS, SELARL à L'ARBRESLE (69210) | 54, rue Claude Terrasse</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>edouard.ruchon@notaires.fr</t>
+          <t>office.larbresle@onpa.notaires.fr</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>edouard.ruchon@notaires.fr</t>
+          <t>office.larbresle@onpa.notaires.fr</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>0472544808</t>
+          <t>0474010014</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>0472544808</t>
+          <t>0474010014</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 60 avenue du Point du Jour 69005 LYON France</t>
+          <t>Bureau principal 54, rue Claude Terrasse 69210 L'ARBRESLE France</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
@@ -7597,12 +7605,12 @@
       </c>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>L'arbresle</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/ruchon-edouard</t>
+          <t>https://www.notaires.fr/fr/office/office-notarial-du-pays-arbreslois-selarl</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
@@ -7612,39 +7620,39 @@
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:50</t>
+          <t>2026-08-30 11:02:56</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Office notarial S2R NOTAIRES CONSEILS, SELARL à LYON (69006) | 50 boulevard des Belges</t>
+          <t>Office notarial OFFICE ROOSEVELT et associés, SELARL à LYON (69006) | 24 Cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>simon.reboul@69225.notaires.fr</t>
+          <t>scp.bronnert@notaires.fr</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>simon.reboul@69225.notaires.fr</t>
+          <t>scp.bronnert@notaires.fr</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>0437479982</t>
+          <t>0472838080</t>
         </is>
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>0437479982</t>
+          <t>0472838080</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 50 boulevard des Belges 69006 LYON France</t>
+          <t>Bureau principal 24 Cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
@@ -7664,7 +7672,7 @@
       </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/s2r-notaires-conseils-selarl</t>
+          <t>https://www.notaires.fr/fr/office/office-roosevelt-et-associes-selarl</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr">
@@ -7674,39 +7682,39 @@
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:52</t>
+          <t>2026-08-30 11:02:58</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SALAGNAT Frédéric à CHASSIEU (69680) | 56 route de Genas</t>
+          <t>Office notarial ONPC NOTAIRES, SELARL à LYON (69006) | 58 rue Tête d'Or</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>salagnat@notaires.fr</t>
+          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>salagnat@notaires.fr</t>
+          <t>alexandre.kleinhans@onpc-lyon.notaires.fr</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>0472797470</t>
+          <t>0481098330</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>0472797470</t>
+          <t>0481098330</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 56 route de Genas 69680 CHASSIEU France</t>
+          <t>Bureau principal 58 rue Tête d'Or 69006 LYON France</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
@@ -7721,12 +7729,12 @@
       </c>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>Chassieu</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/salagnat-frederic</t>
+          <t>https://www.notaires.fr/fr/office/onpc-notaires-selarl</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
@@ -7736,39 +7744,39 @@
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:54</t>
+          <t>2026-08-30 11:03:00</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SALICHON &amp; ASSOCIES, SARL à LYON (69006) | 3 Cours Franklin Roosevelt</t>
+          <t>Office notarial PARISET, Notaire, SARL à LYON (69001) | 2 rue de Provence</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>salichonetassocies@notaires.fr</t>
+          <t>scp.paillard-pariset@notaires.fr</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>salichonetassocies@notaires.fr</t>
+          <t>scp.paillard-pariset@notaires.fr</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>0478931098</t>
+          <t>0472982798</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>0478931098</t>
+          <t>0472982798</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 3 Cours Franklin Roosevelt 69006 LYON France</t>
+          <t>Bureau principal 2 rue de Provence 69001 LYON France</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
@@ -7788,7 +7796,7 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/salichon-associes-sarl</t>
+          <t>https://www.notaires.fr/fr/office/pariset-notaire-sarl</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
@@ -7798,39 +7806,39 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:56</t>
+          <t>2026-08-30 11:03:02</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique GONDRAN, notaire associée à BELLEVILLE (69220) | 19 rue des Remparts</t>
+          <t>Office notarial PARTOUCHE Sébastien à LISSIEU (69380) | 101 Route Nationale 6</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>anne.gondran@69248.notaires.fr</t>
+          <t>sebastien.partouche@notaires.fr</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>anne.gondran@69248.notaires.fr</t>
+          <t>sebastien.partouche@notaires.fr</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>04 87 01 02 10</t>
+          <t>0472599128</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>04 87 01 02 10</t>
+          <t>0472599128</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 19 rue des Remparts 69220 BELLEVILLE France</t>
+          <t>Bureau principal 101 Route Nationale 6 69380 LISSIEU France</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
@@ -7845,12 +7853,12 @@
       </c>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>Belleville</t>
+          <t>Lissieu</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-gondran-notaire-associee</t>
+          <t>https://www.notaires.fr/fr/office/partouche-sebastien</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
@@ -7860,39 +7868,39 @@
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:58</t>
+          <t>2026-08-30 11:03:03</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique Notaires du Promenoir à VILLEFRANCHE-SUR-SAÔNE (69400) | 61 rue d'Anse</t>
+          <t>Office notarial PAUL &amp; associés – Notaires Lyon, SELAS à LYON (69009) | 28 rue Joannès Carret</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>etude@promenoir.notaires.fr</t>
+          <t>corinne.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>etude@promenoir.notaires.fr</t>
+          <t>corinne.nicolle@notaires.fr</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>0474654500</t>
+          <t>0412054740</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>0474654500</t>
+          <t>0412054740</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 61 rue d'Anse 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 28 rue Joannès Carret 69009 LYON France</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
@@ -7907,12 +7915,12 @@
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-notaires-du-promenoir</t>
+          <t>https://www.notaires.fr/fr/office/paul-associes-notaires-lyon-selas</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
@@ -7922,39 +7930,39 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:00</t>
+          <t>2026-08-30 11:03:05</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associé unique OFFICE NOTARIAL DE LA TABLE DE PIERRE à FRANCHEVILLE (69340) | 26 Avenue de la Table de Pierre</t>
+          <t>Office notarial PCMV NOTAIRES, SARL à LYON (69004) | 18/19 Place de la Croix Rousse</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>christelle.farce@69220.notaires.fr</t>
+          <t>office@pcmv.notaires.fr</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>christelle.farce@69220.notaires.fr</t>
+          <t>office@pcmv.notaires.fr</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>0437202524</t>
+          <t>0437408084</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>0437202524</t>
+          <t>0437408084</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 26 Avenue de la Table de Pierre 69340 FRANCHEVILLE France</t>
+          <t>Bureau principal 18/19 Place de la Croix Rousse 69004 LYON France</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
@@ -7969,12 +7977,12 @@
       </c>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>Francheville</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-office-notarial-de-la-table-de-pierre</t>
+          <t>https://www.notaires.fr/fr/office/pcmv-notaires-sarl</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
@@ -7984,39 +7992,31 @@
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:01</t>
+          <t>2026-08-30 11:03:07</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL à associée unique NOTAIRE VALLE D'AZERGUES à LAMURE-SUR-AZERGUES (69870) | 10 impasse Chavanet</t>
+          <t>Office notarial PERRAUD &amp; Associés - Notaires, SAS à LYON (69003) | 19 boulevard Eugène Deruelle</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>office@69095.notaires.fr</t>
+          <t>perraud.lyon@notaires.fr</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>office@69095.notaires.fr</t>
-        </is>
-      </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>0474030522</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="inlineStr">
-        <is>
-          <t>0474030522</t>
-        </is>
-      </c>
+          <t>perraud.lyon@notaires.fr</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr"/>
+      <c r="E121" s="7" t="inlineStr"/>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 10 impasse Chavanet 69870 LAMURE-SUR-AZERGUES France</t>
+          <t>Bureau principal 19 boulevard Eugène Deruelle 69003 LYON France</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>Lamure-Sur-Azergues</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-associee-unique-notaire-valle-dazergues</t>
+          <t>https://www.notaires.fr/fr/office/perraud-associes-notaires-sas-0</t>
         </is>
       </c>
       <c r="K121" s="7" t="inlineStr">
@@ -8046,39 +8046,39 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:03</t>
+          <t>2026-08-30 11:03:08</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL CADRAN Notaires Conseils à LYON (69007) | 75 rue Chevreul</t>
+          <t>Office notarial PESSIA Faustine à DOMMARTIN (69380) | 1702 route des Bois</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>faustine.pessia@69072.notaires.fr</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>faustine.pessia@69072.notaires.fr</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>0437261144</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>0437261144</t>
+          <t>0000000000</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 75 rue Chevreul 69007 LYON France</t>
+          <t>Bureau principal 1702 route des Bois 69380 DOMMARTIN France</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="I122" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Dommartin</t>
         </is>
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils</t>
+          <t>https://www.notaires.fr/fr/office/pessia-faustine</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
@@ -8108,39 +8108,39 @@
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:05</t>
+          <t>2026-08-30 11:03:10</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Office notarial SARL CADRAN Notaires Conseils à TASSIN-LA-DEMI-LUNE (69160) | 3 avenue de Lauterbourg</t>
+          <t>Office notarial PICOT Laura à LYON (69006) | 63 rue Boileau</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>laura.picot@69212.notaires.fr</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>accueil@cadran.notaires.fr</t>
+          <t>laura.picot@69212.notaires.fr</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>0478343602</t>
+          <t>0478133758</t>
         </is>
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>0478343602</t>
+          <t>0478133758</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 3 avenue de Lauterbourg 69160 TASSIN-LA-DEMI-LUNE France</t>
+          <t>Bureau principal 63 rue Boileau 69006 LYON France</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
-          <t>Tassin-La-Demi-Lune</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils-0</t>
+          <t>https://www.notaires.fr/fr/office/picot-laura</t>
         </is>
       </c>
       <c r="K123" s="7" t="inlineStr">
@@ -8170,39 +8170,39 @@
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:06</t>
+          <t>2026-08-30 11:03:13</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
-          <t>Office notarial SARL CHAINE ET ASSOCIES NOTAIRES à LYON (69006) | 139 rue Vendôme</t>
+          <t>Office notarial PROUVOST-CLAEYS, SAS à associé unique à L'ARBRESLE (69210) | 193 Route de Sain-Bel</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>etude.chaine@notaires.fr</t>
+          <t>louise.prouvost@69209.notaires.fr</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>etude.chaine@notaires.fr</t>
+          <t>louise.prouvost@69209.notaires.fr</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>0472757600</t>
+          <t>0428299066</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>0472757600</t>
+          <t>0428299066</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 139 rue Vendôme 69006 LYON France</t>
+          <t>Bureau principal 193 Route de Sain-Bel 69210 L'ARBRESLE France</t>
         </is>
       </c>
       <c r="G124" s="5" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="I124" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>L'arbresle</t>
         </is>
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/sarl-chaine-et-associes-notaires</t>
+          <t>https://www.notaires.fr/fr/office/prouvost-claeys-sas-associe-unique</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
@@ -8232,39 +8232,39 @@
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:31:07</t>
+          <t>2026-08-30 11:03:15</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MARIOTTE Stéphanie à LYON (69006) | 10 Boulevard Jules Favre</t>
+          <t>Office notarial RAY et associé, SELARL à SAINT-FONS (69190) | 1 Avenue Jean Jaurès</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>stephanie.mariotte@notaires.fr</t>
+          <t>ray.sassard@notaires.fr</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>stephanie.mariotte@notaires.fr</t>
+          <t>ray.sassard@notaires.fr</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>0481060795</t>
+          <t>0478700047</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>0481060795</t>
+          <t>0478700047</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 10 Boulevard Jules Favre 69006 LYON France</t>
+          <t>Bureau principal 1 Avenue Jean Jaurès 69190 SAINT-FONS France</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
@@ -8279,12 +8279,12 @@
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Saint-Fons</t>
         </is>
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mariotte-stephanie</t>
+          <t>https://www.notaires.fr/fr/office/ray-et-associe-selarl</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr">
@@ -8294,39 +8294,39 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:47</t>
+          <t>2026-08-30 11:03:17</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MATA Victoria à LYON (69008) | 310 Avenue Berthelot</t>
+          <t>Office notarial REAL LEX Notaires à CRAPONNE (69290) | 123 AVENUE PIERRE DUMOND</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>victoria.mata@notaires.fr</t>
+          <t>office69066.craponne@notaires.fr</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>victoria.mata@notaires.fr</t>
+          <t>office69066.craponne@notaires.fr</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>0472780290</t>
+          <t>0478578039</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>0472780290</t>
+          <t>0478578039</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 310 Avenue Berthelot 69008 LYON France</t>
+          <t>Bureau principal 123 AVENUE PIERRE DUMOND 69290 CRAPONNE France</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Craponne</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mata-victoria</t>
+          <t>https://www.notaires.fr/fr/office/real-lex-notaires</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
@@ -8356,39 +8356,39 @@
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:49</t>
+          <t>2026-08-30 11:03:21</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MAUGAIN NOTAIRES, SELARL à LYON (69003) | 34 cours Lafayette</t>
+          <t>Office notarial REBOTIER PERET LEVRAULT ET MERLE NOTAIRES ASSOCIES, SELARL à LYON (69009) | 2 boulevard Antoine de Saint Exupéry</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>bertram.julienne@notaires.fr</t>
+          <t>notaires.vaise@notaires.fr</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>bertram.julienne@notaires.fr</t>
+          <t>notaires.vaise@notaires.fr</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>0472130397</t>
+          <t>0478646749</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>0472130397</t>
+          <t>0478646749</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 34 cours Lafayette 69003 LYON France</t>
+          <t>Bureau principal 2 boulevard Antoine de Saint Exupéry 69009 LYON France</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/maugain-notaires-selarl</t>
+          <t>https://www.notaires.fr/fr/office/rebotier-peret-levrault-et-merle-notaires-associes-selarl</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
@@ -8418,39 +8418,39 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:50</t>
+          <t>2026-08-30 11:03:24</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MERMET Pierre à LIMAS (69400) | 84 rue Henri Dépagneux</t>
+          <t>Office notarial RENETEAU Anaïs à CHAPONOST (69630) | 1 Route des Troques</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>pierre.mermet@notaires.fr</t>
+          <t>anais.reneteau@reneteau.notaires.fr</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>pierre.mermet@notaires.fr</t>
+          <t>anais.reneteau@reneteau.notaires.fr</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>0474045153</t>
+          <t>0478563572</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>0474045153</t>
+          <t>0478563572</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 84 rue Henri Dépagneux 69400 LIMAS France</t>
+          <t>Bureau principal 1 Route des Troques 69630 CHAPONOST France</t>
         </is>
       </c>
       <c r="G128" s="5" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
-          <t>Limas</t>
+          <t>Chaponost</t>
         </is>
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/mermet-pierre</t>
+          <t>https://www.notaires.fr/fr/office/reneteau-anais</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
@@ -8480,39 +8480,39 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:51</t>
+          <t>2026-08-30 11:03:26</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MESSERI Aurore à LYON (69003) | 6 cours de la Liberté</t>
+          <t>Office notarial REY Karyne à LYON (69002) | 3 rue Victor Hugo</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>aurore.messeri@notaires.fr</t>
+          <t>etude.rey@notaires.fr</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>aurore.messeri@notaires.fr</t>
+          <t>etude.rey@notaires.fr</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>0481061360</t>
+          <t>0472162590</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>0481061360</t>
+          <t>0472162590</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 6 cours de la Liberté 69003 LYON France</t>
+          <t>Bureau principal 3 rue Victor Hugo 69002 LYON France</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="J129" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/messeri-aurore</t>
+          <t>https://www.notaires.fr/fr/office/rey-karyne</t>
         </is>
       </c>
       <c r="K129" s="7" t="inlineStr">
@@ -8542,39 +8542,39 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:53</t>
+          <t>2026-08-30 11:03:27</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MONTEL Hélène à VERNAISON (69390) | 336 rue de la Fée des Eaux</t>
+          <t>Office notarial ROBIN Axel à LYON (69003) | 123 cours Albert Thomas</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>h.montel@notaires.fr</t>
+          <t>etude@69047.notaires.fr</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>h.montel@notaires.fr</t>
+          <t>etude@69047.notaires.fr</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>0482531832</t>
+          <t>0449232420</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>0482531832</t>
+          <t>0449232420</t>
         </is>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 336 rue de la Fée des Eaux 69390 VERNAISON France</t>
+          <t>Bureau principal 123 cours Albert Thomas 69003 LYON France</t>
         </is>
       </c>
       <c r="G130" s="5" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>Vernaison</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/montel-helene</t>
+          <t>https://www.notaires.fr/fr/office/robin-axel</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
@@ -8604,39 +8604,39 @@
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:55</t>
+          <t>2026-08-30 11:03:30</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MOREL Laetitia à LYON (69003) | 127 cours du Docteur Long</t>
+          <t>Office notarial ROCHELOIS LYON, SELAS à LYON (69003) | 10-12 boulevard Marius Vivier Merle</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>morel.laetitia@notaires.fr</t>
+          <t>contact@rocheloislyon.notaires.fr</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>morel.laetitia@notaires.fr</t>
+          <t>contact@rocheloislyon.notaires.fr</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>0481061095</t>
+          <t>0487658201</t>
         </is>
       </c>
       <c r="E131" s="7" t="inlineStr">
         <is>
-          <t>0481061095</t>
+          <t>0487658201</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 127 cours du Docteur Long 69003 LYON France</t>
+          <t>Bureau principal 10-12 boulevard Marius Vivier Merle 69003 LYON France</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="J131" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/morel-laetitia</t>
+          <t>https://www.notaires.fr/fr/office/rochelois-lyon-selas</t>
         </is>
       </c>
       <c r="K131" s="7" t="inlineStr">
@@ -8666,39 +8666,39 @@
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:57</t>
+          <t>2026-08-30 11:03:32</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Office notarial MURANA-CHARLUET Raphaëlle à SAINT-DIDIER-AU-MONT-D'OR (69370) | 11 rue Voie Lactée</t>
+          <t>Office notarial ROSTAING-MUSSIO et associée, SELARL à LYON (69003) | 40 Rue Antoine Charial</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>r.murana@notaires.fr</t>
+          <t>corine.mussio@notaires.fr</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>r.murana@notaires.fr</t>
+          <t>corine.mussio@notaires.fr</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>0485680145</t>
+          <t>0472459539</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>0485680145</t>
+          <t>0472459539</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 11 rue Voie Lactée 69370 SAINT-DIDIER-AU-MONT-D'OR France</t>
+          <t>Bureau principal 40 Rue Antoine Charial 69003 LYON France</t>
         </is>
       </c>
       <c r="G132" s="5" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="I132" s="5" t="inlineStr">
         <is>
-          <t>Saint-Didier-Au-Mont-D'or</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J132" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/murana-charluet-raphaelle</t>
+          <t>https://www.notaires.fr/fr/office/rostaing-mussio-et-associee-selarl-0</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
@@ -8728,39 +8728,39 @@
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:59</t>
+          <t>2026-08-30 11:03:34</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Office notarial MURAT Marie-Pierre à VILLEURBANNE (69100) | 109 Cours Emile Zola</t>
+          <t>Office notarial RUCHON Edouard à LYON (69005) | 60 avenue du Point du Jour</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>office.murat@notaires.fr</t>
+          <t>edouard.ruchon@notaires.fr</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>office.murat@notaires.fr</t>
+          <t>edouard.ruchon@notaires.fr</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>0437431922</t>
+          <t>0472544808</t>
         </is>
       </c>
       <c r="E133" s="7" t="inlineStr">
         <is>
-          <t>0437431922</t>
+          <t>0472544808</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 109 Cours Emile Zola 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 60 avenue du Point du Jour 69005 LYON France</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="I133" s="7" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J133" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/murat-marie-pierre</t>
+          <t>https://www.notaires.fr/fr/office/ruchon-edouard</t>
         </is>
       </c>
       <c r="K133" s="7" t="inlineStr">
@@ -8790,39 +8790,39 @@
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:01</t>
+          <t>2026-08-30 11:03:36</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NARDINI Magali à CHAZAY-D'AZERGUES (69380) | 9 rue Marius Berliet</t>
+          <t>Office notarial S2R NOTAIRES CONSEILS, SELARL à LYON (69006) | 50 boulevard des Belges</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>office.nardini@notaires.fr</t>
+          <t>simon.reboul@69225.notaires.fr</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>office.nardini@notaires.fr</t>
+          <t>simon.reboul@69225.notaires.fr</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>04.86.11.05.15</t>
+          <t>0437479982</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>04.86.11.05.15</t>
+          <t>0437479982</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 9 rue Marius Berliet 69380 CHAZAY-D'AZERGUES France</t>
+          <t>Bureau principal 50 boulevard des Belges 69006 LYON France</t>
         </is>
       </c>
       <c r="G134" s="5" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
-          <t>Chazay-D'azergues</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J134" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/nardini-magali</t>
+          <t>https://www.notaires.fr/fr/office/s2r-notaires-conseils-selarl</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
@@ -8852,39 +8852,39 @@
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:03</t>
+          <t>2026-08-30 11:03:37</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NICOLLE et associés à LYON (69003) | 90 rue Paul Bert</t>
+          <t>Office notarial SALAGNAT Frédéric à CHASSIEU (69680) | 56 route de Genas</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>christian.nicolle@notaires.fr</t>
+          <t>salagnat@notaires.fr</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>christian.nicolle@notaires.fr</t>
+          <t>salagnat@notaires.fr</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>0492309230</t>
+          <t>0472797470</t>
         </is>
       </c>
       <c r="E135" s="7" t="inlineStr">
         <is>
-          <t>0492309230</t>
+          <t>0472797470</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 90 rue Paul Bert 69003 LYON France</t>
+          <t>Bureau principal 56 route de Genas 69680 CHASSIEU France</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="I135" s="7" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Chassieu</t>
         </is>
       </c>
       <c r="J135" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/nicolle-et-associes-0</t>
+          <t>https://www.notaires.fr/fr/office/salagnat-frederic</t>
         </is>
       </c>
       <c r="K135" s="7" t="inlineStr">
@@ -8914,39 +8914,39 @@
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:05</t>
+          <t>2026-08-30 11:03:39</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOHARET Françoise à LYON (69007) | 200 AVENUE JEAN JAURES</t>
+          <t>Office notarial SALICHON &amp; ASSOCIES, SARL à LYON (69006) | 3 Cours Franklin Roosevelt</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>office.noharet@notaires.fr</t>
+          <t>salichonetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>office.noharet@notaires.fr</t>
+          <t>salichonetassocies@notaires.fr</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>0437376850</t>
+          <t>0478931098</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>0437376850</t>
+          <t>0478931098</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 200 AVENUE JEAN JAURES 69007 LYON France</t>
+          <t>Bureau principal 3 Cours Franklin Roosevelt 69006 LYON France</t>
         </is>
       </c>
       <c r="G136" s="5" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/noharet-francoise</t>
+          <t>https://www.notaires.fr/fr/office/salichon-associes-sarl</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
@@ -8976,39 +8976,39 @@
       </c>
       <c r="L136" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:07</t>
+          <t>2026-08-30 11:03:41</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOT’ACTES MARCY à MARCY (69480) | 20, Rue de la Tour</t>
+          <t>Office notarial SARL à associé unique GONDRAN, notaire associée à BELLEVILLE (69220) | 19 rue des Remparts</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>renaud.fontaine@69169.notaires.fr</t>
+          <t>anne.gondran@69248.notaires.fr</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>renaud.fontaine@69169.notaires.fr</t>
+          <t>anne.gondran@69248.notaires.fr</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>0437552285</t>
+          <t>04 87 01 02 10</t>
         </is>
       </c>
       <c r="E137" s="7" t="inlineStr">
         <is>
-          <t>0437552285</t>
+          <t>04 87 01 02 10</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 20, Rue de la Tour 69480 MARCY France</t>
+          <t>Bureau principal 19 rue des Remparts 69220 BELLEVILLE France</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="I137" s="7" t="inlineStr">
         <is>
-          <t>Marcy</t>
+          <t>Belleville</t>
         </is>
       </c>
       <c r="J137" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notactes-marcy</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-gondran-notaire-associee</t>
         </is>
       </c>
       <c r="K137" s="7" t="inlineStr">
@@ -9038,39 +9038,39 @@
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:09</t>
+          <t>2026-08-30 11:03:44</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOTAEM et associés à SAINT-CYR-AU-MONT-D'OR (69450) | 1 rue Reynier</t>
+          <t>Office notarial SARL à associé unique Notaires du Promenoir à VILLEFRANCHE-SUR-SAÔNE (69400) | 61 rue d'Anse</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>notaem@notaem.notaires.fr</t>
+          <t>etude@promenoir.notaires.fr</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>notaem@notaem.notaires.fr</t>
+          <t>etude@promenoir.notaires.fr</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>0478472483</t>
+          <t>0474654500</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>0478472483</t>
+          <t>0474654500</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 1 rue Reynier 69450 SAINT-CYR-AU-MONT-D'OR France</t>
+          <t>Bureau principal 61 rue d'Anse 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
         </is>
       </c>
       <c r="G138" s="5" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="I138" s="5" t="inlineStr">
         <is>
-          <t>Saint-Cyr-Au-Mont-D'or</t>
+          <t>Villefranche-Sur-Saône</t>
         </is>
       </c>
       <c r="J138" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notaem-et-associes</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-notaires-du-promenoir</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
@@ -9100,39 +9100,39 @@
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:11</t>
+          <t>2026-08-30 11:03:45</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Office notarial NOTAIRES GAMBETTA à VILLEFRANCHE-SUR-SAÔNE (69400) | 257 rue Boiron</t>
+          <t>Office notarial SARL à associé unique OFFICE NOTARIAL DE LA TABLE DE PIERRE à FRANCHEVILLE (69340) | 26 Avenue de la Table de Pierre</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>secretariat@etudegambetta.notaires.fr</t>
+          <t>christelle.farce@69220.notaires.fr</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>secretariat@etudegambetta.notaires.fr</t>
+          <t>christelle.farce@69220.notaires.fr</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>0474029910</t>
+          <t>0437202524</t>
         </is>
       </c>
       <c r="E139" s="7" t="inlineStr">
         <is>
-          <t>0474029910</t>
+          <t>0437202524</t>
         </is>
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 257 rue Boiron 69400 VILLEFRANCHE-SUR-SAÔNE France</t>
+          <t>Bureau principal 26 Avenue de la Table de Pierre 69340 FRANCHEVILLE France</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
@@ -9147,12 +9147,12 @@
       </c>
       <c r="I139" s="7" t="inlineStr">
         <is>
-          <t>Villefranche-Sur-Saône</t>
+          <t>Francheville</t>
         </is>
       </c>
       <c r="J139" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notaires-gambetta</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associe-unique-office-notarial-de-la-table-de-pierre</t>
         </is>
       </c>
       <c r="K139" s="7" t="inlineStr">
@@ -9162,39 +9162,39 @@
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:11</t>
+          <t>2026-08-30 11:03:47</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="inlineStr">
         <is>
-          <t>Office notarial NOTARA à LYON (69007) | 152 Grande Rue de la Guillotière</t>
+          <t>Office notarial SARL à associée unique NOTAIRE VALLE D'AZERGUES à LAMURE-SUR-AZERGUES (69870) | 10 impasse Chavanet</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>notara.lyon@notaires.fr</t>
+          <t>office@69095.notaires.fr</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>notara.lyon@notaires.fr</t>
+          <t>office@69095.notaires.fr</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>0983211434</t>
+          <t>0474030522</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>0983211434</t>
+          <t>0474030522</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 152 Grande Rue de la Guillotière 69007 LYON France</t>
+          <t>Bureau principal 10 impasse Chavanet 69870 LAMURE-SUR-AZERGUES France</t>
         </is>
       </c>
       <c r="G140" s="5" t="inlineStr">
@@ -9209,12 +9209,12 @@
       </c>
       <c r="I140" s="5" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lamure-Sur-Azergues</t>
         </is>
       </c>
       <c r="J140" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/notara</t>
+          <t>https://www.notaires.fr/fr/office/sarl-associee-unique-notaire-valle-dazergues</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
@@ -9224,39 +9224,39 @@
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:13</t>
+          <t>2026-08-30 11:03:48</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Office notarial ODO, notaire à THIZY-LES-BOURGS (69240) | 47 RUE JEAN JAURES</t>
+          <t>Office notarial SARL CADRAN Notaires Conseils à LYON (69007) | 75 rue Chevreul</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>notaires.thizy@notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>notaires.thizy@notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>0474640048</t>
+          <t>0437261144</t>
         </is>
       </c>
       <c r="E141" s="7" t="inlineStr">
         <is>
-          <t>0474640048</t>
+          <t>0437261144</t>
         </is>
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 47 RUE JEAN JAURES 69240 THIZY-LES-BOURGS France</t>
+          <t>Bureau principal 75 rue Chevreul 69007 LYON France</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
@@ -9271,12 +9271,12 @@
       </c>
       <c r="I141" s="7" t="inlineStr">
         <is>
-          <t>Thizy-Les-Bourgs</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J141" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/odo-notaire</t>
+          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils</t>
         </is>
       </c>
       <c r="K141" s="7" t="inlineStr">
@@ -9286,39 +9286,39 @@
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:15</t>
+          <t>2026-08-30 11:03:49</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DE PRESSENSE, SELARL à VILLEURBANNE (69100) | 46 rue Francis de Pressensé</t>
+          <t>Office notarial SARL CADRAN Notaires Conseils à TASSIN-LA-DEMI-LUNE (69160) | 3 avenue de Lauterbourg</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>helene.geraud@notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>helene.geraud@notaires.fr</t>
+          <t>accueil@cadran.notaires.fr</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>0437482561</t>
+          <t>0478343602</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>0437482561</t>
+          <t>0478343602</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
-          <t>Bureau principal 46 rue Francis de Pressensé 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 3 avenue de Lauterbourg 69160 TASSIN-LA-DEMI-LUNE France</t>
         </is>
       </c>
       <c r="G142" s="5" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="I142" s="5" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Tassin-La-Demi-Lune</t>
         </is>
       </c>
       <c r="J142" s="5" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-de-pressense-selarl</t>
+          <t>https://www.notaires.fr/fr/office/sarl-cadran-notaires-conseils-0</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
@@ -9348,39 +9348,39 @@
       </c>
       <c r="L142" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:17</t>
+          <t>2026-08-30 11:03:51</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Office notarial OFFICE NOTARIAL DES CHARPENNES-VILLEURBANNE, SELARL à VILLEURBANNE (69100) | 50 A Cours Emile Zola</t>
+          <t>Office notarial SARL CHAINE ET ASSOCIES NOTAIRES à LYON (69006) | 139 rue Vendôme</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>oncv@69136.notaires.fr</t>
+          <t>etude.chaine@notaires.fr</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>oncv@69136.notaires.fr</t>
+          <t>etude.chaine@notaires.fr</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>0472759396</t>
+          <t>0472757600</t>
         </is>
       </c>
       <c r="E143" s="7" t="inlineStr">
         <is>
-          <t>0472759396</t>
+          <t>0472757600</t>
         </is>
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>Bureau principal 50 A Cours Emile Zola 69100 VILLEURBANNE France</t>
+          <t>Bureau principal 139 rue Vendôme 69006 LYON France</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="I143" s="7" t="inlineStr">
         <is>
-          <t>Villeurbanne</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="J143" s="7" t="inlineStr">
         <is>
-          <t>https://www.notaires.fr/fr/office/office-notarial-des-charpennes-villeurbanne-selarl</t>
+          <t>https://www.notaires.fr/fr/office/sarl-chaine-et-associes-notaires</t>
         </is>
       </c>
       <c r="K143" s="7" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L143" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:30:18</t>
+          <t>2026-08-30 11:03:52</t>
         </is>
       </c>
     </row>
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L144" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:28</t>
+          <t>2026-08-30 11:00:39</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:30</t>
+          <t>2026-08-30 11:00:41</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="L146" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:31</t>
+          <t>2026-08-30 11:00:43</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:33</t>
+          <t>2026-08-30 11:00:45</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="L148" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:34</t>
+          <t>2026-08-30 11:00:47</t>
         </is>
       </c>
     </row>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:36</t>
+          <t>2026-08-30 11:00:49</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:38</t>
+          <t>2026-08-30 11:00:51</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:39</t>
+          <t>2026-08-30 11:00:53</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:40</t>
+          <t>2026-08-30 11:00:55</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:42</t>
+          <t>2026-08-30 11:00:57</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:44</t>
+          <t>2026-08-30 11:00:59</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="L155" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:45</t>
+          <t>2026-08-30 11:01:01</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="L156" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:47</t>
+          <t>2026-08-30 11:01:03</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:49</t>
+          <t>2026-08-30 11:01:04</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="L158" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:51</t>
+          <t>2026-08-30 11:01:06</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="L159" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:52</t>
+          <t>2026-08-30 11:01:07</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:55</t>
+          <t>2026-08-30 11:01:09</t>
         </is>
       </c>
     </row>
@@ -10518,7 +10518,7 @@
       </c>
       <c r="L161" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:56</t>
+          <t>2026-08-30 11:01:12</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:58</t>
+          <t>2026-08-30 11:01:14</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="L163" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:00</t>
+          <t>2026-08-30 11:01:16</t>
         </is>
       </c>
     </row>
@@ -10704,7 +10704,7 @@
       </c>
       <c r="L164" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:01</t>
+          <t>2026-08-30 11:01:18</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:03</t>
+          <t>2026-08-30 11:01:21</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="L166" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:05</t>
+          <t>2026-08-30 11:01:24</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="L167" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:07</t>
+          <t>2026-08-30 11:01:27</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:08</t>
+          <t>2026-08-30 11:01:28</t>
         </is>
       </c>
     </row>
@@ -11014,7 +11014,7 @@
       </c>
       <c r="L169" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:10</t>
+          <t>2026-08-30 11:01:31</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:12</t>
+          <t>2026-08-30 11:01:33</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:13</t>
+          <t>2026-08-30 11:01:35</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:15</t>
+          <t>2026-08-30 11:01:37</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:16</t>
+          <t>2026-08-30 11:01:38</t>
         </is>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
       </c>
       <c r="L174" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:18</t>
+          <t>2026-08-30 11:01:40</t>
         </is>
       </c>
     </row>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:20</t>
+          <t>2026-08-30 11:01:42</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="L176" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:21</t>
+          <t>2026-08-30 11:01:45</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="L177" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:22</t>
+          <t>2026-08-30 11:01:47</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:23</t>
+          <t>2026-08-30 11:01:49</t>
         </is>
       </c>
     </row>
@@ -11634,7 +11634,7 @@
       </c>
       <c r="L179" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:24</t>
+          <t>2026-08-30 11:01:51</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="L180" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:26</t>
+          <t>2026-08-30 11:01:52</t>
         </is>
       </c>
     </row>
@@ -11758,7 +11758,7 @@
       </c>
       <c r="L181" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:28</t>
+          <t>2026-08-30 11:01:54</t>
         </is>
       </c>
     </row>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:29</t>
+          <t>2026-08-30 11:01:56</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:31</t>
+          <t>2026-08-30 11:01:57</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:32</t>
+          <t>2026-08-30 11:01:59</t>
         </is>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="L185" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:34</t>
+          <t>2026-08-30 11:02:01</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="L186" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:35</t>
+          <t>2026-08-30 11:02:03</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="L187" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:37</t>
+          <t>2026-08-30 11:02:04</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:38</t>
+          <t>2026-08-30 11:02:05</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12254,7 @@
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:40</t>
+          <t>2026-08-30 11:02:07</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:41</t>
+          <t>2026-08-30 11:02:08</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="L191" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:43</t>
+          <t>2026-08-30 11:02:10</t>
         </is>
       </c>
     </row>
@@ -12440,7 +12440,7 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:44</t>
+          <t>2026-08-30 11:02:11</t>
         </is>
       </c>
     </row>
@@ -12502,7 +12502,7 @@
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:29:46</t>
+          <t>2026-08-30 11:02:13</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="L194" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:04</t>
+          <t>2026-08-30 10:58:58</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="L195" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:04</t>
+          <t>2026-08-30 10:59:00</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="L196" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:05</t>
+          <t>2026-08-30 10:59:03</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="L197" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:07</t>
+          <t>2026-08-30 10:59:04</t>
         </is>
       </c>
     </row>
@@ -12812,7 +12812,7 @@
       </c>
       <c r="L198" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:08</t>
+          <t>2026-08-30 10:59:06</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:10</t>
+          <t>2026-08-30 10:59:08</t>
         </is>
       </c>
     </row>
@@ -12936,7 +12936,7 @@
       </c>
       <c r="L200" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:12</t>
+          <t>2026-08-30 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:13</t>
+          <t>2026-08-30 10:59:12</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="L202" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:16</t>
+          <t>2026-08-30 10:59:15</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13122,7 @@
       </c>
       <c r="L203" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:18</t>
+          <t>2026-08-30 10:59:18</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="L204" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:20</t>
+          <t>2026-08-30 10:59:20</t>
         </is>
       </c>
     </row>
@@ -13246,7 +13246,7 @@
       </c>
       <c r="L205" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:21</t>
+          <t>2026-08-30 10:59:22</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13308,7 @@
       </c>
       <c r="L206" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:23</t>
+          <t>2026-08-30 10:59:24</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="L207" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:25</t>
+          <t>2026-08-30 10:59:25</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="L208" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:27</t>
+          <t>2026-08-30 10:59:27</t>
         </is>
       </c>
     </row>
@@ -13494,7 +13494,7 @@
       </c>
       <c r="L209" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:29</t>
+          <t>2026-08-30 10:59:29</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="L210" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:31</t>
+          <t>2026-08-30 10:59:31</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="L211" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:32</t>
+          <t>2026-08-30 10:59:33</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="L212" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:34</t>
+          <t>2026-08-30 10:59:35</t>
         </is>
       </c>
     </row>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="L213" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:36</t>
+          <t>2026-08-30 10:59:37</t>
         </is>
       </c>
     </row>
@@ -13804,7 +13804,7 @@
       </c>
       <c r="L214" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:38</t>
+          <t>2026-08-30 10:59:39</t>
         </is>
       </c>
     </row>
@@ -13866,7 +13866,7 @@
       </c>
       <c r="L215" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:39</t>
+          <t>2026-08-30 10:59:42</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13928,7 @@
       </c>
       <c r="L216" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:41</t>
+          <t>2026-08-30 10:59:45</t>
         </is>
       </c>
     </row>
@@ -13990,7 +13990,7 @@
       </c>
       <c r="L217" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:43</t>
+          <t>2026-08-30 10:59:47</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14052,7 @@
       </c>
       <c r="L218" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:44</t>
+          <t>2026-08-30 10:59:48</t>
         </is>
       </c>
     </row>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L219" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:46</t>
+          <t>2026-08-30 10:59:50</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
       </c>
       <c r="L220" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:47</t>
+          <t>2026-08-30 10:59:52</t>
         </is>
       </c>
     </row>
@@ -14238,7 +14238,7 @@
       </c>
       <c r="L221" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:49</t>
+          <t>2026-08-30 10:59:53</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="L222" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:51</t>
+          <t>2026-08-30 10:59:55</t>
         </is>
       </c>
     </row>
@@ -14362,7 +14362,7 @@
       </c>
       <c r="L223" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:52</t>
+          <t>2026-08-30 10:59:57</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="L224" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:54</t>
+          <t>2026-08-30 10:59:58</t>
         </is>
       </c>
     </row>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="L225" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:55</t>
+          <t>2026-08-30 11:00:00</t>
         </is>
       </c>
     </row>
@@ -14548,7 +14548,7 @@
       </c>
       <c r="L226" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:57</t>
+          <t>2026-08-30 11:00:02</t>
         </is>
       </c>
     </row>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="L227" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:27:59</t>
+          <t>2026-08-30 11:00:04</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="L228" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:00</t>
+          <t>2026-08-30 11:00:06</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="L229" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:02</t>
+          <t>2026-08-30 11:00:08</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="L230" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:04</t>
+          <t>2026-08-30 11:00:09</t>
         </is>
       </c>
     </row>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="L231" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:06</t>
+          <t>2026-08-30 11:00:11</t>
         </is>
       </c>
     </row>
@@ -14920,7 +14920,7 @@
       </c>
       <c r="L232" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:07</t>
+          <t>2026-08-30 11:00:12</t>
         </is>
       </c>
     </row>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="L233" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:09</t>
+          <t>2026-08-30 11:00:14</t>
         </is>
       </c>
     </row>
@@ -15044,7 +15044,7 @@
       </c>
       <c r="L234" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:11</t>
+          <t>2026-08-30 11:00:16</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="L235" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:13</t>
+          <t>2026-08-30 11:00:19</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15168,7 @@
       </c>
       <c r="L236" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:14</t>
+          <t>2026-08-30 11:00:23</t>
         </is>
       </c>
     </row>
@@ -15230,7 +15230,7 @@
       </c>
       <c r="L237" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:16</t>
+          <t>2026-08-30 11:00:24</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="L238" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:18</t>
+          <t>2026-08-30 11:00:26</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="L239" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:20</t>
+          <t>2026-08-30 11:00:28</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="L240" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:21</t>
+          <t>2026-08-30 11:00:30</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15478,7 @@
       </c>
       <c r="L241" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:23</t>
+          <t>2026-08-30 11:00:32</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="L242" s="5" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:24</t>
+          <t>2026-08-30 11:00:35</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="L243" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23 06:28:26</t>
+          <t>2026-08-30 11:00:36</t>
         </is>
       </c>
     </row>
